--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827DD131-AA09-4B8F-B211-00446D76A3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B45521-67E3-40F5-A969-625CB904174A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -8,13 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B45521-67E3-40F5-A969-625CB904174A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5DC7AB-ECA3-4506-8C82-1270AE563070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="rates" sheetId="1" r:id="rId1"/>
+    <sheet name="rates_alt" sheetId="1" r:id="rId1"/>
+    <sheet name="rates_sw" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="BBDATA">OFFSET('[1]INPUT DATA'!$C$8,0,0,'[1]INPUT DATA'!$A$6,50)</definedName>
+    <definedName name="CalcDate" localSheetId="1">rates_sw!$D$4</definedName>
+    <definedName name="DateList">OFFSET('[1]INPUT DATA'!$B$8,0,0,'[1]INPUT DATA'!$A$6,1)</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
     <t>Tenor</t>
   </si>
@@ -54,13 +63,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -80,14 +95,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{2351E727-7914-4128-83BF-CE6273F2D9EE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -100,6 +117,46 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Read Me "/>
+      <sheetName val="Smith-Wilson RFR"/>
+      <sheetName val="Graphs"/>
+      <sheetName val="INPUT DATA"/>
+      <sheetName val="LOG"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="6">
+          <cell r="A6">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>41640</v>
+          </cell>
+          <cell r="C8">
+            <v>1.8644559400154886E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2492,4 +2549,581 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA0E8BDC-F229-420E-9A56-65EC6A90BF84}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>9.2496718772093669E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1.0589694258098003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1.1032270549913577E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1.1044292518813812E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1.3788334788232146E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1.6944242364738148E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>1.8429378313447282E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>1.8642466810056619E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>2.0102347240970622E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>2.1872288777203999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>2.2981233811356312E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>2.4615215165166154E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>2.5867811793301054E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>2.6940024191389973E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>2.7786457864007751E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>2.7961998837721332E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>2.8432307445889947E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>2.8665104618739178E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>2.8956926872526014E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>2.9492299797021254E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>3.0425194965994863E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>3.0899262864683863E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>3.1509179791222114E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>3.2274458320078969E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>3.3004411020988313E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>3.349589889482734E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28">
+        <v>3.3780265686537352E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>3.4466641415851526E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30">
+        <v>3.4588648213692223E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>3.4633928585448177E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32">
+        <v>3.4923272597156385E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>3.541116892193058E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>3.5713706153336522E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>3.6297765136776385E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>3.6464062868989157E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37">
+        <v>3.6835715037200692E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38">
+        <v>3.7061412798874274E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>3.7461684848288324E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40">
+        <v>3.7774971723381533E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>3.8056420537358172E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>3.8489913626744553E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43">
+        <v>42</v>
+      </c>
+      <c r="C43">
+        <v>3.8828913271326211E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44">
+        <v>43</v>
+      </c>
+      <c r="C44">
+        <v>3.8915424852211743E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45">
+        <v>3.9224144229902523E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46">
+        <v>3.9421649415220895E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47">
+        <v>3.9495100727106977E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48">
+        <v>3.9679731487326481E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+      <c r="C49">
+        <v>3.980159479077483E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50">
+        <v>49</v>
+      </c>
+      <c r="C50">
+        <v>4.0207915648931766E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+      <c r="C51">
+        <v>4.0221039434912016E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5DC7AB-ECA3-4506-8C82-1270AE563070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B13B19-C822-4A05-8626-3D1360020ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rates_alt" sheetId="1" r:id="rId1"/>
     <sheet name="rates_sw" sheetId="2" r:id="rId2"/>
+    <sheet name="spreads_va" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="BBDATA">OFFSET('[1]INPUT DATA'!$C$8,0,0,'[1]INPUT DATA'!$A$6,50)</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>Tenor</t>
   </si>
@@ -58,12 +59,174 @@
   <si>
     <t>LLFR Weights</t>
   </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>CY</t>
+  </si>
+  <si>
+    <t>CZ</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>GR</t>
+  </si>
+  <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>IE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>LU</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>HK</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Issuer</t>
+  </si>
+  <si>
+    <t>Finan_0</t>
+  </si>
+  <si>
+    <t>Finan_1</t>
+  </si>
+  <si>
+    <t>Finan_2</t>
+  </si>
+  <si>
+    <t>Finan_3</t>
+  </si>
+  <si>
+    <t>Finan_4</t>
+  </si>
+  <si>
+    <t>Finan_5</t>
+  </si>
+  <si>
+    <t>Finan_6</t>
+  </si>
+  <si>
+    <t>Nonfinan_0</t>
+  </si>
+  <si>
+    <t>Nonfinan_1</t>
+  </si>
+  <si>
+    <t>Nonfinan_2</t>
+  </si>
+  <si>
+    <t>Nonfinan_3</t>
+  </si>
+  <si>
+    <t>Nonfinan_4</t>
+  </si>
+  <si>
+    <t>Nonfinan_5</t>
+  </si>
+  <si>
+    <t>Nonfinan_6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,16 +240,48 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,19 +289,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{2351E727-7914-4128-83BF-CE6273F2D9EE}"/>
+    <cellStyle name="Percent 2" xfId="2" xr:uid="{8E3C7290-F3EB-4F4F-810B-1E8706B54683}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9958800012207406E-2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9958800012207406E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3126,4 +3365,4042 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E398A87-82CA-4B50-B75F-313C6B1D2BBE}">
+  <dimension ref="A1:U53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+      <c r="N1">
+        <v>13</v>
+      </c>
+      <c r="O1">
+        <v>14</v>
+      </c>
+      <c r="P1">
+        <v>15</v>
+      </c>
+      <c r="Q1">
+        <v>16</v>
+      </c>
+      <c r="R1">
+        <v>17</v>
+      </c>
+      <c r="S1">
+        <v>18</v>
+      </c>
+      <c r="T1">
+        <v>19</v>
+      </c>
+      <c r="U1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <f ca="1">RAND()</f>
+        <v>0.32879153275548356</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:R3" ca="1" si="0">RAND()</f>
+        <v>0.75329708019983532</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.1900882851673584E-2</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.5561343813362567</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.5156789691012214E-2</v>
+      </c>
+      <c r="G2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.8057504005152456</v>
+      </c>
+      <c r="H2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.89500126908120936</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.99169631016811666</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.97791454914364528</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.72527063721151097</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.3263343896113065E-2</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.35624123280862974</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.2883324211136914</v>
+      </c>
+      <c r="O2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.46798847437607005</v>
+      </c>
+      <c r="P2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.99718939412882324</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.11386781022712889</v>
+      </c>
+      <c r="R2">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.96008610376158932</v>
+      </c>
+      <c r="S2">
+        <f t="shared" ref="S2:U3" ca="1" si="1">RAND()</f>
+        <v>0.13331338367232315</v>
+      </c>
+      <c r="T2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.48135203321645015</v>
+      </c>
+      <c r="U2">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.1857418944855516E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <f ca="1">RAND()</f>
+        <v>0.81370766511264525</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.72667639676506335</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.91791747155625947</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.63886731249650153</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.1382472643246007E-2</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.11399323540280337</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.34037395865969178</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.5821963287956976</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.21568181537834574</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.18655112329081802</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.36796995168392022</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.12161721263099567</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.3780544620275168</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.2360732544573324</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.49096868533516302</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.12580437303107805</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.33499540482954648</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.34019605613945936</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.31391710111168736</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.23856446983787505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <f t="shared" ref="B10:Q12" ca="1" si="2">RAND()</f>
+        <v>0.28609500297072543</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.19901660806193511</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.6581556714443989</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.81268342660872817</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.46201883193962578</v>
+      </c>
+      <c r="G10">
+        <f t="shared" ca="1" si="2"/>
+        <v>3.1848856190636488E-2</v>
+      </c>
+      <c r="H10">
+        <f t="shared" ca="1" si="2"/>
+        <v>2.5473278331028082E-2</v>
+      </c>
+      <c r="I10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.54573043006149879</v>
+      </c>
+      <c r="J10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.87220071738587091</v>
+      </c>
+      <c r="K10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.14212163255109345</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.11214109566507213</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.14724270150243501</v>
+      </c>
+      <c r="N10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.40379769916163677</v>
+      </c>
+      <c r="O10">
+        <f t="shared" ca="1" si="2"/>
+        <v>2.7415107181676612E-2</v>
+      </c>
+      <c r="P10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.80284652653707622</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.15587525646002254</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R10:U12" ca="1" si="3">RAND()</f>
+        <v>0.27685248365824044</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.45331814262553383</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.70355483833213617</v>
+      </c>
+      <c r="U10">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.14894707603706447</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.90743037639072321</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.20574770964166222</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ca="1" si="2"/>
+        <v>9.41107062964186E-2</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.99744152501241889</v>
+      </c>
+      <c r="F11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.28064048819033727</v>
+      </c>
+      <c r="G11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.14284376757063966</v>
+      </c>
+      <c r="H11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.98168448579099199</v>
+      </c>
+      <c r="I11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.5311564549363873</v>
+      </c>
+      <c r="J11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.80787625451015044</v>
+      </c>
+      <c r="K11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.65142579502085329</v>
+      </c>
+      <c r="L11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.49402380367600263</v>
+      </c>
+      <c r="M11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.37757229012610438</v>
+      </c>
+      <c r="N11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.55052715449365164</v>
+      </c>
+      <c r="O11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.33462903891059315</v>
+      </c>
+      <c r="P11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.15915411683399305</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.63819451715410946</v>
+      </c>
+      <c r="R11">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.7233719387003148</v>
+      </c>
+      <c r="S11">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.92659352795056915</v>
+      </c>
+      <c r="T11">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.99945635434475089</v>
+      </c>
+      <c r="U11">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.71338484827790904</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.37006668095109985</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.79716740534033093</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.9751008956793995</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.21667400190137687</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.81356617706448275</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.70700524294876177</v>
+      </c>
+      <c r="H12">
+        <f t="shared" ca="1" si="2"/>
+        <v>5.6252375527537368E-2</v>
+      </c>
+      <c r="I12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.11559376073194094</v>
+      </c>
+      <c r="J12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.47974866185919873</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.68442313704009405</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.38658597455614929</v>
+      </c>
+      <c r="M12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.12435175477281857</v>
+      </c>
+      <c r="N12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.55063765349971527</v>
+      </c>
+      <c r="O12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.91083068253644817</v>
+      </c>
+      <c r="P12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.73809565011987632</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.83927346103975875</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.99867259409797349</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.66610466188117845</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.24754690443470928</v>
+      </c>
+      <c r="U12">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.76494809582672518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="4">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16:Q17" ca="1" si="4">RAND()</f>
+        <v>0.95534972573863486</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.23485379432362419</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.84728786303754444</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.24321198532369359</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.63006314130900631</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.33350457822470003</v>
+      </c>
+      <c r="H16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.16691724858741541</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ca="1" si="4"/>
+        <v>7.6089777928422864E-2</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.16623449889883746</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.92462164955751414</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.36691439299406137</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.2504461784666786</v>
+      </c>
+      <c r="N16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.21619525436290832</v>
+      </c>
+      <c r="O16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.59402016706608063</v>
+      </c>
+      <c r="P16">
+        <f t="shared" ca="1" si="4"/>
+        <v>3.0641000245942851E-2</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" ca="1" si="4"/>
+        <v>4.3878823057493355E-2</v>
+      </c>
+      <c r="R16">
+        <f t="shared" ref="R16:U17" ca="1" si="5">RAND()</f>
+        <v>0.4293019588990965</v>
+      </c>
+      <c r="S16">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.39789977271852361</v>
+      </c>
+      <c r="T16">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.26191266268874547</v>
+      </c>
+      <c r="U16">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.53661846874155383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.82937223374804547</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.97268840248893473</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ca="1" si="4"/>
+        <v>5.1421126556198349E-2</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.58081945667721713</v>
+      </c>
+      <c r="F17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.83667692845124464</v>
+      </c>
+      <c r="G17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.24482802003561155</v>
+      </c>
+      <c r="H17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.31548771507875961</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.17734510689275873</v>
+      </c>
+      <c r="J17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.53126211980220506</v>
+      </c>
+      <c r="K17">
+        <f t="shared" ca="1" si="4"/>
+        <v>4.8545390185432691E-3</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ca="1" si="4"/>
+        <v>1.2201525619716436E-2</v>
+      </c>
+      <c r="M17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.63129449866576082</v>
+      </c>
+      <c r="N17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.2028270507463461</v>
+      </c>
+      <c r="O17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.28585956529037393</v>
+      </c>
+      <c r="P17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.25838801163224712</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0.34673099599185009</v>
+      </c>
+      <c r="R17">
+        <f t="shared" ca="1" si="5"/>
+        <v>8.8205666480333345E-2</v>
+      </c>
+      <c r="S17">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.78341955440427147</v>
+      </c>
+      <c r="T17">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.90934797600586259</v>
+      </c>
+      <c r="U17">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.69994918789379978</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4">
+        <v>0</v>
+      </c>
+      <c r="P22" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23">
+        <f t="shared" ref="B23:U23" ca="1" si="6">RAND()</f>
+        <v>0.35885620650313865</v>
+      </c>
+      <c r="C23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.17140996871985015</v>
+      </c>
+      <c r="D23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.79979857821667899</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.45080413722546753</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.28009459146845528</v>
+      </c>
+      <c r="G23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.70738348751093039</v>
+      </c>
+      <c r="H23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.40846745432301867</v>
+      </c>
+      <c r="I23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.23370295854440104</v>
+      </c>
+      <c r="J23">
+        <f t="shared" ca="1" si="6"/>
+        <v>6.1671551435345084E-2</v>
+      </c>
+      <c r="K23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.23762893064163748</v>
+      </c>
+      <c r="L23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.64323777939948223</v>
+      </c>
+      <c r="M23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.2229812006428803</v>
+      </c>
+      <c r="N23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.93698742344403418</v>
+      </c>
+      <c r="O23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.88635402981358402</v>
+      </c>
+      <c r="P23">
+        <f t="shared" ca="1" si="6"/>
+        <v>3.8859684963647667E-2</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.70250973248518389</v>
+      </c>
+      <c r="R23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.50839085522241434</v>
+      </c>
+      <c r="S23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.92569618413002097</v>
+      </c>
+      <c r="T23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.20423082076717403</v>
+      </c>
+      <c r="U23">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.68679146529953694</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>0</v>
+      </c>
+      <c r="R24" s="4">
+        <v>0</v>
+      </c>
+      <c r="S24" s="4">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ref="B25:Q26" ca="1" si="7">RAND()</f>
+        <v>6.9596003511846694E-2</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ca="1" si="7"/>
+        <v>4.685267232306678E-2</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.34100079253814419</v>
+      </c>
+      <c r="E25">
+        <f t="shared" ca="1" si="7"/>
+        <v>1.3263426762092023E-2</v>
+      </c>
+      <c r="F25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.86461897616754946</v>
+      </c>
+      <c r="G25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.85777521481674168</v>
+      </c>
+      <c r="H25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.98181061811941095</v>
+      </c>
+      <c r="I25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.94106864811833668</v>
+      </c>
+      <c r="J25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.50529669625722451</v>
+      </c>
+      <c r="K25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.54211918581221841</v>
+      </c>
+      <c r="L25">
+        <f t="shared" ca="1" si="7"/>
+        <v>1.456147084501036E-2</v>
+      </c>
+      <c r="M25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.41901791669933419</v>
+      </c>
+      <c r="N25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.14958119485079668</v>
+      </c>
+      <c r="O25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.15998919757108654</v>
+      </c>
+      <c r="P25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.97313672829891562</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.76506546357494587</v>
+      </c>
+      <c r="R25">
+        <f t="shared" ref="R25:U26" ca="1" si="8">RAND()</f>
+        <v>0.59396988012778495</v>
+      </c>
+      <c r="S25">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.39422154094035644</v>
+      </c>
+      <c r="T25">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.90266512462109505</v>
+      </c>
+      <c r="U25">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.2933675523585132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.54383009819791583</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.76735047814612856</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.38575361382064821</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ca="1" si="7"/>
+        <v>4.1354739565843235E-2</v>
+      </c>
+      <c r="F26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.94107659743992844</v>
+      </c>
+      <c r="G26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.18952877832710358</v>
+      </c>
+      <c r="H26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.58154519283944051</v>
+      </c>
+      <c r="I26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.39973671646996933</v>
+      </c>
+      <c r="J26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.34883583710826815</v>
+      </c>
+      <c r="K26">
+        <f t="shared" ca="1" si="7"/>
+        <v>7.1760913862593423E-2</v>
+      </c>
+      <c r="L26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.84991410937227296</v>
+      </c>
+      <c r="M26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.33197163905428217</v>
+      </c>
+      <c r="N26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.92415384154134284</v>
+      </c>
+      <c r="O26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.97908013475248312</v>
+      </c>
+      <c r="P26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.6582481913963828</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.35771602059493302</v>
+      </c>
+      <c r="R26">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.2028703004594119</v>
+      </c>
+      <c r="S26">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.10831814614954061</v>
+      </c>
+      <c r="T26">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.44242745739253952</v>
+      </c>
+      <c r="U26">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.25850868240146729</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="4">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4">
+        <v>0</v>
+      </c>
+      <c r="N27" s="4">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4">
+        <v>0</v>
+      </c>
+      <c r="P27" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>0</v>
+      </c>
+      <c r="R27" s="4">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ref="B28:Q30" ca="1" si="9">RAND()</f>
+        <v>0.95667947026854661</v>
+      </c>
+      <c r="C28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.19375468102596272</v>
+      </c>
+      <c r="D28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.89214565312181759</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.85401145105068399</v>
+      </c>
+      <c r="F28">
+        <f t="shared" ca="1" si="9"/>
+        <v>2.2549564321348248E-2</v>
+      </c>
+      <c r="G28">
+        <f t="shared" ca="1" si="9"/>
+        <v>9.2128023342778143E-2</v>
+      </c>
+      <c r="H28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.50952461353588185</v>
+      </c>
+      <c r="I28">
+        <f t="shared" ca="1" si="9"/>
+        <v>3.8064074340413034E-2</v>
+      </c>
+      <c r="J28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.56128826541091503</v>
+      </c>
+      <c r="K28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.86035471067916003</v>
+      </c>
+      <c r="L28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.29394907435368389</v>
+      </c>
+      <c r="M28">
+        <f t="shared" ca="1" si="9"/>
+        <v>9.901745767207204E-2</v>
+      </c>
+      <c r="N28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.93498291231659236</v>
+      </c>
+      <c r="O28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.43854435212754395</v>
+      </c>
+      <c r="P28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.24087604657069961</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.70770046217672056</v>
+      </c>
+      <c r="R28">
+        <f t="shared" ref="R28:U30" ca="1" si="10">RAND()</f>
+        <v>0.50292779738814197</v>
+      </c>
+      <c r="S28">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.40028064815595499</v>
+      </c>
+      <c r="T28">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.40241224920296703</v>
+      </c>
+      <c r="U28">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.30119091383404994</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.74374214595681942</v>
+      </c>
+      <c r="C29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.75938590469171752</v>
+      </c>
+      <c r="D29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.93011609701697184</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.57712769404625541</v>
+      </c>
+      <c r="F29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.70729979614367455</v>
+      </c>
+      <c r="G29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.94648696384037168</v>
+      </c>
+      <c r="H29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.25588497490452788</v>
+      </c>
+      <c r="I29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.80936653395773595</v>
+      </c>
+      <c r="J29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.40609963021549866</v>
+      </c>
+      <c r="K29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.61234768751097113</v>
+      </c>
+      <c r="L29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.16013121903369898</v>
+      </c>
+      <c r="M29">
+        <f t="shared" ca="1" si="9"/>
+        <v>7.3046434896776424E-2</v>
+      </c>
+      <c r="N29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.30160494982441832</v>
+      </c>
+      <c r="O29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.82040685606814112</v>
+      </c>
+      <c r="P29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.56721943303947464</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.4628542506292832</v>
+      </c>
+      <c r="R29">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.50934203131306777</v>
+      </c>
+      <c r="S29">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.55580351844379328</v>
+      </c>
+      <c r="T29">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.63727720797744858</v>
+      </c>
+      <c r="U29">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.98301536133943557</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.36148837382099863</v>
+      </c>
+      <c r="C30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.51505299655315262</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ca="1" si="9"/>
+        <v>4.429766998240614E-2</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.68246213387612298</v>
+      </c>
+      <c r="F30">
+        <f t="shared" ca="1" si="9"/>
+        <v>8.4300259559227597E-2</v>
+      </c>
+      <c r="G30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.8510177614821306</v>
+      </c>
+      <c r="H30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.70786205880811481</v>
+      </c>
+      <c r="I30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.10045427695553721</v>
+      </c>
+      <c r="J30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.3484268077353353</v>
+      </c>
+      <c r="K30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.79747706995973167</v>
+      </c>
+      <c r="L30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.56341775754542944</v>
+      </c>
+      <c r="M30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.97542467492953178</v>
+      </c>
+      <c r="N30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.3819625859787652</v>
+      </c>
+      <c r="O30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.11808170606109303</v>
+      </c>
+      <c r="P30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.50859808957797037</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.21988592180736355</v>
+      </c>
+      <c r="R30">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.61352841899286936</v>
+      </c>
+      <c r="S30">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.86814654592186657</v>
+      </c>
+      <c r="T30">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.10755148378222612</v>
+      </c>
+      <c r="U30">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.69886661853005705</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0</v>
+      </c>
+      <c r="C31" s="4">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4">
+        <v>0</v>
+      </c>
+      <c r="P31" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>0</v>
+      </c>
+      <c r="R31" s="4">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4">
+        <v>0</v>
+      </c>
+      <c r="T31" s="4">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="4">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4">
+        <v>0</v>
+      </c>
+      <c r="P32" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>0</v>
+      </c>
+      <c r="R32" s="4">
+        <v>0</v>
+      </c>
+      <c r="S32" s="4">
+        <v>0</v>
+      </c>
+      <c r="T32" s="4">
+        <v>0</v>
+      </c>
+      <c r="U32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33">
+        <f t="shared" ref="B33:Q36" ca="1" si="11">RAND()</f>
+        <v>0.2634511635444966</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.4463431608790589</v>
+      </c>
+      <c r="D33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.70657141913060417</v>
+      </c>
+      <c r="E33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.24433142676032149</v>
+      </c>
+      <c r="F33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.43080012376299925</v>
+      </c>
+      <c r="G33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.71352361632608918</v>
+      </c>
+      <c r="H33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.34005440264391651</v>
+      </c>
+      <c r="I33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.64216999517685902</v>
+      </c>
+      <c r="J33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.8702032287094642</v>
+      </c>
+      <c r="K33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.33246818839868042</v>
+      </c>
+      <c r="L33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.64536701163164323</v>
+      </c>
+      <c r="M33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.65058925503219722</v>
+      </c>
+      <c r="N33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.39520471785370215</v>
+      </c>
+      <c r="O33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.88238127239727049</v>
+      </c>
+      <c r="P33">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.13463568534008441</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" ca="1" si="11"/>
+        <v>3.0403962907946225E-2</v>
+      </c>
+      <c r="R33">
+        <f t="shared" ref="R33:U36" ca="1" si="12">RAND()</f>
+        <v>0.65220534625959348</v>
+      </c>
+      <c r="S33">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.98335713268441283</v>
+      </c>
+      <c r="T33">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.26541324930745136</v>
+      </c>
+      <c r="U33">
+        <f t="shared" ca="1" si="12"/>
+        <v>6.4855035469933098E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.65861206988009846</v>
+      </c>
+      <c r="C34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.6120927366333232</v>
+      </c>
+      <c r="D34">
+        <f t="shared" ca="1" si="11"/>
+        <v>4.3503797082272921E-2</v>
+      </c>
+      <c r="E34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.45424005200862849</v>
+      </c>
+      <c r="F34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.51512152829123181</v>
+      </c>
+      <c r="G34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.25998102799536293</v>
+      </c>
+      <c r="H34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.2814042808224605</v>
+      </c>
+      <c r="I34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.31204611425582152</v>
+      </c>
+      <c r="J34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.52475395022722771</v>
+      </c>
+      <c r="K34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.64312989459403247</v>
+      </c>
+      <c r="L34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.69134569109698074</v>
+      </c>
+      <c r="M34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.71510220992878526</v>
+      </c>
+      <c r="N34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.5039163844293979</v>
+      </c>
+      <c r="O34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.83447538751899919</v>
+      </c>
+      <c r="P34">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.81279637634634183</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" ca="1" si="11"/>
+        <v>3.7267947777835153E-2</v>
+      </c>
+      <c r="R34">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.23215656683986641</v>
+      </c>
+      <c r="S34">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.21136315709749154</v>
+      </c>
+      <c r="T34">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.41054547023373722</v>
+      </c>
+      <c r="U34">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.32131552829721832</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.16952758299547455</v>
+      </c>
+      <c r="C35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.89388600643893024</v>
+      </c>
+      <c r="D35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.91217695500656182</v>
+      </c>
+      <c r="E35">
+        <f t="shared" ca="1" si="11"/>
+        <v>7.5736230114858305E-2</v>
+      </c>
+      <c r="F35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.33775992264538013</v>
+      </c>
+      <c r="G35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.84231309579038649</v>
+      </c>
+      <c r="H35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.18433247814230891</v>
+      </c>
+      <c r="I35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.51793959810063128</v>
+      </c>
+      <c r="J35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.84455510333793782</v>
+      </c>
+      <c r="K35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.3492378383107948</v>
+      </c>
+      <c r="L35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.42609446193086431</v>
+      </c>
+      <c r="M35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.12823615588780668</v>
+      </c>
+      <c r="N35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.51682758308182353</v>
+      </c>
+      <c r="O35">
+        <f t="shared" ca="1" si="11"/>
+        <v>3.0802476165482373E-3</v>
+      </c>
+      <c r="P35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.72217937124338205</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.16458460566310207</v>
+      </c>
+      <c r="R35">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.47699913200226185</v>
+      </c>
+      <c r="S35">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.75615239683645741</v>
+      </c>
+      <c r="T35">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.83390251894015988</v>
+      </c>
+      <c r="U35">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.76859695945976114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.94985306809239678</v>
+      </c>
+      <c r="C36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.30972377122713579</v>
+      </c>
+      <c r="D36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.54183490229249254</v>
+      </c>
+      <c r="E36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.71472035209710028</v>
+      </c>
+      <c r="F36">
+        <f t="shared" ca="1" si="11"/>
+        <v>9.5305584647929709E-2</v>
+      </c>
+      <c r="G36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.82667617956994532</v>
+      </c>
+      <c r="H36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.74796105154779358</v>
+      </c>
+      <c r="I36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.57852649591102978</v>
+      </c>
+      <c r="J36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.74218905026510495</v>
+      </c>
+      <c r="K36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.12021201655803782</v>
+      </c>
+      <c r="L36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.86082952374411537</v>
+      </c>
+      <c r="M36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.87524418251320235</v>
+      </c>
+      <c r="N36">
+        <f t="shared" ca="1" si="11"/>
+        <v>6.9070581112578466E-2</v>
+      </c>
+      <c r="O36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.60717577720977822</v>
+      </c>
+      <c r="P36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.69012769632312176</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.29262923959210463</v>
+      </c>
+      <c r="R36">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.93956076709133196</v>
+      </c>
+      <c r="S36">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.10927441410059446</v>
+      </c>
+      <c r="T36">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.67806700068193104</v>
+      </c>
+      <c r="U36">
+        <f t="shared" ca="1" si="12"/>
+        <v>4.8665905693893174E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="4">
+        <v>0</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4">
+        <v>0</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0</v>
+      </c>
+      <c r="T37" s="4">
+        <v>0</v>
+      </c>
+      <c r="U37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38">
+        <f t="shared" ref="B38:Q44" ca="1" si="13">RAND()</f>
+        <v>0.26679942536692691</v>
+      </c>
+      <c r="C38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.31112087465104943</v>
+      </c>
+      <c r="D38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.24565014697156895</v>
+      </c>
+      <c r="E38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.37673716819142467</v>
+      </c>
+      <c r="F38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.13724742986023186</v>
+      </c>
+      <c r="G38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.95793518970822689</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.68971196738140084</v>
+      </c>
+      <c r="I38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.98855278074487063</v>
+      </c>
+      <c r="J38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.41025688672679395</v>
+      </c>
+      <c r="K38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.55551219563208365</v>
+      </c>
+      <c r="L38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.84718484578251829</v>
+      </c>
+      <c r="M38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.74982472821819468</v>
+      </c>
+      <c r="N38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.75430661742919258</v>
+      </c>
+      <c r="O38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.805150246156215</v>
+      </c>
+      <c r="P38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.83333387605190279</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.30800057010565052</v>
+      </c>
+      <c r="R38">
+        <f t="shared" ref="R38:U44" ca="1" si="14">RAND()</f>
+        <v>0.1536674584031229</v>
+      </c>
+      <c r="S38">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.47282963702374059</v>
+      </c>
+      <c r="T38">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.15792337415848989</v>
+      </c>
+      <c r="U38">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.1609506786443341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.2523695863127362</v>
+      </c>
+      <c r="C39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.10318002838788276</v>
+      </c>
+      <c r="D39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.98761262522388105</v>
+      </c>
+      <c r="E39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.44860819495377657</v>
+      </c>
+      <c r="F39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.57635163155754454</v>
+      </c>
+      <c r="G39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.50119382505249466</v>
+      </c>
+      <c r="H39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.50296575408880662</v>
+      </c>
+      <c r="I39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.85405327557605193</v>
+      </c>
+      <c r="J39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.94761715342655095</v>
+      </c>
+      <c r="K39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.66168543049887185</v>
+      </c>
+      <c r="L39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.34048933196064735</v>
+      </c>
+      <c r="M39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.96155336346944564</v>
+      </c>
+      <c r="N39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.7758690545527982</v>
+      </c>
+      <c r="O39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.67694076377886103</v>
+      </c>
+      <c r="P39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.59099689876827166</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.39799188307921696</v>
+      </c>
+      <c r="R39">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.90176682810591546</v>
+      </c>
+      <c r="S39">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.37648774869764345</v>
+      </c>
+      <c r="T39">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.62707383727811505</v>
+      </c>
+      <c r="U39">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.28978446611100284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.49679124154815968</v>
+      </c>
+      <c r="C40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.58667709567303239</v>
+      </c>
+      <c r="D40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.99220057092384784</v>
+      </c>
+      <c r="E40">
+        <f t="shared" ca="1" si="13"/>
+        <v>3.3171239476036729E-2</v>
+      </c>
+      <c r="F40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.71525172920618507</v>
+      </c>
+      <c r="G40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.87971762590169489</v>
+      </c>
+      <c r="H40">
+        <f t="shared" ca="1" si="13"/>
+        <v>5.8082446275473765E-2</v>
+      </c>
+      <c r="I40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.50842901241909932</v>
+      </c>
+      <c r="J40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.68822435606082633</v>
+      </c>
+      <c r="K40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.80312478478885185</v>
+      </c>
+      <c r="L40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.27751397283304069</v>
+      </c>
+      <c r="M40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.13328360600066702</v>
+      </c>
+      <c r="N40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.45155419473246716</v>
+      </c>
+      <c r="O40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.46206036157560471</v>
+      </c>
+      <c r="P40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.42931822704603662</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.93936551827421977</v>
+      </c>
+      <c r="R40">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.66583615578444444</v>
+      </c>
+      <c r="S40">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.89893940511295212</v>
+      </c>
+      <c r="T40">
+        <f t="shared" ca="1" si="14"/>
+        <v>5.8670796596195784E-2</v>
+      </c>
+      <c r="U40">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.39153241797302818</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.34929796014151215</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.39498481137015351</v>
+      </c>
+      <c r="D41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.76940494212142518</v>
+      </c>
+      <c r="E41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.33486355111356347</v>
+      </c>
+      <c r="F41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.55350794820010152</v>
+      </c>
+      <c r="G41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.25371269339706204</v>
+      </c>
+      <c r="H41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.80358997611133498</v>
+      </c>
+      <c r="I41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.85752475893320246</v>
+      </c>
+      <c r="J41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.20791712351005032</v>
+      </c>
+      <c r="K41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.82530745708260622</v>
+      </c>
+      <c r="L41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.95118981945401282</v>
+      </c>
+      <c r="M41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.50046047813422845</v>
+      </c>
+      <c r="N41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.58006083919708284</v>
+      </c>
+      <c r="O41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.8268935795539748</v>
+      </c>
+      <c r="P41">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.91560236186893895</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" ca="1" si="13"/>
+        <v>3.6383542810021097E-2</v>
+      </c>
+      <c r="R41">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.9274753200136624</v>
+      </c>
+      <c r="S41">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.89601077555076858</v>
+      </c>
+      <c r="T41">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.83856103125758297</v>
+      </c>
+      <c r="U41">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.40408102203359908</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.622934815091161</v>
+      </c>
+      <c r="C42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.9572771644618191</v>
+      </c>
+      <c r="D42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.2513602446569112</v>
+      </c>
+      <c r="E42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.32427962130893151</v>
+      </c>
+      <c r="F42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.96844895224285976</v>
+      </c>
+      <c r="G42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.28295965450109528</v>
+      </c>
+      <c r="H42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.43378693975686444</v>
+      </c>
+      <c r="I42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.16542129287589458</v>
+      </c>
+      <c r="J42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.48202666825036267</v>
+      </c>
+      <c r="K42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.85860869072119295</v>
+      </c>
+      <c r="L42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.22299410061278702</v>
+      </c>
+      <c r="M42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.79459977711518115</v>
+      </c>
+      <c r="N42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.55719967577960539</v>
+      </c>
+      <c r="O42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.88576766870446211</v>
+      </c>
+      <c r="P42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.62487594830182214</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.23605814634334976</v>
+      </c>
+      <c r="R42">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.63427492263368779</v>
+      </c>
+      <c r="S42">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.62474285140185326</v>
+      </c>
+      <c r="T42">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.82179065477848356</v>
+      </c>
+      <c r="U42">
+        <f t="shared" ca="1" si="14"/>
+        <v>3.2944468612008726E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.9079524015753021</v>
+      </c>
+      <c r="C43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.351778264982616</v>
+      </c>
+      <c r="D43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.69212222588374295</v>
+      </c>
+      <c r="E43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.21494620275516607</v>
+      </c>
+      <c r="F43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.11112276493928874</v>
+      </c>
+      <c r="G43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.11541833033325322</v>
+      </c>
+      <c r="H43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.24132793348960979</v>
+      </c>
+      <c r="I43">
+        <f t="shared" ca="1" si="13"/>
+        <v>5.5463836993736582E-2</v>
+      </c>
+      <c r="J43">
+        <f t="shared" ca="1" si="13"/>
+        <v>3.9270799944444712E-2</v>
+      </c>
+      <c r="K43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.36525435747758861</v>
+      </c>
+      <c r="L43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.98698216178536768</v>
+      </c>
+      <c r="M43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.61233187269241185</v>
+      </c>
+      <c r="N43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.45938235374447633</v>
+      </c>
+      <c r="O43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.97955716221504863</v>
+      </c>
+      <c r="P43">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.86222181299559963</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" ca="1" si="13"/>
+        <v>8.5046450192737932E-2</v>
+      </c>
+      <c r="R43">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.38447322941256012</v>
+      </c>
+      <c r="S43">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.52386791548415734</v>
+      </c>
+      <c r="T43">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.1608754839813693</v>
+      </c>
+      <c r="U43">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.51168085630377913</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.79808094825767184</v>
+      </c>
+      <c r="C44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.16325158981660515</v>
+      </c>
+      <c r="D44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.27633808934508974</v>
+      </c>
+      <c r="E44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.57885540060009655</v>
+      </c>
+      <c r="F44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.23328206783492444</v>
+      </c>
+      <c r="G44">
+        <f t="shared" ca="1" si="13"/>
+        <v>1.7270907195652385E-2</v>
+      </c>
+      <c r="H44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.25406225119623571</v>
+      </c>
+      <c r="I44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.98484967897832199</v>
+      </c>
+      <c r="J44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.46716593029023323</v>
+      </c>
+      <c r="K44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.42428853904915487</v>
+      </c>
+      <c r="L44">
+        <f t="shared" ca="1" si="13"/>
+        <v>3.641620786339006E-3</v>
+      </c>
+      <c r="M44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.18947220096105999</v>
+      </c>
+      <c r="N44">
+        <f t="shared" ca="1" si="13"/>
+        <v>2.375329903846557E-2</v>
+      </c>
+      <c r="O44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.47859556926507718</v>
+      </c>
+      <c r="P44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.40158272045132348</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.76500266925456362</v>
+      </c>
+      <c r="R44">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.51557972022697385</v>
+      </c>
+      <c r="S44">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.12345726161432991</v>
+      </c>
+      <c r="T44">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.16458215901005457</v>
+      </c>
+      <c r="U44">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.96497478368177803</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="4">
+        <v>0</v>
+      </c>
+      <c r="C45" s="4">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4">
+        <v>0</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0</v>
+      </c>
+      <c r="N45" s="4">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4">
+        <v>0</v>
+      </c>
+      <c r="P45" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4">
+        <v>0</v>
+      </c>
+      <c r="T45" s="4">
+        <v>0</v>
+      </c>
+      <c r="U45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="4">
+        <v>0</v>
+      </c>
+      <c r="C46" s="4">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4">
+        <v>0</v>
+      </c>
+      <c r="M46" s="4">
+        <v>0</v>
+      </c>
+      <c r="N46" s="4">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4">
+        <v>0</v>
+      </c>
+      <c r="P46" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4">
+        <v>0</v>
+      </c>
+      <c r="S46" s="4">
+        <v>0</v>
+      </c>
+      <c r="T46" s="4">
+        <v>0</v>
+      </c>
+      <c r="U46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47">
+        <f t="shared" ref="B47:Q51" ca="1" si="15">RAND()</f>
+        <v>6.7765916272566229E-2</v>
+      </c>
+      <c r="C47">
+        <f t="shared" ca="1" si="15"/>
+        <v>7.8683206913990777E-2</v>
+      </c>
+      <c r="D47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.33204122904657363</v>
+      </c>
+      <c r="E47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.91665269087378476</v>
+      </c>
+      <c r="F47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.74771176012747331</v>
+      </c>
+      <c r="G47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.6826329705711357</v>
+      </c>
+      <c r="H47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.16510529360690174</v>
+      </c>
+      <c r="I47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.63644151860991904</v>
+      </c>
+      <c r="J47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.65291219332593542</v>
+      </c>
+      <c r="K47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.89092495178483966</v>
+      </c>
+      <c r="L47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.38890032124280272</v>
+      </c>
+      <c r="M47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.46001174677204826</v>
+      </c>
+      <c r="N47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.10907162223484801</v>
+      </c>
+      <c r="O47">
+        <f t="shared" ca="1" si="15"/>
+        <v>4.9897612687668347E-2</v>
+      </c>
+      <c r="P47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.63053972504960631</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.77253662409136514</v>
+      </c>
+      <c r="R47">
+        <f t="shared" ref="R47:U51" ca="1" si="16">RAND()</f>
+        <v>0.95836631421064999</v>
+      </c>
+      <c r="S47">
+        <f t="shared" ca="1" si="16"/>
+        <v>4.1131826313015596E-2</v>
+      </c>
+      <c r="T47">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.62341330476019208</v>
+      </c>
+      <c r="U47">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.48242183146205952</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.44201850196230619</v>
+      </c>
+      <c r="C48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.11222622979281061</v>
+      </c>
+      <c r="D48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.22824943759719218</v>
+      </c>
+      <c r="E48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.91782106009600628</v>
+      </c>
+      <c r="F48">
+        <f t="shared" ca="1" si="15"/>
+        <v>8.9774856826118188E-2</v>
+      </c>
+      <c r="G48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.3463097178806156</v>
+      </c>
+      <c r="H48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.51182677824376144</v>
+      </c>
+      <c r="I48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.65387281057705149</v>
+      </c>
+      <c r="J48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.49454030593053189</v>
+      </c>
+      <c r="K48">
+        <f t="shared" ca="1" si="15"/>
+        <v>7.8298834645999627E-2</v>
+      </c>
+      <c r="L48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.26053488051109241</v>
+      </c>
+      <c r="M48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.12759184685681768</v>
+      </c>
+      <c r="N48">
+        <f t="shared" ca="1" si="15"/>
+        <v>4.0671159807036728E-2</v>
+      </c>
+      <c r="O48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.67455362569455157</v>
+      </c>
+      <c r="P48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.20663090735082157</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.92147928735602425</v>
+      </c>
+      <c r="R48">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.14126790376043297</v>
+      </c>
+      <c r="S48">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.78267731500557969</v>
+      </c>
+      <c r="T48">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.27769706369675917</v>
+      </c>
+      <c r="U48">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.73248637531159122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.14304878505491991</v>
+      </c>
+      <c r="C49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.26302265889258902</v>
+      </c>
+      <c r="D49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.29807811558755826</v>
+      </c>
+      <c r="E49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.35335050532531298</v>
+      </c>
+      <c r="F49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.19827369203000011</v>
+      </c>
+      <c r="G49">
+        <f t="shared" ca="1" si="15"/>
+        <v>4.6588525681797388E-2</v>
+      </c>
+      <c r="H49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.57464789544360995</v>
+      </c>
+      <c r="I49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.45192639460546546</v>
+      </c>
+      <c r="J49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.5404591940546144</v>
+      </c>
+      <c r="K49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.68790744237848589</v>
+      </c>
+      <c r="L49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.13038410907771525</v>
+      </c>
+      <c r="M49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.98493872885520539</v>
+      </c>
+      <c r="N49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.26403551750874688</v>
+      </c>
+      <c r="O49">
+        <f t="shared" ca="1" si="15"/>
+        <v>9.3510702261641931E-2</v>
+      </c>
+      <c r="P49">
+        <f t="shared" ca="1" si="15"/>
+        <v>6.1749785749609432E-2</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.54040314349599206</v>
+      </c>
+      <c r="R49">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.39614730741105397</v>
+      </c>
+      <c r="S49">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.90161690277327378</v>
+      </c>
+      <c r="T49">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.57513361821908637</v>
+      </c>
+      <c r="U49">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.168824441612625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.1146621436989409</v>
+      </c>
+      <c r="C50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.55001534938466456</v>
+      </c>
+      <c r="D50">
+        <f t="shared" ca="1" si="15"/>
+        <v>2.3136423202467782E-2</v>
+      </c>
+      <c r="E50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.94336117025919641</v>
+      </c>
+      <c r="F50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.95281489920284157</v>
+      </c>
+      <c r="G50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.84108391750179468</v>
+      </c>
+      <c r="H50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.41568614642178559</v>
+      </c>
+      <c r="I50">
+        <f t="shared" ca="1" si="15"/>
+        <v>7.5178547249413752E-3</v>
+      </c>
+      <c r="J50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.19656972183605981</v>
+      </c>
+      <c r="K50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.66748175025529877</v>
+      </c>
+      <c r="L50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.27827693107662876</v>
+      </c>
+      <c r="M50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.81722333803023184</v>
+      </c>
+      <c r="N50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.7149933611610958</v>
+      </c>
+      <c r="O50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.90714047524822117</v>
+      </c>
+      <c r="P50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.6775229682415812</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.26693236517595254</v>
+      </c>
+      <c r="R50">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.38031240115159981</v>
+      </c>
+      <c r="S50">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.24909809904355784</v>
+      </c>
+      <c r="T50">
+        <f t="shared" ca="1" si="16"/>
+        <v>9.56193530102315E-2</v>
+      </c>
+      <c r="U50">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.30945106324905824</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.35741480167658213</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ca="1" si="15"/>
+        <v>1.9036224580679328E-2</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.22419873414011027</v>
+      </c>
+      <c r="E51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.48553231140032216</v>
+      </c>
+      <c r="F51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.46961604796492284</v>
+      </c>
+      <c r="G51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.11523427327605629</v>
+      </c>
+      <c r="H51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.35291075674254624</v>
+      </c>
+      <c r="I51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.65266088113824805</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ca="1" si="15"/>
+        <v>8.5936979363917976E-2</v>
+      </c>
+      <c r="K51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.80359335736910475</v>
+      </c>
+      <c r="L51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.55358728290000803</v>
+      </c>
+      <c r="M51">
+        <f t="shared" ca="1" si="15"/>
+        <v>1.2239702437443212E-3</v>
+      </c>
+      <c r="N51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.29779659955661375</v>
+      </c>
+      <c r="O51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.8776412456781888</v>
+      </c>
+      <c r="P51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.82163221467805925</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.98053884439076777</v>
+      </c>
+      <c r="R51">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.64550818962162115</v>
+      </c>
+      <c r="S51">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.10808415852876641</v>
+      </c>
+      <c r="T51">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.86322220360281954</v>
+      </c>
+      <c r="U51">
+        <f t="shared" ca="1" si="16"/>
+        <v>0.90397349298902219</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="4">
+        <v>0</v>
+      </c>
+      <c r="C52" s="4">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4">
+        <v>0</v>
+      </c>
+      <c r="M52" s="4">
+        <v>0</v>
+      </c>
+      <c r="N52" s="4">
+        <v>0</v>
+      </c>
+      <c r="O52" s="4">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>0</v>
+      </c>
+      <c r="R52" s="4">
+        <v>0</v>
+      </c>
+      <c r="S52" s="4">
+        <v>0</v>
+      </c>
+      <c r="T52" s="4">
+        <v>0</v>
+      </c>
+      <c r="U52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="4">
+        <v>0</v>
+      </c>
+      <c r="C53" s="4">
+        <v>0</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4">
+        <v>0</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0</v>
+      </c>
+      <c r="N53" s="4">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>0</v>
+      </c>
+      <c r="R53" s="4">
+        <v>0</v>
+      </c>
+      <c r="S53" s="4">
+        <v>0</v>
+      </c>
+      <c r="T53" s="4">
+        <v>0</v>
+      </c>
+      <c r="U53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B13B19-C822-4A05-8626-3D1360020ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E0D9B-BB3F-49EA-BD09-384FD1A6FB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -310,7 +310,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -328,24 +328,17 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{2351E727-7914-4128-83BF-CE6273F2D9EE}"/>
     <cellStyle name="Percent 2" xfId="2" xr:uid="{8E3C7290-F3EB-4F4F-810B-1E8706B54683}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9958800012207406E-2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9958800012207406E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3369,7 +3362,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E398A87-82CA-4B50-B75F-313C6B1D2BBE}">
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:AB54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -3444,85 +3437,65 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <f ca="1">RAND()</f>
-        <v>0.32879153275548356</v>
-      </c>
-      <c r="C2">
-        <f t="shared" ref="C2:R3" ca="1" si="0">RAND()</f>
-        <v>0.75329708019983532</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.1900882851673584E-2</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.5561343813362567</v>
-      </c>
-      <c r="F2">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.5156789691012214E-2</v>
-      </c>
-      <c r="G2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.8057504005152456</v>
-      </c>
-      <c r="H2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.89500126908120936</v>
-      </c>
-      <c r="I2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.99169631016811666</v>
-      </c>
-      <c r="J2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.97791454914364528</v>
-      </c>
-      <c r="K2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.72527063721151097</v>
-      </c>
-      <c r="L2">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.3263343896113065E-2</v>
-      </c>
-      <c r="M2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.35624123280862974</v>
-      </c>
-      <c r="N2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.2883324211136914</v>
-      </c>
-      <c r="O2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.46798847437607005</v>
-      </c>
-      <c r="P2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.99718939412882324</v>
-      </c>
-      <c r="Q2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.11386781022712889</v>
-      </c>
-      <c r="R2">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.96008610376158932</v>
-      </c>
-      <c r="S2">
-        <f t="shared" ref="S2:U3" ca="1" si="1">RAND()</f>
-        <v>0.13331338367232315</v>
-      </c>
-      <c r="T2">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.48135203321645015</v>
-      </c>
-      <c r="U2">
-        <f t="shared" ca="1" si="1"/>
-        <v>5.1857418944855516E-2</v>
+      <c r="B2" s="8">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="C2" s="8">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="D2" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F2" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="G2" s="8">
+        <v>2.8E-3</v>
+      </c>
+      <c r="H2" s="8">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I2" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J2" s="8">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K2" s="8">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="L2" s="8">
+        <v>3.2499999999999999E-3</v>
+      </c>
+      <c r="M2" s="8">
+        <v>3.3E-3</v>
+      </c>
+      <c r="N2" s="8">
+        <v>3.3500000000000001E-3</v>
+      </c>
+      <c r="O2" s="8">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="P2" s="8">
+        <v>3.4499999999999999E-3</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="R2" s="8">
+        <v>3.5500000000000002E-3</v>
+      </c>
+      <c r="S2" s="8">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="T2" s="8">
+        <v>3.65E-3</v>
+      </c>
+      <c r="U2" s="8">
+        <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -3530,84 +3503,64 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <f ca="1">RAND()</f>
-        <v>0.81370766511264525</v>
+        <v>3.8E-3</v>
       </c>
       <c r="C3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.72667639676506335</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.91791747155625947</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.63886731249650153</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="F3">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.1382472643246007E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="G3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.11399323540280337</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="H3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.34037395865969178</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="I3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.5821963287956976</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="J3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.21568181537834574</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="K3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.18655112329081802</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="L3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.36796995168392022</v>
+        <v>4.8500000000000001E-3</v>
       </c>
       <c r="M3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.12161721263099567</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="N3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.3780544620275168</v>
+        <v>4.9500000000000004E-3</v>
       </c>
       <c r="O3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.2360732544573324</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.49096868533516302</v>
+        <v>5.0499999999999998E-3</v>
       </c>
       <c r="Q3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.12580437303107805</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="R3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.33499540482954648</v>
+        <v>5.1500000000000001E-3</v>
       </c>
       <c r="S3">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.34019605613945936</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="T3">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.31391710111168736</v>
+        <v>5.2500000000000003E-3</v>
       </c>
       <c r="U3">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.23856446983787505</v>
+        <v>5.3E-3</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -4004,170 +3957,130 @@
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <f t="shared" ref="B10:Q12" ca="1" si="2">RAND()</f>
-        <v>0.28609500297072543</v>
-      </c>
-      <c r="C10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.19901660806193511</v>
-      </c>
-      <c r="D10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.6581556714443989</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.81268342660872817</v>
-      </c>
-      <c r="F10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.46201883193962578</v>
-      </c>
-      <c r="G10">
-        <f t="shared" ca="1" si="2"/>
-        <v>3.1848856190636488E-2</v>
-      </c>
-      <c r="H10">
-        <f t="shared" ca="1" si="2"/>
-        <v>2.5473278331028082E-2</v>
-      </c>
-      <c r="I10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.54573043006149879</v>
-      </c>
-      <c r="J10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.87220071738587091</v>
-      </c>
-      <c r="K10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.14212163255109345</v>
-      </c>
-      <c r="L10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.11214109566507213</v>
-      </c>
-      <c r="M10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.14724270150243501</v>
-      </c>
-      <c r="N10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.40379769916163677</v>
-      </c>
-      <c r="O10">
-        <f t="shared" ca="1" si="2"/>
-        <v>2.7415107181676612E-2</v>
-      </c>
-      <c r="P10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.80284652653707622</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.15587525646002254</v>
-      </c>
-      <c r="R10">
-        <f t="shared" ref="R10:U12" ca="1" si="3">RAND()</f>
-        <v>0.27685248365824044</v>
-      </c>
-      <c r="S10">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.45331814262553383</v>
-      </c>
-      <c r="T10">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.70355483833213617</v>
-      </c>
-      <c r="U10">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.14894707603706447</v>
+      <c r="B10" s="8">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="D10" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="G10" s="8">
+        <v>2.8E-3</v>
+      </c>
+      <c r="H10" s="8">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I10" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J10" s="8">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K10" s="8">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="L10" s="8">
+        <v>3.2499999999999999E-3</v>
+      </c>
+      <c r="M10" s="8">
+        <v>3.3E-3</v>
+      </c>
+      <c r="N10" s="8">
+        <v>3.3500000000000001E-3</v>
+      </c>
+      <c r="O10" s="8">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="P10" s="8">
+        <v>3.4499999999999999E-3</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="R10" s="8">
+        <v>3.5500000000000002E-3</v>
+      </c>
+      <c r="S10" s="8">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="T10" s="8">
+        <v>3.65E-3</v>
+      </c>
+      <c r="U10" s="8">
+        <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.90743037639072321</v>
-      </c>
-      <c r="C11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.20574770964166222</v>
-      </c>
-      <c r="D11">
-        <f t="shared" ca="1" si="2"/>
-        <v>9.41107062964186E-2</v>
-      </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.99744152501241889</v>
-      </c>
-      <c r="F11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.28064048819033727</v>
-      </c>
-      <c r="G11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.14284376757063966</v>
-      </c>
-      <c r="H11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.98168448579099199</v>
-      </c>
-      <c r="I11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.5311564549363873</v>
-      </c>
-      <c r="J11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.80787625451015044</v>
-      </c>
-      <c r="K11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.65142579502085329</v>
-      </c>
-      <c r="L11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.49402380367600263</v>
-      </c>
-      <c r="M11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.37757229012610438</v>
-      </c>
-      <c r="N11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.55052715449365164</v>
-      </c>
-      <c r="O11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.33462903891059315</v>
-      </c>
-      <c r="P11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.15915411683399305</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.63819451715410946</v>
-      </c>
-      <c r="R11">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.7233719387003148</v>
-      </c>
-      <c r="S11">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.92659352795056915</v>
-      </c>
-      <c r="T11">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.99945635434475089</v>
-      </c>
-      <c r="U11">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.71338484827790904</v>
+      <c r="B11" s="8">
+        <v>1.20625E-2</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.2437500000000001E-2</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.257638888888889E-2</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.271527777777778E-2</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1.285416666666667E-2</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1.30125E-2</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1.317083333333333E-2</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1.332916666666667E-2</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1.3487499999999999E-2</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1.3645833333333329E-2</v>
+      </c>
+      <c r="L11" s="8">
+        <v>1.3724999999999999E-2</v>
+      </c>
+      <c r="M11" s="8">
+        <v>1.3804166666666669E-2</v>
+      </c>
+      <c r="N11" s="8">
+        <v>1.3883333333333331E-2</v>
+      </c>
+      <c r="O11" s="8">
+        <v>1.3962499999999999E-2</v>
+      </c>
+      <c r="P11" s="8">
+        <v>1.4041666666666669E-2</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>1.4120833333333331E-2</v>
+      </c>
+      <c r="R11" s="8">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="S11" s="8">
+        <v>1.4279166666666669E-2</v>
+      </c>
+      <c r="T11" s="8">
+        <v>1.4358333333333331E-2</v>
+      </c>
+      <c r="U11" s="8">
+        <v>1.4437500000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
@@ -4175,84 +4088,64 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.37006668095109985</v>
+        <v>1E-4</v>
       </c>
       <c r="C12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.79716740534033093</v>
-      </c>
-      <c r="D12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.9751008956793995</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.21667400190137687</v>
-      </c>
-      <c r="F12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.81356617706448275</v>
-      </c>
-      <c r="G12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.70700524294876177</v>
-      </c>
-      <c r="H12">
-        <f t="shared" ca="1" si="2"/>
-        <v>5.6252375527537368E-2</v>
-      </c>
-      <c r="I12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.11559376073194094</v>
-      </c>
-      <c r="J12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.47974866185919873</v>
-      </c>
-      <c r="K12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.68442313704009405</v>
-      </c>
-      <c r="L12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.38658597455614929</v>
-      </c>
-      <c r="M12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.12435175477281857</v>
-      </c>
-      <c r="N12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.55063765349971527</v>
-      </c>
-      <c r="O12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.91083068253644817</v>
-      </c>
-      <c r="P12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.73809565011987632</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.83927346103975875</v>
-      </c>
-      <c r="R12">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.99867259409797349</v>
-      </c>
-      <c r="S12">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.66610466188117845</v>
-      </c>
-      <c r="T12">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.24754690443470928</v>
-      </c>
-      <c r="U12">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.76494809582672518</v>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="D12" s="8">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="E12" s="8">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F12" s="8">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G12" s="8">
+        <v>6.0000000000000006E-4</v>
+      </c>
+      <c r="H12" s="8">
+        <v>7.000000000000001E-4</v>
+      </c>
+      <c r="I12" s="8">
+        <v>8.0000000000000015E-4</v>
+      </c>
+      <c r="J12" s="8">
+        <v>9.0000000000000019E-4</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1.0000000000000002E-3</v>
+      </c>
+      <c r="L12" s="8">
+        <v>1.1000000000000003E-3</v>
+      </c>
+      <c r="M12" s="8">
+        <v>1.2000000000000003E-3</v>
+      </c>
+      <c r="N12" s="8">
+        <v>1.3000000000000004E-3</v>
+      </c>
+      <c r="O12" s="8">
+        <v>1.4000000000000004E-3</v>
+      </c>
+      <c r="P12" s="8">
+        <v>1.5000000000000005E-3</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>1.6000000000000005E-3</v>
+      </c>
+      <c r="R12" s="8">
+        <v>1.7000000000000006E-3</v>
+      </c>
+      <c r="S12" s="8">
+        <v>1.8000000000000006E-3</v>
+      </c>
+      <c r="T12" s="8">
+        <v>1.9000000000000006E-3</v>
+      </c>
+      <c r="U12" s="8">
+        <v>2.0000000000000005E-3</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -4455,84 +4348,64 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <f t="shared" ref="B16:Q17" ca="1" si="4">RAND()</f>
-        <v>0.95534972573863486</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="C16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.23485379432362419</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="D16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.84728786303754444</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.24321198532369359</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="F16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.63006314130900631</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.33350457822470003</v>
+        <v>3.3E-3</v>
       </c>
       <c r="H16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.16691724858741541</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="I16">
-        <f t="shared" ca="1" si="4"/>
-        <v>7.6089777928422864E-2</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="J16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.16623449889883746</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="K16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.92462164955751414</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="L16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.36691439299406137</v>
+        <v>3.7499999999999999E-3</v>
       </c>
       <c r="M16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.2504461784666786</v>
+        <v>3.8E-3</v>
       </c>
       <c r="N16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.21619525436290832</v>
+        <v>3.8500000000000001E-3</v>
       </c>
       <c r="O16">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.59402016706608063</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="P16">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.0641000245942851E-2</v>
+        <v>3.9500000000000004E-3</v>
       </c>
       <c r="Q16">
-        <f t="shared" ca="1" si="4"/>
-        <v>4.3878823057493355E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="R16">
-        <f t="shared" ref="R16:U17" ca="1" si="5">RAND()</f>
-        <v>0.4293019588990965</v>
+        <v>4.0499999999999998E-3</v>
       </c>
       <c r="S16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.39789977271852361</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="T16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.26191266268874547</v>
+        <v>4.15E-3</v>
       </c>
       <c r="U16">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.53661846874155383</v>
+        <v>4.1999999999999997E-3</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
@@ -4540,84 +4413,64 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.82937223374804547</v>
+        <v>1.14E-2</v>
       </c>
       <c r="C17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.97268840248893473</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="D17">
-        <f t="shared" ca="1" si="4"/>
-        <v>5.1421126556198349E-2</v>
+        <v>1.17E-2</v>
       </c>
       <c r="E17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.58081945667721713</v>
+        <v>1.18E-2</v>
       </c>
       <c r="F17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.83667692845124464</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="G17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.24482802003561155</v>
+        <v>1.2E-2</v>
       </c>
       <c r="H17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.31548771507875961</v>
+        <v>1.21E-2</v>
       </c>
       <c r="I17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.17734510689275873</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="J17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.53126211980220506</v>
+        <v>1.23E-2</v>
       </c>
       <c r="K17">
-        <f t="shared" ca="1" si="4"/>
-        <v>4.8545390185432691E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="L17">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.2201525619716436E-2</v>
+        <v>1.2449999999999999E-2</v>
       </c>
       <c r="M17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.63129449866576082</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="N17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.2028270507463461</v>
+        <v>1.255E-2</v>
       </c>
       <c r="O17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.28585956529037393</v>
+        <v>1.26E-2</v>
       </c>
       <c r="P17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.25838801163224712</v>
+        <v>1.265E-2</v>
       </c>
       <c r="Q17">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.34673099599185009</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="R17">
-        <f t="shared" ca="1" si="5"/>
-        <v>8.8205666480333345E-2</v>
+        <v>1.2749999999999999E-2</v>
       </c>
       <c r="S17">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.78341955440427147</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="T17">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.90934797600586259</v>
+        <v>1.285E-2</v>
       </c>
       <c r="U17">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.69994918789379978</v>
+        <v>1.29E-2</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
@@ -4950,84 +4803,64 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <f t="shared" ref="B23:U23" ca="1" si="6">RAND()</f>
-        <v>0.35885620650313865</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="C23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.17140996871985015</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="D23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.79979857821667899</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="E23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.45080413722546753</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="F23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.28009459146845528</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.70738348751093039</v>
+        <v>2.8E-3</v>
       </c>
       <c r="H23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.40846745432301867</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="I23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.23370295854440104</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="J23">
-        <f t="shared" ca="1" si="6"/>
-        <v>6.1671551435345084E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="K23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.23762893064163748</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="L23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.64323777939948223</v>
+        <v>3.2499999999999999E-3</v>
       </c>
       <c r="M23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.2229812006428803</v>
+        <v>3.3E-3</v>
       </c>
       <c r="N23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.93698742344403418</v>
+        <v>3.3500000000000001E-3</v>
       </c>
       <c r="O23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.88635402981358402</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="P23">
-        <f t="shared" ca="1" si="6"/>
-        <v>3.8859684963647667E-2</v>
+        <v>3.4499999999999999E-3</v>
       </c>
       <c r="Q23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.70250973248518389</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="R23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.50839085522241434</v>
+        <v>3.5500000000000002E-3</v>
       </c>
       <c r="S23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.92569618413002097</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="T23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.20423082076717403</v>
+        <v>3.65E-3</v>
       </c>
       <c r="U23">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.68679146529953694</v>
+        <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
@@ -5099,85 +4932,65 @@
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
-        <f t="shared" ref="B25:Q26" ca="1" si="7">RAND()</f>
-        <v>6.9596003511846694E-2</v>
-      </c>
-      <c r="C25">
-        <f t="shared" ca="1" si="7"/>
-        <v>4.685267232306678E-2</v>
-      </c>
-      <c r="D25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.34100079253814419</v>
-      </c>
-      <c r="E25">
-        <f t="shared" ca="1" si="7"/>
-        <v>1.3263426762092023E-2</v>
-      </c>
-      <c r="F25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.86461897616754946</v>
-      </c>
-      <c r="G25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.85777521481674168</v>
-      </c>
-      <c r="H25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.98181061811941095</v>
-      </c>
-      <c r="I25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.94106864811833668</v>
-      </c>
-      <c r="J25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.50529669625722451</v>
-      </c>
-      <c r="K25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.54211918581221841</v>
-      </c>
-      <c r="L25">
-        <f t="shared" ca="1" si="7"/>
-        <v>1.456147084501036E-2</v>
-      </c>
-      <c r="M25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.41901791669933419</v>
-      </c>
-      <c r="N25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.14958119485079668</v>
-      </c>
-      <c r="O25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.15998919757108654</v>
-      </c>
-      <c r="P25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.97313672829891562</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.76506546357494587</v>
-      </c>
-      <c r="R25">
-        <f t="shared" ref="R25:U26" ca="1" si="8">RAND()</f>
-        <v>0.59396988012778495</v>
-      </c>
-      <c r="S25">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.39422154094035644</v>
-      </c>
-      <c r="T25">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.90266512462109505</v>
-      </c>
-      <c r="U25">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.2933675523585132</v>
+      <c r="B25" s="8">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="D25" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F25" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="G25" s="8">
+        <v>2.8E-3</v>
+      </c>
+      <c r="H25" s="8">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I25" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J25" s="8">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K25" s="8">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="L25" s="8">
+        <v>3.2499999999999999E-3</v>
+      </c>
+      <c r="M25" s="8">
+        <v>3.3E-3</v>
+      </c>
+      <c r="N25" s="8">
+        <v>3.3500000000000001E-3</v>
+      </c>
+      <c r="O25" s="8">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="P25" s="8">
+        <v>3.4499999999999999E-3</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="R25" s="8">
+        <v>3.5500000000000002E-3</v>
+      </c>
+      <c r="S25" s="8">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="T25" s="8">
+        <v>3.65E-3</v>
+      </c>
+      <c r="U25" s="8">
+        <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
@@ -5185,84 +4998,64 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.54383009819791583</v>
+        <v>4.3E-3</v>
       </c>
       <c r="C26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.76735047814612856</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="D26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.38575361382064821</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="E26">
-        <f t="shared" ca="1" si="7"/>
-        <v>4.1354739565843235E-2</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="F26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.94107659743992844</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="G26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.18952877832710358</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="H26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.58154519283944051</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.39973671646996933</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="J26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.34883583710826815</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="K26">
-        <f t="shared" ca="1" si="7"/>
-        <v>7.1760913862593423E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="L26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.84991410937227296</v>
+        <v>5.3499999999999997E-3</v>
       </c>
       <c r="M26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.33197163905428217</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="N26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.92415384154134284</v>
+        <v>5.45E-3</v>
       </c>
       <c r="O26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.97908013475248312</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="P26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.6582481913963828</v>
+        <v>5.5500000000000002E-3</v>
       </c>
       <c r="Q26">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.35771602059493302</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="R26">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.2028703004594119</v>
+        <v>5.6499999999999996E-3</v>
       </c>
       <c r="S26">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.10831814614954061</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="T26">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.44242745739253952</v>
+        <v>5.7499999999999999E-3</v>
       </c>
       <c r="U26">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.25850868240146729</v>
+        <v>5.7999999999999996E-3</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
@@ -5334,170 +5127,130 @@
       <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B28">
-        <f t="shared" ref="B28:Q30" ca="1" si="9">RAND()</f>
-        <v>0.95667947026854661</v>
-      </c>
-      <c r="C28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.19375468102596272</v>
-      </c>
-      <c r="D28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.89214565312181759</v>
-      </c>
-      <c r="E28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.85401145105068399</v>
-      </c>
-      <c r="F28">
-        <f t="shared" ca="1" si="9"/>
-        <v>2.2549564321348248E-2</v>
-      </c>
-      <c r="G28">
-        <f t="shared" ca="1" si="9"/>
-        <v>9.2128023342778143E-2</v>
-      </c>
-      <c r="H28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.50952461353588185</v>
-      </c>
-      <c r="I28">
-        <f t="shared" ca="1" si="9"/>
-        <v>3.8064074340413034E-2</v>
-      </c>
-      <c r="J28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.56128826541091503</v>
-      </c>
-      <c r="K28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.86035471067916003</v>
-      </c>
-      <c r="L28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.29394907435368389</v>
-      </c>
-      <c r="M28">
-        <f t="shared" ca="1" si="9"/>
-        <v>9.901745767207204E-2</v>
-      </c>
-      <c r="N28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.93498291231659236</v>
-      </c>
-      <c r="O28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.43854435212754395</v>
-      </c>
-      <c r="P28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.24087604657069961</v>
-      </c>
-      <c r="Q28">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.70770046217672056</v>
-      </c>
-      <c r="R28">
-        <f t="shared" ref="R28:U30" ca="1" si="10">RAND()</f>
-        <v>0.50292779738814197</v>
-      </c>
-      <c r="S28">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.40028064815595499</v>
-      </c>
-      <c r="T28">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.40241224920296703</v>
-      </c>
-      <c r="U28">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.30119091383404994</v>
+      <c r="B28" s="8">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="D28" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F28" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="G28" s="8">
+        <v>2.8E-3</v>
+      </c>
+      <c r="H28" s="8">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I28" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J28" s="8">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K28" s="8">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="L28" s="8">
+        <v>3.2499999999999999E-3</v>
+      </c>
+      <c r="M28" s="8">
+        <v>3.3E-3</v>
+      </c>
+      <c r="N28" s="8">
+        <v>3.3500000000000001E-3</v>
+      </c>
+      <c r="O28" s="8">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="P28" s="8">
+        <v>3.4499999999999999E-3</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="R28" s="8">
+        <v>3.5500000000000002E-3</v>
+      </c>
+      <c r="S28" s="8">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="T28" s="8">
+        <v>3.65E-3</v>
+      </c>
+      <c r="U28" s="8">
+        <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.74374214595681942</v>
-      </c>
-      <c r="C29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.75938590469171752</v>
-      </c>
-      <c r="D29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.93011609701697184</v>
-      </c>
-      <c r="E29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.57712769404625541</v>
-      </c>
-      <c r="F29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.70729979614367455</v>
-      </c>
-      <c r="G29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.94648696384037168</v>
-      </c>
-      <c r="H29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.25588497490452788</v>
-      </c>
-      <c r="I29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.80936653395773595</v>
-      </c>
-      <c r="J29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.40609963021549866</v>
-      </c>
-      <c r="K29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.61234768751097113</v>
-      </c>
-      <c r="L29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.16013121903369898</v>
-      </c>
-      <c r="M29">
-        <f t="shared" ca="1" si="9"/>
-        <v>7.3046434896776424E-2</v>
-      </c>
-      <c r="N29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.30160494982441832</v>
-      </c>
-      <c r="O29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.82040685606814112</v>
-      </c>
-      <c r="P29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.56721943303947464</v>
-      </c>
-      <c r="Q29">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.4628542506292832</v>
-      </c>
-      <c r="R29">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.50934203131306777</v>
-      </c>
-      <c r="S29">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.55580351844379328</v>
-      </c>
-      <c r="T29">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.63727720797744858</v>
-      </c>
-      <c r="U29">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.98301536133943557</v>
+      <c r="B29" s="8">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="D29" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="G29" s="8">
+        <v>2.8E-3</v>
+      </c>
+      <c r="H29" s="8">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I29" s="8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J29" s="8">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K29" s="8">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="L29" s="8">
+        <v>3.2499999999999999E-3</v>
+      </c>
+      <c r="M29" s="8">
+        <v>3.3E-3</v>
+      </c>
+      <c r="N29" s="8">
+        <v>3.3500000000000001E-3</v>
+      </c>
+      <c r="O29" s="8">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="P29" s="8">
+        <v>3.4499999999999999E-3</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="R29" s="8">
+        <v>3.5500000000000002E-3</v>
+      </c>
+      <c r="S29" s="8">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="T29" s="8">
+        <v>3.65E-3</v>
+      </c>
+      <c r="U29" s="8">
+        <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
@@ -5505,84 +5258,64 @@
         <v>32</v>
       </c>
       <c r="B30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.36148837382099863</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="C30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.51505299655315262</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="D30">
-        <f t="shared" ca="1" si="9"/>
-        <v>4.429766998240614E-2</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="E30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.68246213387612298</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="F30">
-        <f t="shared" ca="1" si="9"/>
-        <v>8.4300259559227597E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="G30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.8510177614821306</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="H30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.70786205880811481</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="I30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.10045427695553721</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="J30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.3484268077353353</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="K30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.79747706995973167</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="L30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.56341775754542944</v>
+        <v>7.5500000000000003E-3</v>
       </c>
       <c r="M30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.97542467492953178</v>
+        <v>7.6E-3</v>
       </c>
       <c r="N30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.3819625859787652</v>
+        <v>7.6499999999999997E-3</v>
       </c>
       <c r="O30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.11808170606109303</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="P30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.50859808957797037</v>
+        <v>7.7499999999999999E-3</v>
       </c>
       <c r="Q30">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.21988592180736355</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="R30">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.61352841899286936</v>
+        <v>7.8499999999999993E-3</v>
       </c>
       <c r="S30">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.86814654592186657</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="T30">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.10755148378222612</v>
+        <v>7.9500000000000005E-3</v>
       </c>
       <c r="U30">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.69886661853005705</v>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
@@ -5715,347 +5448,267 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B33">
-        <f t="shared" ref="B33:Q36" ca="1" si="11">RAND()</f>
-        <v>0.2634511635444966</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="C33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.4463431608790589</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="D33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.70657141913060417</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="E33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.24433142676032149</v>
+        <v>2.18E-2</v>
       </c>
       <c r="F33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.43080012376299925</v>
+        <v>2.1899999999999999E-2</v>
       </c>
       <c r="G33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.71352361632608918</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.34005440264391651</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="I33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.64216999517685902</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="J33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.8702032287094642</v>
+        <v>2.23E-2</v>
       </c>
       <c r="K33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.33246818839868042</v>
+        <v>2.24E-2</v>
       </c>
       <c r="L33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.64536701163164323</v>
+        <v>2.2450000000000001E-2</v>
       </c>
       <c r="M33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.65058925503219722</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="N33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.39520471785370215</v>
+        <v>2.2550000000000001E-2</v>
       </c>
       <c r="O33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.88238127239727049</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="P33">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.13463568534008441</v>
+        <v>2.265E-2</v>
       </c>
       <c r="Q33">
-        <f t="shared" ca="1" si="11"/>
-        <v>3.0403962907946225E-2</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="R33">
-        <f t="shared" ref="R33:U36" ca="1" si="12">RAND()</f>
-        <v>0.65220534625959348</v>
+        <v>2.2749999999999999E-2</v>
       </c>
       <c r="S33">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.98335713268441283</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="T33">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.26541324930745136</v>
+        <v>2.2849999999999999E-2</v>
       </c>
       <c r="U33">
-        <f t="shared" ca="1" si="12"/>
-        <v>6.4855035469933098E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+        <v>2.29E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.65861206988009846</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="C34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.6120927366333232</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="D34">
-        <f t="shared" ca="1" si="11"/>
-        <v>4.3503797082272921E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="E34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.45424005200862849</v>
+        <v>0.02</v>
       </c>
       <c r="F34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.51512152829123181</v>
+        <v>2.01E-2</v>
       </c>
       <c r="G34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.25998102799536293</v>
+        <v>2.0199999999999999E-2</v>
       </c>
       <c r="H34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.2814042808224605</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="I34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.31204611425582152</v>
+        <v>2.0400000000000001E-2</v>
       </c>
       <c r="J34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.52475395022722771</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="K34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.64312989459403247</v>
+        <v>2.06E-2</v>
       </c>
       <c r="L34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.69134569109698074</v>
+        <v>2.0650000000000002E-2</v>
       </c>
       <c r="M34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.71510220992878526</v>
+        <v>2.07E-2</v>
       </c>
       <c r="N34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.5039163844293979</v>
+        <v>2.0750000000000001E-2</v>
       </c>
       <c r="O34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.83447538751899919</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="P34">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.81279637634634183</v>
+        <v>2.085E-2</v>
       </c>
       <c r="Q34">
-        <f t="shared" ca="1" si="11"/>
-        <v>3.7267947777835153E-2</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="R34">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.23215656683986641</v>
+        <v>2.095E-2</v>
       </c>
       <c r="S34">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.21136315709749154</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="T34">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.41054547023373722</v>
+        <v>2.1049999999999999E-2</v>
       </c>
       <c r="U34">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.32131552829721832</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+        <v>2.1100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.16952758299547455</v>
-      </c>
-      <c r="C35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.89388600643893024</v>
-      </c>
-      <c r="D35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.91217695500656182</v>
-      </c>
-      <c r="E35">
-        <f t="shared" ca="1" si="11"/>
-        <v>7.5736230114858305E-2</v>
-      </c>
-      <c r="F35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.33775992264538013</v>
-      </c>
-      <c r="G35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.84231309579038649</v>
-      </c>
-      <c r="H35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.18433247814230891</v>
-      </c>
-      <c r="I35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.51793959810063128</v>
-      </c>
-      <c r="J35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.84455510333793782</v>
-      </c>
-      <c r="K35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.3492378383107948</v>
-      </c>
-      <c r="L35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.42609446193086431</v>
-      </c>
-      <c r="M35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.12823615588780668</v>
-      </c>
-      <c r="N35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.51682758308182353</v>
-      </c>
-      <c r="O35">
-        <f t="shared" ca="1" si="11"/>
-        <v>3.0802476165482373E-3</v>
-      </c>
-      <c r="P35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.72217937124338205</v>
-      </c>
-      <c r="Q35">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.16458460566310207</v>
-      </c>
-      <c r="R35">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.47699913200226185</v>
-      </c>
-      <c r="S35">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.75615239683645741</v>
-      </c>
-      <c r="T35">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.83390251894015988</v>
-      </c>
-      <c r="U35">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.76859695945976114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B35" s="8">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2.12E-2</v>
+      </c>
+      <c r="D35" s="8">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="E35" s="8">
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="F35" s="8">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="G35" s="8">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="H35" s="8">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="I35" s="8">
+        <v>2.18E-2</v>
+      </c>
+      <c r="J35" s="8">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="K35" s="8">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="L35" s="8">
+        <v>2.205E-2</v>
+      </c>
+      <c r="M35" s="8">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="N35" s="8">
+        <v>2.215E-2</v>
+      </c>
+      <c r="O35" s="8">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="P35" s="8">
+        <v>2.2249999999999999E-2</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>2.23E-2</v>
+      </c>
+      <c r="R35" s="8">
+        <v>2.2349999999999998E-2</v>
+      </c>
+      <c r="S35" s="8">
+        <v>2.24E-2</v>
+      </c>
+      <c r="T35" s="8">
+        <v>2.2450000000000001E-2</v>
+      </c>
+      <c r="U35" s="8">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.94985306809239678</v>
-      </c>
-      <c r="C36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.30972377122713579</v>
-      </c>
-      <c r="D36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.54183490229249254</v>
-      </c>
-      <c r="E36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.71472035209710028</v>
-      </c>
-      <c r="F36">
-        <f t="shared" ca="1" si="11"/>
-        <v>9.5305584647929709E-2</v>
-      </c>
-      <c r="G36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.82667617956994532</v>
-      </c>
-      <c r="H36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.74796105154779358</v>
-      </c>
-      <c r="I36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.57852649591102978</v>
-      </c>
-      <c r="J36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.74218905026510495</v>
-      </c>
-      <c r="K36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.12021201655803782</v>
-      </c>
-      <c r="L36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.86082952374411537</v>
-      </c>
-      <c r="M36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.87524418251320235</v>
-      </c>
-      <c r="N36">
-        <f t="shared" ca="1" si="11"/>
-        <v>6.9070581112578466E-2</v>
-      </c>
-      <c r="O36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.60717577720977822</v>
-      </c>
-      <c r="P36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.69012769632312176</v>
-      </c>
-      <c r="Q36">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.29262923959210463</v>
-      </c>
-      <c r="R36">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.93956076709133196</v>
-      </c>
-      <c r="S36">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.10927441410059446</v>
-      </c>
-      <c r="T36">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.67806700068193104</v>
-      </c>
-      <c r="U36">
-        <f t="shared" ca="1" si="12"/>
-        <v>4.8665905693893174E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B36" s="8">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="C36" s="8">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="D36" s="8">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="E36" s="8">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="F36" s="8">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G36" s="8">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="H36" s="8">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="I36" s="8">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="J36" s="8">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="K36" s="8">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="L36" s="8">
+        <v>7.5500000000000003E-3</v>
+      </c>
+      <c r="M36" s="8">
+        <v>7.6E-3</v>
+      </c>
+      <c r="N36" s="8">
+        <v>7.6499999999999997E-3</v>
+      </c>
+      <c r="O36" s="8">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="P36" s="8">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="R36" s="8">
+        <v>7.8499999999999993E-3</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="T36" s="8">
+        <v>7.9500000000000005E-3</v>
+      </c>
+      <c r="U36" s="8">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
@@ -6120,1285 +5773,1122 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B38">
-        <f t="shared" ref="B38:Q44" ca="1" si="13">RAND()</f>
-        <v>0.26679942536692691</v>
+        <v>-1.34E-2</v>
       </c>
       <c r="C38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.31112087465104943</v>
+        <v>-1.32E-2</v>
       </c>
       <c r="D38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.24565014697156895</v>
+        <v>-1.3100000000000001E-2</v>
       </c>
       <c r="E38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.37673716819142467</v>
+        <v>-1.2999999999999999E-2</v>
       </c>
       <c r="F38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.13724742986023186</v>
+        <v>-1.29E-2</v>
       </c>
       <c r="G38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.95793518970822689</v>
+        <v>-1.2800000000000001E-2</v>
       </c>
       <c r="H38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.68971196738140084</v>
+        <v>-1.2699999999999999E-2</v>
       </c>
       <c r="I38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.98855278074487063</v>
+        <v>-1.26E-2</v>
       </c>
       <c r="J38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.41025688672679395</v>
+        <v>-1.2500000000000001E-2</v>
       </c>
       <c r="K38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.55551219563208365</v>
+        <v>-1.24E-2</v>
       </c>
       <c r="L38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.84718484578251829</v>
+        <v>-1.235E-2</v>
       </c>
       <c r="M38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.74982472821819468</v>
+        <v>-1.23E-2</v>
       </c>
       <c r="N38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.75430661742919258</v>
+        <v>-1.225E-2</v>
       </c>
       <c r="O38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.805150246156215</v>
+        <v>-1.2200000000000001E-2</v>
       </c>
       <c r="P38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.83333387605190279</v>
+        <v>-1.2149999999999999E-2</v>
       </c>
       <c r="Q38">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.30800057010565052</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="R38">
-        <f t="shared" ref="R38:U44" ca="1" si="14">RAND()</f>
-        <v>0.1536674584031229</v>
+        <v>-1.205E-2</v>
       </c>
       <c r="S38">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.47282963702374059</v>
+        <v>-1.2E-2</v>
       </c>
       <c r="T38">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.15792337415848989</v>
+        <v>-1.1950000000000001E-2</v>
       </c>
       <c r="U38">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.1609506786443341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+        <v>-1.1900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.2523695863127362</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="C39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.10318002838788276</v>
+        <v>2.12E-2</v>
       </c>
       <c r="D39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.98761262522388105</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="E39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.44860819495377657</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="F39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.57635163155754454</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="G39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.50119382505249466</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="H39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.50296575408880662</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="I39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.85405327557605193</v>
+        <v>2.18E-2</v>
       </c>
       <c r="J39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.94761715342655095</v>
+        <v>2.1899999999999999E-2</v>
       </c>
       <c r="K39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.66168543049887185</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="L39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.34048933196064735</v>
+        <v>2.205E-2</v>
       </c>
       <c r="M39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.96155336346944564</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="N39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.7758690545527982</v>
+        <v>2.215E-2</v>
       </c>
       <c r="O39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.67694076377886103</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="P39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.59099689876827166</v>
+        <v>2.2249999999999999E-2</v>
       </c>
       <c r="Q39">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.39799188307921696</v>
+        <v>2.23E-2</v>
       </c>
       <c r="R39">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.90176682810591546</v>
+        <v>2.2349999999999998E-2</v>
       </c>
       <c r="S39">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.37648774869764345</v>
+        <v>2.24E-2</v>
       </c>
       <c r="T39">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.62707383727811505</v>
+        <v>2.2450000000000001E-2</v>
       </c>
       <c r="U39">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.28978446611100284</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.49679124154815968</v>
+        <v>0.01</v>
       </c>
       <c r="C40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.58667709567303239</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="D40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.99220057092384784</v>
+        <v>1.066666666666667E-2</v>
       </c>
       <c r="E40">
-        <f t="shared" ca="1" si="13"/>
-        <v>3.3171239476036729E-2</v>
+        <v>1.083333333333333E-2</v>
       </c>
       <c r="F40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.71525172920618507</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="G40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.87971762590169489</v>
+        <v>1.12E-2</v>
       </c>
       <c r="H40">
-        <f t="shared" ca="1" si="13"/>
-        <v>5.8082446275473765E-2</v>
+        <v>1.14E-2</v>
       </c>
       <c r="I40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.50842901241909932</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="J40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.68822435606082633</v>
+        <v>1.18E-2</v>
       </c>
       <c r="K40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.80312478478885185</v>
+        <v>1.2E-2</v>
       </c>
       <c r="L40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.27751397283304069</v>
+        <v>1.21E-2</v>
       </c>
       <c r="M40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.13328360600066702</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="N40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.45155419473246716</v>
+        <v>1.23E-2</v>
       </c>
       <c r="O40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.46206036157560471</v>
+        <v>1.24E-2</v>
       </c>
       <c r="P40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.42931822704603662</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="Q40">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.93936551827421977</v>
+        <v>1.26E-2</v>
       </c>
       <c r="R40">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.66583615578444444</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="S40">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.89893940511295212</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="T40">
-        <f t="shared" ca="1" si="14"/>
-        <v>5.8670796596195784E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="U40">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.39153241797302818</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.34929796014151215</v>
+        <v>1.2E-2</v>
       </c>
       <c r="C41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.39498481137015351</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="D41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.76940494212142518</v>
+        <v>1.266666666666667E-2</v>
       </c>
       <c r="E41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.33486355111356347</v>
+        <v>1.2833333333333329E-2</v>
       </c>
       <c r="F41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.55350794820010152</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.25371269339706204</v>
+        <v>1.32E-2</v>
       </c>
       <c r="H41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.80358997611133498</v>
+        <v>1.34E-2</v>
       </c>
       <c r="I41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.85752475893320246</v>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="J41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.20791712351005032</v>
+        <v>1.38E-2</v>
       </c>
       <c r="K41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.82530745708260622</v>
+        <v>1.4E-2</v>
       </c>
       <c r="L41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.95118981945401282</v>
+        <v>1.41E-2</v>
       </c>
       <c r="M41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.50046047813422845</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="N41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.58006083919708284</v>
+        <v>1.43E-2</v>
       </c>
       <c r="O41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.8268935795539748</v>
+        <v>1.44E-2</v>
       </c>
       <c r="P41">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.91560236186893895</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="Q41">
-        <f t="shared" ca="1" si="13"/>
-        <v>3.6383542810021097E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="R41">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.9274753200136624</v>
+        <v>1.47E-2</v>
       </c>
       <c r="S41">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.89601077555076858</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="T41">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.83856103125758297</v>
+        <v>1.49E-2</v>
       </c>
       <c r="U41">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.40408102203359908</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="7"/>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.622934815091161</v>
+        <v>1.4E-2</v>
       </c>
       <c r="C42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.9572771644618191</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="D42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.2513602446569112</v>
+        <v>1.4666666666666672E-2</v>
       </c>
       <c r="E42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.32427962130893151</v>
+        <v>1.4833333333333329E-2</v>
       </c>
       <c r="F42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.96844895224285976</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.28295965450109528</v>
+        <v>1.52E-2</v>
       </c>
       <c r="H42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.43378693975686444</v>
+        <v>1.54E-2</v>
       </c>
       <c r="I42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.16542129287589458</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="J42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.48202666825036267</v>
+        <v>1.5800000000000002E-2</v>
       </c>
       <c r="K42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.85860869072119295</v>
+        <v>1.6E-2</v>
       </c>
       <c r="L42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.22299410061278702</v>
+        <v>1.61E-2</v>
       </c>
       <c r="M42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.79459977711518115</v>
+        <v>1.6199999999999999E-2</v>
       </c>
       <c r="N42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.55719967577960539</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="O42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.88576766870446211</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="P42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.62487594830182214</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q42">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.23605814634334976</v>
+        <v>1.66E-2</v>
       </c>
       <c r="R42">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.63427492263368779</v>
+        <v>1.67E-2</v>
       </c>
       <c r="S42">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.62474285140185326</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="T42">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.82179065477848356</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="U42">
-        <f t="shared" ca="1" si="14"/>
-        <v>3.2944468612008726E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
+      <c r="AA42" s="7"/>
+      <c r="AB42" s="7"/>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.9079524015753021</v>
+        <v>1.6E-2</v>
       </c>
       <c r="C43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.351778264982616</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="D43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.69212222588374295</v>
+        <v>1.666666666666667E-2</v>
       </c>
       <c r="E43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.21494620275516607</v>
+        <v>1.6833333333333329E-2</v>
       </c>
       <c r="F43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.11112276493928874</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.11541833033325322</v>
+        <v>1.72E-2</v>
       </c>
       <c r="H43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.24132793348960979</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="I43">
-        <f t="shared" ca="1" si="13"/>
-        <v>5.5463836993736582E-2</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="J43">
-        <f t="shared" ca="1" si="13"/>
-        <v>3.9270799944444712E-2</v>
+        <v>1.78E-2</v>
       </c>
       <c r="K43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.36525435747758861</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="L43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.98698216178536768</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="M43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.61233187269241185</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="N43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.45938235374447633</v>
+        <v>1.83E-2</v>
       </c>
       <c r="O43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.97955716221504863</v>
+        <v>1.84E-2</v>
       </c>
       <c r="P43">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.86222181299559963</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="Q43">
-        <f t="shared" ca="1" si="13"/>
-        <v>8.5046450192737932E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="R43">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.38447322941256012</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="S43">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.52386791548415734</v>
+        <v>1.8800000000000001E-2</v>
       </c>
       <c r="T43">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.1608754839813693</v>
+        <v>1.89E-2</v>
       </c>
       <c r="U43">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.51168085630377913</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+        <v>1.9E-2</v>
+      </c>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="7"/>
+      <c r="AA43" s="7"/>
+      <c r="AB43" s="7"/>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.79808094825767184</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="C44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.16325158981660515</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="D44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.27633808934508974</v>
+        <v>1.8666666666666672E-2</v>
       </c>
       <c r="E44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.57885540060009655</v>
+        <v>1.8833333333333327E-2</v>
       </c>
       <c r="F44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.23328206783492444</v>
+        <v>1.9E-2</v>
       </c>
       <c r="G44">
-        <f t="shared" ca="1" si="13"/>
-        <v>1.7270907195652385E-2</v>
+        <v>1.9199999999999998E-2</v>
       </c>
       <c r="H44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.25406225119623571</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="I44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.98484967897832199</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="J44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.46716593029023323</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="K44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.42428853904915487</v>
+        <v>0.02</v>
       </c>
       <c r="L44">
-        <f t="shared" ca="1" si="13"/>
-        <v>3.641620786339006E-3</v>
+        <v>2.01E-2</v>
       </c>
       <c r="M44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.18947220096105999</v>
+        <v>2.0199999999999999E-2</v>
       </c>
       <c r="N44">
-        <f t="shared" ca="1" si="13"/>
-        <v>2.375329903846557E-2</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="O44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.47859556926507718</v>
+        <v>2.0400000000000001E-2</v>
       </c>
       <c r="P44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.40158272045132348</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="Q44">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.76500266925456362</v>
+        <v>2.06E-2</v>
       </c>
       <c r="R44">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.51557972022697385</v>
+        <v>2.07E-2</v>
       </c>
       <c r="S44">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.12345726161432991</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="T44">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.16458215901005457</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="U44">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.96497478368177803</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="W44" s="7"/>
+      <c r="X44" s="7"/>
+      <c r="Y44" s="7"/>
+      <c r="Z44" s="7"/>
+      <c r="AA44" s="7"/>
+      <c r="AB44" s="7"/>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C45" s="4">
-        <v>0</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="D45" s="4">
-        <v>0</v>
+        <v>2.066666666666667E-2</v>
       </c>
       <c r="E45" s="4">
-        <v>0</v>
+        <v>2.0833333333333329E-2</v>
       </c>
       <c r="F45" s="4">
-        <v>0</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G45" s="4">
-        <v>0</v>
+        <v>2.12E-2</v>
       </c>
       <c r="H45" s="4">
-        <v>0</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="I45" s="4">
-        <v>0</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="J45" s="4">
-        <v>0</v>
+        <v>2.18E-2</v>
       </c>
       <c r="K45" s="4">
-        <v>0</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="L45" s="4">
-        <v>0</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="M45" s="4">
-        <v>0</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="N45" s="4">
-        <v>0</v>
+        <v>2.23E-2</v>
       </c>
       <c r="O45" s="4">
-        <v>0</v>
+        <v>2.24E-2</v>
       </c>
       <c r="P45" s="4">
-        <v>0</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="Q45" s="4">
-        <v>0</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="R45" s="4">
-        <v>0</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="S45" s="4">
-        <v>0</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="T45" s="4">
-        <v>0</v>
+        <v>2.29E-2</v>
       </c>
       <c r="U45" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+        <v>2.3E-2</v>
+      </c>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="7"/>
+      <c r="AA45" s="7"/>
+      <c r="AB45" s="7"/>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="4">
-        <v>0</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="C46" s="4">
-        <v>0</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="D46" s="4">
-        <v>0</v>
+        <v>2.2666666666666672E-2</v>
       </c>
       <c r="E46" s="4">
-        <v>0</v>
+        <v>2.2833333333333327E-2</v>
       </c>
       <c r="F46" s="4">
-        <v>0</v>
+        <v>2.3E-2</v>
       </c>
       <c r="G46" s="4">
-        <v>0</v>
+        <v>2.3199999999999998E-2</v>
       </c>
       <c r="H46" s="4">
-        <v>0</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="I46" s="4">
-        <v>0</v>
+        <v>2.3599999999999999E-2</v>
       </c>
       <c r="J46" s="4">
-        <v>0</v>
+        <v>2.3800000000000002E-2</v>
       </c>
       <c r="K46" s="4">
-        <v>0</v>
+        <v>2.4E-2</v>
       </c>
       <c r="L46" s="4">
-        <v>0</v>
+        <v>2.41E-2</v>
       </c>
       <c r="M46" s="4">
-        <v>0</v>
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="N46" s="4">
-        <v>0</v>
+        <v>2.4299999999999999E-2</v>
       </c>
       <c r="O46" s="4">
-        <v>0</v>
+        <v>2.4400000000000002E-2</v>
       </c>
       <c r="P46" s="4">
-        <v>0</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="Q46" s="4">
-        <v>0</v>
+        <v>2.46E-2</v>
       </c>
       <c r="R46" s="4">
-        <v>0</v>
+        <v>2.47E-2</v>
       </c>
       <c r="S46" s="4">
-        <v>0</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="T46" s="4">
-        <v>0</v>
+        <v>2.4899999999999999E-2</v>
       </c>
       <c r="U46" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
+      <c r="Y46" s="7"/>
+      <c r="Z46" s="7"/>
+      <c r="AA46" s="7"/>
+      <c r="AB46" s="7"/>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B47">
-        <f t="shared" ref="B47:Q51" ca="1" si="15">RAND()</f>
-        <v>6.7765916272566229E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="C47">
-        <f t="shared" ca="1" si="15"/>
-        <v>7.8683206913990777E-2</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="D47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.33204122904657363</v>
+        <v>8.666666666666668E-3</v>
       </c>
       <c r="E47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.91665269087378476</v>
+        <v>8.8333333333333337E-3</v>
       </c>
       <c r="F47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.74771176012747331</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.6826329705711357</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="H47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.16510529360690174</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="I47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.63644151860991904</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.65291219332593542</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="K47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.89092495178483966</v>
+        <v>0.01</v>
       </c>
       <c r="L47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.38890032124280272</v>
+        <v>1.01E-2</v>
       </c>
       <c r="M47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.46001174677204826</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="N47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.10907162223484801</v>
+        <v>1.03E-2</v>
       </c>
       <c r="O47">
-        <f t="shared" ca="1" si="15"/>
-        <v>4.9897612687668347E-2</v>
+        <v>1.04E-2</v>
       </c>
       <c r="P47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.63053972504960631</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="Q47">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.77253662409136514</v>
+        <v>1.06E-2</v>
       </c>
       <c r="R47">
-        <f t="shared" ref="R47:U51" ca="1" si="16">RAND()</f>
-        <v>0.95836631421064999</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="S47">
-        <f t="shared" ca="1" si="16"/>
-        <v>4.1131826313015596E-2</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="T47">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.62341330476019208</v>
+        <v>1.09E-2</v>
       </c>
       <c r="U47">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.48242183146205952</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="W47" s="7"/>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.44201850196230619</v>
+        <v>0.01</v>
       </c>
       <c r="C48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.11222622979281061</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="D48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.22824943759719218</v>
+        <v>1.066666666666667E-2</v>
       </c>
       <c r="E48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.91782106009600628</v>
+        <v>1.083333333333333E-2</v>
       </c>
       <c r="F48">
-        <f t="shared" ca="1" si="15"/>
-        <v>8.9774856826118188E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="G48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.3463097178806156</v>
+        <v>1.12E-2</v>
       </c>
       <c r="H48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.51182677824376144</v>
+        <v>1.14E-2</v>
       </c>
       <c r="I48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.65387281057705149</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="J48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.49454030593053189</v>
+        <v>1.18E-2</v>
       </c>
       <c r="K48">
-        <f t="shared" ca="1" si="15"/>
-        <v>7.8298834645999627E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="L48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.26053488051109241</v>
+        <v>1.21E-2</v>
       </c>
       <c r="M48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.12759184685681768</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="N48">
-        <f t="shared" ca="1" si="15"/>
-        <v>4.0671159807036728E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="O48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.67455362569455157</v>
+        <v>1.24E-2</v>
       </c>
       <c r="P48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.20663090735082157</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="Q48">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.92147928735602425</v>
+        <v>1.26E-2</v>
       </c>
       <c r="R48">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.14126790376043297</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="S48">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.78267731500557969</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="T48">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.27769706369675917</v>
+        <v>1.29E-2</v>
       </c>
       <c r="U48">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.73248637531159122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="W48" s="7"/>
+      <c r="X48" s="7"/>
+      <c r="Y48" s="7"/>
+      <c r="Z48" s="7"/>
+      <c r="AA48" s="7"/>
+      <c r="AB48" s="7"/>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.14304878505491991</v>
+        <v>1.2E-2</v>
       </c>
       <c r="C49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.26302265889258902</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="D49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.29807811558755826</v>
+        <v>1.266666666666667E-2</v>
       </c>
       <c r="E49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.35335050532531298</v>
+        <v>1.2833333333333329E-2</v>
       </c>
       <c r="F49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.19827369203000011</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G49">
-        <f t="shared" ca="1" si="15"/>
-        <v>4.6588525681797388E-2</v>
+        <v>1.32E-2</v>
       </c>
       <c r="H49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.57464789544360995</v>
+        <v>1.34E-2</v>
       </c>
       <c r="I49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.45192639460546546</v>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="J49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.5404591940546144</v>
+        <v>1.38E-2</v>
       </c>
       <c r="K49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.68790744237848589</v>
+        <v>1.4E-2</v>
       </c>
       <c r="L49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.13038410907771525</v>
+        <v>1.41E-2</v>
       </c>
       <c r="M49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.98493872885520539</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="N49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.26403551750874688</v>
+        <v>1.43E-2</v>
       </c>
       <c r="O49">
-        <f t="shared" ca="1" si="15"/>
-        <v>9.3510702261641931E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="P49">
-        <f t="shared" ca="1" si="15"/>
-        <v>6.1749785749609432E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="Q49">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.54040314349599206</v>
+        <v>1.46E-2</v>
       </c>
       <c r="R49">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.39614730741105397</v>
+        <v>1.47E-2</v>
       </c>
       <c r="S49">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.90161690277327378</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="T49">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.57513361821908637</v>
+        <v>1.49E-2</v>
       </c>
       <c r="U49">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.168824441612625</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
+      <c r="Y49" s="7"/>
+      <c r="Z49" s="7"/>
+      <c r="AA49" s="7"/>
+      <c r="AB49" s="7"/>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.1146621436989409</v>
+        <v>1.4E-2</v>
       </c>
       <c r="C50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.55001534938466456</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="D50">
-        <f t="shared" ca="1" si="15"/>
-        <v>2.3136423202467782E-2</v>
+        <v>1.4666666666666672E-2</v>
       </c>
       <c r="E50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.94336117025919641</v>
+        <v>1.4833333333333329E-2</v>
       </c>
       <c r="F50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.95281489920284157</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.84108391750179468</v>
+        <v>1.52E-2</v>
       </c>
       <c r="H50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.41568614642178559</v>
+        <v>1.54E-2</v>
       </c>
       <c r="I50">
-        <f t="shared" ca="1" si="15"/>
-        <v>7.5178547249413752E-3</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="J50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.19656972183605981</v>
+        <v>1.5800000000000002E-2</v>
       </c>
       <c r="K50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.66748175025529877</v>
+        <v>1.6E-2</v>
       </c>
       <c r="L50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.27827693107662876</v>
+        <v>1.61E-2</v>
       </c>
       <c r="M50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.81722333803023184</v>
+        <v>1.6199999999999999E-2</v>
       </c>
       <c r="N50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.7149933611610958</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="O50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.90714047524822117</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="P50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.6775229682415812</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q50">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.26693236517595254</v>
+        <v>1.66E-2</v>
       </c>
       <c r="R50">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.38031240115159981</v>
+        <v>1.67E-2</v>
       </c>
       <c r="S50">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.24909809904355784</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="T50">
-        <f t="shared" ca="1" si="16"/>
-        <v>9.56193530102315E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="U50">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.30945106324905824</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="W50" s="7"/>
+      <c r="X50" s="7"/>
+      <c r="Y50" s="7"/>
+      <c r="Z50" s="7"/>
+      <c r="AA50" s="7"/>
+      <c r="AB50" s="7"/>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.35741480167658213</v>
+        <v>1.6E-2</v>
       </c>
       <c r="C51">
-        <f t="shared" ca="1" si="15"/>
-        <v>1.9036224580679328E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="D51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.22419873414011027</v>
+        <v>1.666666666666667E-2</v>
       </c>
       <c r="E51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.48553231140032216</v>
+        <v>1.6833333333333329E-2</v>
       </c>
       <c r="F51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.46961604796492284</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.11523427327605629</v>
+        <v>1.72E-2</v>
       </c>
       <c r="H51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.35291075674254624</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="I51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.65266088113824805</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="J51">
-        <f t="shared" ca="1" si="15"/>
-        <v>8.5936979363917976E-2</v>
+        <v>1.78E-2</v>
       </c>
       <c r="K51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.80359335736910475</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="L51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.55358728290000803</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="M51">
-        <f t="shared" ca="1" si="15"/>
-        <v>1.2239702437443212E-3</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="N51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.29779659955661375</v>
+        <v>1.83E-2</v>
       </c>
       <c r="O51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.8776412456781888</v>
+        <v>1.84E-2</v>
       </c>
       <c r="P51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.82163221467805925</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="Q51">
-        <f t="shared" ca="1" si="15"/>
-        <v>0.98053884439076777</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="R51">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.64550818962162115</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="S51">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.10808415852876641</v>
+        <v>1.8800000000000001E-2</v>
       </c>
       <c r="T51">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.86322220360281954</v>
+        <v>1.89E-2</v>
       </c>
       <c r="U51">
-        <f t="shared" ca="1" si="16"/>
-        <v>0.90397349298902219</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1.9E-2</v>
+      </c>
+      <c r="X51" s="7"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="7"/>
+      <c r="AA51" s="7"/>
+      <c r="AB51" s="7"/>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="4">
-        <v>0</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="C52" s="4">
-        <v>0</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="D52" s="4">
-        <v>0</v>
+        <v>1.8666666666666672E-2</v>
       </c>
       <c r="E52" s="4">
-        <v>0</v>
+        <v>1.8833333333333327E-2</v>
       </c>
       <c r="F52" s="4">
-        <v>0</v>
+        <v>1.9E-2</v>
       </c>
       <c r="G52" s="4">
-        <v>0</v>
+        <v>1.9199999999999998E-2</v>
       </c>
       <c r="H52" s="4">
-        <v>0</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="I52" s="4">
-        <v>0</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="J52" s="4">
-        <v>0</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="K52" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L52" s="4">
-        <v>0</v>
+        <v>2.01E-2</v>
       </c>
       <c r="M52" s="4">
-        <v>0</v>
+        <v>2.0199999999999999E-2</v>
       </c>
       <c r="N52" s="4">
-        <v>0</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="O52" s="4">
-        <v>0</v>
+        <v>2.0400000000000001E-2</v>
       </c>
       <c r="P52" s="4">
-        <v>0</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="Q52" s="4">
-        <v>0</v>
+        <v>2.06E-2</v>
       </c>
       <c r="R52" s="4">
-        <v>0</v>
+        <v>2.07E-2</v>
       </c>
       <c r="S52" s="4">
-        <v>0</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="T52" s="4">
-        <v>0</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="U52" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X52" s="7"/>
+      <c r="Y52" s="7"/>
+      <c r="Z52" s="7"/>
+      <c r="AA52" s="7"/>
+      <c r="AB52" s="7"/>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C53" s="4">
-        <v>0</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="D53" s="4">
-        <v>0</v>
+        <v>2.066666666666667E-2</v>
       </c>
       <c r="E53" s="4">
-        <v>0</v>
+        <v>2.0833333333333329E-2</v>
       </c>
       <c r="F53" s="4">
-        <v>0</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G53" s="4">
-        <v>0</v>
+        <v>2.12E-2</v>
       </c>
       <c r="H53" s="4">
-        <v>0</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="I53" s="4">
-        <v>0</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="J53" s="4">
-        <v>0</v>
+        <v>2.18E-2</v>
       </c>
       <c r="K53" s="4">
-        <v>0</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="L53" s="4">
-        <v>0</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="M53" s="4">
-        <v>0</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="N53" s="4">
-        <v>0</v>
+        <v>2.23E-2</v>
       </c>
       <c r="O53" s="4">
-        <v>0</v>
+        <v>2.24E-2</v>
       </c>
       <c r="P53" s="4">
-        <v>0</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="Q53" s="4">
-        <v>0</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="R53" s="4">
-        <v>0</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="S53" s="4">
-        <v>0</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="T53" s="4">
-        <v>0</v>
+        <v>2.29E-2</v>
       </c>
       <c r="U53" s="4">
-        <v>0</v>
-      </c>
+        <v>2.3E-2</v>
+      </c>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="7"/>
+      <c r="AA53" s="7"/>
+      <c r="AB53" s="7"/>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7"/>
+      <c r="AA54" s="7"/>
+      <c r="AB54" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -8,21 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E0D9B-BB3F-49EA-BD09-384FD1A6FB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5F7ECE-E0A8-4E67-81F8-91C13364AC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="rates_alt" sheetId="1" r:id="rId1"/>
-    <sheet name="rates_sw" sheetId="2" r:id="rId2"/>
+    <sheet name="zero_rates_alt" sheetId="1" r:id="rId1"/>
+    <sheet name="zero_rates_sw" sheetId="2" r:id="rId2"/>
     <sheet name="spreads_va" sheetId="3" r:id="rId3"/>
+    <sheet name="SWAP_rates_al_EIOPA_EXCEL" sheetId="4" r:id="rId4"/>
+    <sheet name="SWAP_rates_sw_EIOPA_EXCEL" sheetId="5" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="BBDATA">OFFSET('[1]INPUT DATA'!$C$8,0,0,'[1]INPUT DATA'!$A$6,50)</definedName>
-    <definedName name="CalcDate" localSheetId="1">rates_sw!$D$4</definedName>
+    <definedName name="CalcDate" localSheetId="4">SWAP_rates_sw_EIOPA_EXCEL!$D$4</definedName>
+    <definedName name="CalcDate" localSheetId="1">zero_rates_sw!$D$4</definedName>
     <definedName name="DateList">OFFSET('[1]INPUT DATA'!$B$8,0,0,'[1]INPUT DATA'!$A$6,1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>Tenor</t>
   </si>
@@ -660,7 +663,7 @@
   <cols>
     <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -688,8 +691,8 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>-4.449999999999843E-3</v>
+      <c r="D2" s="8">
+        <v>3.5139999999999998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -702,8 +705,8 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3">
-        <v>-4.7492877139407863E-3</v>
+      <c r="D3" s="8">
+        <v>3.0349999999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -716,8 +719,8 @@
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4">
-        <v>-4.8490311393776242E-3</v>
+      <c r="D4" s="8">
+        <v>2.7830000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -730,8 +733,8 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>-4.6506939059682839E-3</v>
+      <c r="D5" s="8">
+        <v>2.6370000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -744,8 +747,8 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6">
-        <v>-4.4523045769666592E-3</v>
+      <c r="D6" s="8">
+        <v>2.5489999999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -758,8 +761,8 @@
       <c r="C7">
         <v>0</v>
       </c>
-      <c r="D7">
-        <v>-4.1548916903217936E-3</v>
+      <c r="D7" s="8">
+        <v>2.5020000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -772,8 +775,8 @@
       <c r="C8">
         <v>0</v>
       </c>
-      <c r="D8">
-        <v>-3.8573434612039215E-3</v>
+      <c r="D8" s="8">
+        <v>2.477E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -786,8 +789,8 @@
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>-3.460578737007669E-3</v>
+      <c r="D9" s="8">
+        <v>2.4660000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -800,8 +803,8 @@
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10">
-        <v>-3.0631946140144972E-3</v>
+      <c r="D10" s="8">
+        <v>2.4639999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -814,8 +817,8 @@
       <c r="C11">
         <v>0</v>
       </c>
-      <c r="D11">
-        <v>-2.6651020891858002E-3</v>
+      <c r="D11" s="8">
+        <v>2.47E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -828,8 +831,8 @@
       <c r="C12">
         <v>0</v>
       </c>
-      <c r="D12">
-        <v>-2.3428351222567478E-3</v>
+      <c r="D12" s="8">
+        <v>2.487E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -842,8 +845,8 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13">
-        <v>-1.8664394833945996E-3</v>
+      <c r="D13" s="8">
+        <v>2.487E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -856,8 +859,8 @@
       <c r="C14">
         <v>0</v>
       </c>
-      <c r="D14">
-        <v>-1.5785481548286073E-3</v>
+      <c r="D14" s="8">
+        <v>2.4920000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -870,8 +873,8 @@
       <c r="C15">
         <v>0</v>
       </c>
-      <c r="D15">
-        <v>-1.2510909281734373E-3</v>
+      <c r="D15" s="8">
+        <v>2.4989999999999998E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -884,8 +887,8 @@
       <c r="C16">
         <v>0</v>
       </c>
-      <c r="D16">
-        <v>-9.4192697808626047E-4</v>
+      <c r="D16" s="8">
+        <v>2.4979999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -898,8 +901,8 @@
       <c r="C17">
         <v>0</v>
       </c>
-      <c r="D17">
-        <v>-7.7497898425404887E-4</v>
+      <c r="D17" s="8">
+        <v>2.486E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -912,8 +915,8 @@
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="D18">
-        <v>-6.276487632096428E-4</v>
+      <c r="D18" s="8">
+        <v>2.4660000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -926,8 +929,8 @@
       <c r="C19">
         <v>0</v>
       </c>
-      <c r="D19">
-        <v>-4.9667033020839302E-4</v>
+      <c r="D19" s="8">
+        <v>2.4459999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -940,8 +943,8 @@
       <c r="C20">
         <v>0</v>
       </c>
-      <c r="D20">
-        <v>-3.7946454996118373E-4</v>
+      <c r="D20" s="8">
+        <v>2.427E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -954,8 +957,8 @@
       <c r="C21">
         <v>0.33</v>
       </c>
-      <c r="D21">
-        <v>-2.7396759664655157E-4</v>
+      <c r="D21" s="8">
+        <v>2.4150000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -968,8 +971,8 @@
       <c r="C22">
         <v>0</v>
       </c>
-      <c r="D22">
-        <v>-1.9306145426889465E-4</v>
+      <c r="D22" s="8">
+        <v>2.409E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -982,8 +985,8 @@
       <c r="C23">
         <v>0</v>
       </c>
-      <c r="D23">
-        <v>3.356441626500839E-5</v>
+      <c r="D23" s="8">
+        <v>2.409E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -996,8 +999,8 @@
       <c r="C24">
         <v>0</v>
       </c>
-      <c r="D24">
-        <v>3.7305572938839404E-4</v>
+      <c r="D24" s="8">
+        <v>2.4129999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1010,8 +1013,8 @@
       <c r="C25">
         <v>0</v>
       </c>
-      <c r="D25">
-        <v>7.9932639103041936E-4</v>
+      <c r="D25" s="8">
+        <v>2.4209999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1024,8 +1027,8 @@
       <c r="C26">
         <v>0.12</v>
       </c>
-      <c r="D26">
-        <v>1.2915728598819065E-3</v>
+      <c r="D26" s="8">
+        <v>2.4309999999999998E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1038,8 +1041,8 @@
       <c r="C27">
         <v>0</v>
       </c>
-      <c r="D27">
-        <v>1.8331481078603939E-3</v>
+      <c r="D27" s="8">
+        <v>2.443E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1052,8 +1055,8 @@
       <c r="C28">
         <v>0</v>
       </c>
-      <c r="D28">
-        <v>2.4106989351067032E-3</v>
+      <c r="D28" s="8">
+        <v>2.4570000000000002E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1066,8 +1069,8 @@
       <c r="C29">
         <v>0</v>
       </c>
-      <c r="D29">
-        <v>3.0134986404870556E-3</v>
+      <c r="D29" s="8">
+        <v>2.4719999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1080,8 +1083,8 @@
       <c r="C30">
         <v>0</v>
       </c>
-      <c r="D30">
-        <v>3.6329263050836058E-3</v>
+      <c r="D30" s="8">
+        <v>2.487E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1094,8 +1097,8 @@
       <c r="C31">
         <v>0.48</v>
       </c>
-      <c r="D31">
-        <v>4.2620572835279091E-3</v>
+      <c r="D31" s="8">
+        <v>2.5020000000000001E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1108,8 +1111,8 @@
       <c r="C32">
         <v>0</v>
       </c>
-      <c r="D32">
-        <v>4.895338870999133E-3</v>
+      <c r="D32" s="8">
+        <v>2.5180000000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1122,8 +1125,8 @@
       <c r="C33">
         <v>0</v>
       </c>
-      <c r="D33">
-        <v>5.5283317896184236E-3</v>
+      <c r="D33" s="8">
+        <v>2.5340000000000001E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1136,8 +1139,8 @@
       <c r="C34">
         <v>0</v>
       </c>
-      <c r="D34">
-        <v>6.1575029522564773E-3</v>
+      <c r="D34" s="8">
+        <v>2.5499999999999998E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1150,8 +1153,8 @@
       <c r="C35">
         <v>0</v>
       </c>
-      <c r="D35">
-        <v>6.7800584737407465E-3</v>
+      <c r="D35" s="8">
+        <v>2.5659999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1164,8 +1167,8 @@
       <c r="C36">
         <v>0</v>
       </c>
-      <c r="D36">
-        <v>7.3938084889249023E-3</v>
+      <c r="D36" s="8">
+        <v>2.581E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1178,8 +1181,8 @@
       <c r="C37">
         <v>0</v>
       </c>
-      <c r="D37">
-        <v>7.997057265482832E-3</v>
+      <c r="D37" s="8">
+        <v>2.596E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1192,8 +1195,8 @@
       <c r="C38">
         <v>0</v>
       </c>
-      <c r="D38">
-        <v>8.5885135487726583E-3</v>
+      <c r="D38" s="8">
+        <v>2.6110000000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1206,8 +1209,8 @@
       <c r="C39">
         <v>0</v>
       </c>
-      <c r="D39">
-        <v>9.1672171750911691E-3</v>
+      <c r="D39" s="8">
+        <v>2.6259999999999999E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1220,8 +1223,8 @@
       <c r="C40">
         <v>0</v>
       </c>
-      <c r="D40">
-        <v>9.7324788296642151E-3</v>
+      <c r="D40" s="8">
+        <v>2.64E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1234,8 +1237,8 @@
       <c r="C41">
         <v>0.04</v>
       </c>
-      <c r="D41">
-        <v>1.0283830472670896E-2</v>
+      <c r="D41" s="8">
+        <v>2.6540000000000001E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1248,8 +1251,8 @@
       <c r="C42">
         <v>0</v>
       </c>
-      <c r="D42">
-        <v>1.0820984458427274E-2</v>
+      <c r="D42" s="8">
+        <v>2.6669999999999999E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1262,8 +1265,8 @@
       <c r="C43">
         <v>0</v>
       </c>
-      <c r="D43">
-        <v>1.1343799764694351E-2</v>
+      <c r="D43" s="8">
+        <v>2.6800000000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1276,8 +1279,8 @@
       <c r="C44">
         <v>0</v>
       </c>
-      <c r="D44">
-        <v>1.1852254056962552E-2</v>
+      <c r="D44" s="8">
+        <v>2.6929999999999999E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1290,8 +1293,8 @@
       <c r="C45">
         <v>0</v>
       </c>
-      <c r="D45">
-        <v>1.234642055588786E-2</v>
+      <c r="D45" s="8">
+        <v>2.7050000000000001E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1304,8 +1307,8 @@
       <c r="C46">
         <v>0</v>
       </c>
-      <c r="D46">
-        <v>1.2826448869438511E-2</v>
+      <c r="D46" s="8">
+        <v>2.717E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1318,8 +1321,8 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="D47">
-        <v>1.3292549105763385E-2</v>
+      <c r="D47" s="8">
+        <v>2.7279999999999999E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1332,8 +1335,8 @@
       <c r="C48">
         <v>0</v>
       </c>
-      <c r="D48">
-        <v>1.3744978706791366E-2</v>
+      <c r="D48" s="8">
+        <v>2.7390000000000001E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1346,8 +1349,8 @@
       <c r="C49">
         <v>0</v>
       </c>
-      <c r="D49">
-        <v>1.4184031542527009E-2</v>
+      <c r="D49" s="8">
+        <v>2.75E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1360,8 +1363,8 @@
       <c r="C50">
         <v>0</v>
       </c>
-      <c r="D50">
-        <v>1.4610028886971271E-2</v>
+      <c r="D50" s="8">
+        <v>2.76E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1374,8 +1377,8 @@
       <c r="C51">
         <v>0.03</v>
       </c>
-      <c r="D51">
-        <v>1.5023311962402364E-2</v>
+      <c r="D51" s="8">
+        <v>2.7709999999999999E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1388,8 +1391,8 @@
       <c r="C52">
         <v>0</v>
       </c>
-      <c r="D52">
-        <v>1.542423579245833E-2</v>
+      <c r="D52" s="8">
+        <v>2.7799999999999998E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1402,8 +1405,8 @@
       <c r="C53">
         <v>0</v>
       </c>
-      <c r="D53">
-        <v>1.581316414844669E-2</v>
+      <c r="D53" s="8">
+        <v>2.7900000000000001E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1416,8 +1419,8 @@
       <c r="C54">
         <v>0</v>
       </c>
-      <c r="D54">
-        <v>1.6190465409437804E-2</v>
+      <c r="D54" s="8">
+        <v>2.7990000000000001E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1430,8 +1433,8 @@
       <c r="C55">
         <v>0</v>
       </c>
-      <c r="D55">
-        <v>1.6556509186476109E-2</v>
+      <c r="D55" s="8">
+        <v>2.8080000000000001E-2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1444,8 +1447,8 @@
       <c r="C56">
         <v>0</v>
       </c>
-      <c r="D56">
-        <v>1.691166358586238E-2</v>
+      <c r="D56" s="8">
+        <v>2.8160000000000001E-2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1458,8 +1461,8 @@
       <c r="C57">
         <v>0</v>
       </c>
-      <c r="D57">
-        <v>1.7256293006847168E-2</v>
+      <c r="D57" s="8">
+        <v>2.8250000000000001E-2</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1472,8 +1475,8 @@
       <c r="C58">
         <v>0</v>
       </c>
-      <c r="D58">
-        <v>1.759075638602825E-2</v>
+      <c r="D58" s="8">
+        <v>2.8330000000000001E-2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1486,8 +1489,8 @@
       <c r="C59">
         <v>0</v>
       </c>
-      <c r="D59">
-        <v>1.7915405814849628E-2</v>
+      <c r="D59" s="8">
+        <v>2.8400000000000002E-2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1500,8 +1503,8 @@
       <c r="C60">
         <v>0</v>
       </c>
-      <c r="D60">
-        <v>1.8230585468377525E-2</v>
+      <c r="D60" s="8">
+        <v>2.8479999999999998E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1514,8 +1517,8 @@
       <c r="C61">
         <v>0</v>
       </c>
-      <c r="D61">
-        <v>1.8536630793370756E-2</v>
+      <c r="D61" s="8">
+        <v>2.8549999999999999E-2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1528,8 +1531,8 @@
       <c r="C62">
         <v>0</v>
       </c>
-      <c r="D62">
-        <v>1.8833867911915103E-2</v>
+      <c r="D62" s="8">
+        <v>2.862E-2</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -1542,8 +1545,8 @@
       <c r="C63">
         <v>0</v>
       </c>
-      <c r="D63">
-        <v>1.9122613203806038E-2</v>
+      <c r="D63" s="8">
+        <v>2.869E-2</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -1556,8 +1559,8 @@
       <c r="C64">
         <v>0</v>
       </c>
-      <c r="D64">
-        <v>1.9403173036683707E-2</v>
+      <c r="D64" s="8">
+        <v>2.8760000000000001E-2</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -1570,8 +1573,8 @@
       <c r="C65">
         <v>0</v>
       </c>
-      <c r="D65">
-        <v>1.9675843617816824E-2</v>
+      <c r="D65" s="8">
+        <v>2.8830000000000001E-2</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1584,8 +1587,8 @@
       <c r="C66">
         <v>0</v>
       </c>
-      <c r="D66">
-        <v>1.9940910945556833E-2</v>
+      <c r="D66" s="8">
+        <v>2.8889999999999999E-2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1598,8 +1601,8 @@
       <c r="C67">
         <v>0</v>
       </c>
-      <c r="D67">
-        <v>2.019865084195871E-2</v>
+      <c r="D67" s="8">
+        <v>2.895E-2</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1612,8 +1615,8 @@
       <c r="C68">
         <v>0</v>
       </c>
-      <c r="D68">
-        <v>2.0449329051009046E-2</v>
+      <c r="D68" s="8">
+        <v>2.9010000000000001E-2</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -1626,8 +1629,8 @@
       <c r="C69">
         <v>0</v>
       </c>
-      <c r="D69">
-        <v>2.0693201389375693E-2</v>
+      <c r="D69" s="8">
+        <v>2.9069999999999999E-2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1640,8 +1643,8 @@
       <c r="C70">
         <v>0</v>
       </c>
-      <c r="D70">
-        <v>2.0930513938697271E-2</v>
+      <c r="D70" s="8">
+        <v>2.912E-2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -1654,8 +1657,8 @@
       <c r="C71">
         <v>0</v>
       </c>
-      <c r="D71">
-        <v>2.1161503270206383E-2</v>
+      <c r="D71" s="8">
+        <v>2.9180000000000001E-2</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -1668,8 +1671,8 @@
       <c r="C72">
         <v>0</v>
       </c>
-      <c r="D72">
-        <v>2.1386396693980902E-2</v>
+      <c r="D72" s="8">
+        <v>2.9229999999999999E-2</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -1682,8 +1685,8 @@
       <c r="C73">
         <v>0</v>
       </c>
-      <c r="D73">
-        <v>2.1605412526390921E-2</v>
+      <c r="D73" s="8">
+        <v>2.928E-2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -1696,8 +1699,8 @@
       <c r="C74">
         <v>0</v>
       </c>
-      <c r="D74">
-        <v>2.1818760370390544E-2</v>
+      <c r="D74" s="8">
+        <v>2.9329999999999998E-2</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -1710,8 +1713,8 @@
       <c r="C75">
         <v>0</v>
       </c>
-      <c r="D75">
-        <v>2.2026641404207181E-2</v>
+      <c r="D75" s="8">
+        <v>2.938E-2</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -1724,8 +1727,8 @@
       <c r="C76">
         <v>0</v>
       </c>
-      <c r="D76">
-        <v>2.2229248674763724E-2</v>
+      <c r="D76" s="8">
+        <v>2.9430000000000001E-2</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -1738,8 +1741,8 @@
       <c r="C77">
         <v>0</v>
       </c>
-      <c r="D77">
-        <v>2.2426767392813352E-2</v>
+      <c r="D77" s="8">
+        <v>2.9479999999999999E-2</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -1752,8 +1755,8 @@
       <c r="C78">
         <v>0</v>
       </c>
-      <c r="D78">
-        <v>2.2619375227323602E-2</v>
+      <c r="D78" s="8">
+        <v>2.9520000000000001E-2</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -1766,8 +1769,8 @@
       <c r="C79">
         <v>0</v>
       </c>
-      <c r="D79">
-        <v>2.2807242597112198E-2</v>
+      <c r="D79" s="8">
+        <v>2.9569999999999999E-2</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -1780,8 +1783,8 @@
       <c r="C80">
         <v>0</v>
       </c>
-      <c r="D80">
-        <v>2.2990532958129695E-2</v>
+      <c r="D80" s="8">
+        <v>2.9610000000000001E-2</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -1794,8 +1797,8 @@
       <c r="C81">
         <v>0</v>
       </c>
-      <c r="D81">
-        <v>2.3169403085117946E-2</v>
+      <c r="D81" s="8">
+        <v>2.9649999999999999E-2</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -1808,8 +1811,8 @@
       <c r="C82">
         <v>0</v>
       </c>
-      <c r="D82">
-        <v>2.3344003346649211E-2</v>
+      <c r="D82" s="8">
+        <v>2.9690000000000001E-2</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -1822,8 +1825,8 @@
       <c r="C83">
         <v>0</v>
       </c>
-      <c r="D83">
-        <v>2.3514477972788494E-2</v>
+      <c r="D83" s="8">
+        <v>2.9729999999999999E-2</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -1836,8 +1839,8 @@
       <c r="C84">
         <v>0</v>
       </c>
-      <c r="D84">
-        <v>2.3680965314814229E-2</v>
+      <c r="D84" s="8">
+        <v>2.9770000000000001E-2</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -1850,8 +1853,8 @@
       <c r="C85">
         <v>0</v>
       </c>
-      <c r="D85">
-        <v>2.3843598096600749E-2</v>
+      <c r="D85" s="8">
+        <v>2.981E-2</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -1864,8 +1867,8 @@
       <c r="C86">
         <v>0</v>
       </c>
-      <c r="D86">
-        <v>2.4002503657397423E-2</v>
+      <c r="D86" s="8">
+        <v>2.9850000000000002E-2</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -1878,8 +1881,8 @@
       <c r="C87">
         <v>0</v>
       </c>
-      <c r="D87">
-        <v>2.4157804185853005E-2</v>
+      <c r="D87" s="8">
+        <v>2.989E-2</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -1892,8 +1895,8 @@
       <c r="C88">
         <v>0</v>
       </c>
-      <c r="D88">
-        <v>2.4309616945233259E-2</v>
+      <c r="D88" s="8">
+        <v>2.9919999999999999E-2</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -1906,8 +1909,8 @@
       <c r="C89">
         <v>0</v>
       </c>
-      <c r="D89">
-        <v>2.4458054489842951E-2</v>
+      <c r="D89" s="8">
+        <v>2.9960000000000001E-2</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -1920,8 +1923,8 @@
       <c r="C90">
         <v>0</v>
       </c>
-      <c r="D90">
-        <v>2.4603224872740137E-2</v>
+      <c r="D90" s="8">
+        <v>2.9989999999999999E-2</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -1934,8 +1937,8 @@
       <c r="C91">
         <v>0</v>
       </c>
-      <c r="D91">
-        <v>2.4745231844867099E-2</v>
+      <c r="D91" s="8">
+        <v>3.0020000000000002E-2</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -1948,8 +1951,8 @@
       <c r="C92">
         <v>0</v>
       </c>
-      <c r="D92">
-        <v>2.4884175045773116E-2</v>
+      <c r="D92" s="8">
+        <v>3.006E-2</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -1962,8 +1965,8 @@
       <c r="C93">
         <v>0</v>
       </c>
-      <c r="D93">
-        <v>2.5020150186124246E-2</v>
+      <c r="D93" s="8">
+        <v>3.0089999999999999E-2</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -1976,8 +1979,8 @@
       <c r="C94">
         <v>0</v>
       </c>
-      <c r="D94">
-        <v>2.5153249222228835E-2</v>
+      <c r="D94" s="8">
+        <v>3.0120000000000001E-2</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -1990,8 +1993,8 @@
       <c r="C95">
         <v>0</v>
       </c>
-      <c r="D95">
-        <v>2.5283560522819881E-2</v>
+      <c r="D95" s="8">
+        <v>3.015E-2</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -2004,8 +2007,8 @@
       <c r="C96">
         <v>0</v>
       </c>
-      <c r="D96">
-        <v>2.5411169028346281E-2</v>
+      <c r="D96" s="8">
+        <v>3.0179999999999998E-2</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -2018,8 +2021,8 @@
       <c r="C97">
         <v>0</v>
       </c>
-      <c r="D97">
-        <v>2.5536156403038746E-2</v>
+      <c r="D97" s="8">
+        <v>3.0210000000000001E-2</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -2032,8 +2035,8 @@
       <c r="C98">
         <v>0</v>
       </c>
-      <c r="D98">
-        <v>2.5658601180016616E-2</v>
+      <c r="D98" s="8">
+        <v>3.024E-2</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -2046,8 +2049,8 @@
       <c r="C99">
         <v>0</v>
       </c>
-      <c r="D99">
-        <v>2.5778578899704474E-2</v>
+      <c r="D99" s="8">
+        <v>3.0269999999999998E-2</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -2060,8 +2063,8 @@
       <c r="C100">
         <v>0</v>
       </c>
-      <c r="D100">
-        <v>2.5896162241828113E-2</v>
+      <c r="D100" s="8">
+        <v>3.0290000000000001E-2</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -2074,8 +2077,8 @@
       <c r="C101">
         <v>0</v>
       </c>
-      <c r="D101">
-        <v>2.6011421151256098E-2</v>
+      <c r="D101" s="8">
+        <v>3.032E-2</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -2088,8 +2091,8 @@
       <c r="C102">
         <v>0</v>
       </c>
-      <c r="D102">
-        <v>2.6124422957949811E-2</v>
+      <c r="D102" s="8">
+        <v>3.0349999999999999E-2</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -2102,8 +2105,8 @@
       <c r="C103">
         <v>0</v>
       </c>
-      <c r="D103">
-        <v>2.6235232491277127E-2</v>
+      <c r="D103" s="8">
+        <v>3.0370000000000001E-2</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -2116,8 +2119,8 @@
       <c r="C104">
         <v>0</v>
       </c>
-      <c r="D104">
-        <v>2.6343912188943941E-2</v>
+      <c r="D104" s="8">
+        <v>3.04E-2</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -2130,8 +2133,8 @@
       <c r="C105">
         <v>0</v>
       </c>
-      <c r="D105">
-        <v>2.64505222007827E-2</v>
+      <c r="D105" s="8">
+        <v>3.0419999999999999E-2</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -2144,8 +2147,8 @@
       <c r="C106">
         <v>0</v>
       </c>
-      <c r="D106">
-        <v>2.6555120487640194E-2</v>
+      <c r="D106" s="8">
+        <v>3.0450000000000001E-2</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -2158,8 +2161,8 @@
       <c r="C107">
         <v>0</v>
       </c>
-      <c r="D107">
-        <v>2.665776291558819E-2</v>
+      <c r="D107" s="8">
+        <v>3.0470000000000001E-2</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -2172,8 +2175,8 @@
       <c r="C108">
         <v>0</v>
       </c>
-      <c r="D108">
-        <v>2.6758503345678752E-2</v>
+      <c r="D108" s="8">
+        <v>3.0499999999999999E-2</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -2186,8 +2189,8 @@
       <c r="C109">
         <v>0</v>
       </c>
-      <c r="D109">
-        <v>2.6857393719457612E-2</v>
+      <c r="D109" s="8">
+        <v>3.0519999999999999E-2</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -2200,8 +2203,8 @@
       <c r="C110">
         <v>0</v>
       </c>
-      <c r="D110">
-        <v>2.6954484140437218E-2</v>
+      <c r="D110" s="8">
+        <v>3.0540000000000001E-2</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -2214,8 +2217,8 @@
       <c r="C111">
         <v>0</v>
       </c>
-      <c r="D111">
-        <v>2.7049822951725311E-2</v>
+      <c r="D111" s="8">
+        <v>3.056E-2</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -2228,8 +2231,8 @@
       <c r="C112">
         <v>0</v>
       </c>
-      <c r="D112">
-        <v>2.7143456809996191E-2</v>
+      <c r="D112" s="8">
+        <v>3.0589999999999999E-2</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -2242,8 +2245,8 @@
       <c r="C113">
         <v>0</v>
       </c>
-      <c r="D113">
-        <v>2.7235430755983003E-2</v>
+      <c r="D113" s="8">
+        <v>3.0609999999999998E-2</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -2256,8 +2259,8 @@
       <c r="C114">
         <v>0</v>
       </c>
-      <c r="D114">
-        <v>2.7325788281662433E-2</v>
+      <c r="D114" s="8">
+        <v>3.0630000000000001E-2</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -2270,8 +2273,8 @@
       <c r="C115">
         <v>0</v>
       </c>
-      <c r="D115">
-        <v>2.7414571394293707E-2</v>
+      <c r="D115" s="8">
+        <v>3.065E-2</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -2284,8 +2287,8 @@
       <c r="C116">
         <v>0</v>
       </c>
-      <c r="D116">
-        <v>2.7501820677467759E-2</v>
+      <c r="D116" s="8">
+        <v>3.0669999999999999E-2</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -2298,8 +2301,8 @@
       <c r="C117">
         <v>0</v>
       </c>
-      <c r="D117">
-        <v>2.7587575349314886E-2</v>
+      <c r="D117" s="8">
+        <v>3.0689999999999999E-2</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -2312,8 +2315,8 @@
       <c r="C118">
         <v>0</v>
       </c>
-      <c r="D118">
-        <v>2.7671873318010798E-2</v>
+      <c r="D118" s="8">
+        <v>3.0710000000000001E-2</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2326,8 +2329,8 @@
       <c r="C119">
         <v>0</v>
       </c>
-      <c r="D119">
-        <v>2.7754751234716935E-2</v>
+      <c r="D119" s="8">
+        <v>3.073E-2</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -2340,8 +2343,8 @@
       <c r="C120">
         <v>0</v>
       </c>
-      <c r="D120">
-        <v>2.7836244544079847E-2</v>
+      <c r="D120" s="8">
+        <v>3.075E-2</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -2354,8 +2357,8 @@
       <c r="C121">
         <v>0</v>
       </c>
-      <c r="D121">
-        <v>2.7916387532413101E-2</v>
+      <c r="D121" s="8">
+        <v>3.0769999999999999E-2</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -2368,8 +2371,8 @@
       <c r="C122">
         <v>0</v>
       </c>
-      <c r="D122">
-        <v>2.7995213373676275E-2</v>
+      <c r="D122" s="8">
+        <v>3.0790000000000001E-2</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2382,8 +2385,8 @@
       <c r="C123">
         <v>0</v>
       </c>
-      <c r="D123">
-        <v>2.8072754173359415E-2</v>
+      <c r="D123" s="8">
+        <v>3.0800000000000001E-2</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -2396,8 +2399,8 @@
       <c r="C124">
         <v>0</v>
       </c>
-      <c r="D124">
-        <v>2.8149041010377518E-2</v>
+      <c r="D124" s="8">
+        <v>3.082E-2</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -2410,8 +2413,8 @@
       <c r="C125">
         <v>0</v>
       </c>
-      <c r="D125">
-        <v>2.8224103977074533E-2</v>
+      <c r="D125" s="8">
+        <v>3.0839999999999999E-2</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -2424,8 +2427,8 @@
       <c r="C126">
         <v>0</v>
       </c>
-      <c r="D126">
-        <v>2.8297972217427692E-2</v>
+      <c r="D126" s="8">
+        <v>3.0859999999999999E-2</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -2438,8 +2441,8 @@
       <c r="C127">
         <v>0</v>
       </c>
-      <c r="D127">
-        <v>2.8370673963544757E-2</v>
+      <c r="D127" s="8">
+        <v>3.0870000000000002E-2</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -2452,8 +2455,8 @@
       <c r="C128">
         <v>0</v>
       </c>
-      <c r="D128">
-        <v>2.8442236570533463E-2</v>
+      <c r="D128" s="8">
+        <v>3.0890000000000001E-2</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -2466,8 +2469,8 @@
       <c r="C129">
         <v>0</v>
       </c>
-      <c r="D129">
-        <v>2.8512686549828858E-2</v>
+      <c r="D129" s="8">
+        <v>3.091E-2</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -2480,8 +2483,8 @@
       <c r="C130">
         <v>0</v>
       </c>
-      <c r="D130">
-        <v>2.8582049601048487E-2</v>
+      <c r="D130" s="8">
+        <v>3.092E-2</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -2494,8 +2497,8 @@
       <c r="C131">
         <v>0</v>
       </c>
-      <c r="D131">
-        <v>2.8650350642451139E-2</v>
+      <c r="D131" s="8">
+        <v>3.0939999999999999E-2</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -2508,8 +2511,8 @@
       <c r="C132">
         <v>0</v>
       </c>
-      <c r="D132">
-        <v>2.871761384006688E-2</v>
+      <c r="D132" s="8">
+        <v>3.0949999999999998E-2</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -2522,8 +2525,8 @@
       <c r="C133">
         <v>0</v>
       </c>
-      <c r="D133">
-        <v>2.8783862635559432E-2</v>
+      <c r="D133" s="8">
+        <v>3.0970000000000001E-2</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -2536,8 +2539,8 @@
       <c r="C134">
         <v>0</v>
       </c>
-      <c r="D134">
-        <v>2.8849119772888399E-2</v>
+      <c r="D134" s="8">
+        <v>3.0980000000000001E-2</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -2550,8 +2553,8 @@
       <c r="C135">
         <v>0</v>
       </c>
-      <c r="D135">
-        <v>2.8913407323822193E-2</v>
+      <c r="D135" s="8">
+        <v>3.1E-2</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -2564,8 +2567,8 @@
       <c r="C136">
         <v>0</v>
       </c>
-      <c r="D136">
-        <v>2.8976746712363832E-2</v>
+      <c r="D136" s="8">
+        <v>3.1009999999999999E-2</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -2578,8 +2581,8 @@
       <c r="C137">
         <v>0</v>
       </c>
-      <c r="D137">
-        <v>2.9039158738135784E-2</v>
+      <c r="D137" s="8">
+        <v>3.1029999999999999E-2</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -2592,8 +2595,8 @@
       <c r="C138">
         <v>0</v>
       </c>
-      <c r="D138">
-        <v>2.9100663598777388E-2</v>
+      <c r="D138" s="8">
+        <v>3.1040000000000002E-2</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -2606,8 +2609,8 @@
       <c r="C139">
         <v>0</v>
       </c>
-      <c r="D139">
-        <v>2.9161280911400578E-2</v>
+      <c r="D139" s="8">
+        <v>3.1060000000000001E-2</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -2620,8 +2623,8 @@
       <c r="C140">
         <v>0</v>
       </c>
-      <c r="D140">
-        <v>2.9221029733147441E-2</v>
+      <c r="D140" s="8">
+        <v>3.107E-2</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -2634,8 +2637,8 @@
       <c r="C141">
         <v>0</v>
       </c>
-      <c r="D141">
-        <v>2.927992858089401E-2</v>
+      <c r="D141" s="8">
+        <v>3.109E-2</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -2648,8 +2651,8 @@
       <c r="C142">
         <v>0</v>
       </c>
-      <c r="D142">
-        <v>2.9337995450139154E-2</v>
+      <c r="D142" s="8">
+        <v>3.1099999999999999E-2</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -2662,8 +2665,8 @@
       <c r="C143">
         <v>0</v>
       </c>
-      <c r="D143">
-        <v>2.9395247833115423E-2</v>
+      <c r="D143" s="8">
+        <v>3.1109999999999999E-2</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -2676,8 +2679,8 @@
       <c r="C144">
         <v>0</v>
       </c>
-      <c r="D144">
-        <v>2.9451702736162044E-2</v>
+      <c r="D144" s="8">
+        <v>3.1130000000000001E-2</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -2690,8 +2693,8 @@
       <c r="C145">
         <v>0</v>
       </c>
-      <c r="D145">
-        <v>2.9507376696388254E-2</v>
+      <c r="D145" s="8">
+        <v>3.1140000000000001E-2</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -2704,8 +2707,8 @@
       <c r="C146">
         <v>0</v>
       </c>
-      <c r="D146">
-        <v>2.9562285797666732E-2</v>
+      <c r="D146" s="8">
+        <v>3.1150000000000001E-2</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -2718,8 +2721,8 @@
       <c r="C147">
         <v>0</v>
       </c>
-      <c r="D147">
-        <v>2.9616445685981319E-2</v>
+      <c r="D147" s="8">
+        <v>3.116E-2</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -2732,8 +2735,8 @@
       <c r="C148">
         <v>0</v>
       </c>
-      <c r="D148">
-        <v>2.9669871584162344E-2</v>
+      <c r="D148" s="8">
+        <v>3.1179999999999999E-2</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -2746,8 +2749,8 @@
       <c r="C149">
         <v>0</v>
       </c>
-      <c r="D149">
-        <v>2.9722578306037306E-2</v>
+      <c r="D149" s="8">
+        <v>3.1189999999999999E-2</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -2760,8 +2763,8 @@
       <c r="C150">
         <v>0</v>
       </c>
-      <c r="D150">
-        <v>2.9774580270021778E-2</v>
+      <c r="D150" s="8">
+        <v>3.1199999999999999E-2</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -2774,8 +2777,8 @@
       <c r="C151">
         <v>0</v>
       </c>
-      <c r="D151">
-        <v>2.9825891512175629E-2</v>
+      <c r="D151" s="8">
+        <v>3.1210000000000002E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2789,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA0E8BDC-F229-420E-9A56-65EC6A90BF84}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -2806,554 +2809,1754 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>9.2496718772093669E-3</v>
+      <c r="C2" s="8">
+        <v>3.5139999999999998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1.0589694258098003E-2</v>
+      <c r="C3" s="8">
+        <v>3.0349999999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1.1032270549913577E-2</v>
+      <c r="C4" s="8">
+        <v>2.7830000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>1.1044292518813812E-2</v>
+      <c r="C5" s="8">
+        <v>2.6370000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="8">
         <v>1</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6">
-        <v>1.3788334788232146E-2</v>
+      <c r="C6" s="8">
+        <v>2.5489999999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="8">
         <v>1</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>1.6944242364738148E-2</v>
+      <c r="C7" s="8">
+        <v>2.5020000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="8">
         <v>1</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8">
-        <v>1.8429378313447282E-2</v>
+      <c r="C8" s="8">
+        <v>2.477E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="8">
         <v>1</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9">
-        <v>1.8642466810056619E-2</v>
+      <c r="C9" s="8">
+        <v>2.4660000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="8">
         <v>1</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10">
-        <v>2.0102347240970622E-2</v>
+      <c r="C10" s="8">
+        <v>2.4639999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="8">
         <v>1</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11">
-        <v>2.1872288777203999E-2</v>
+      <c r="C11" s="8">
+        <v>2.47E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>0</v>
+      <c r="A12" s="8">
+        <v>1</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
-      <c r="C12">
-        <v>2.2981233811356312E-2</v>
+      <c r="C12" s="8">
+        <v>2.487E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13">
-        <v>2.4615215165166154E-2</v>
+      <c r="C13" s="8">
+        <v>2.487E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>0</v>
+      <c r="A14" s="8">
+        <v>1</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14">
-        <v>2.5867811793301054E-2</v>
+      <c r="C14" s="8">
+        <v>2.4920000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>0</v>
+      <c r="A15" s="8">
+        <v>1</v>
       </c>
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15">
-        <v>2.6940024191389973E-2</v>
+      <c r="C15" s="8">
+        <v>2.4989999999999998E-2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="8">
         <v>1</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
-      <c r="C16">
-        <v>2.7786457864007751E-2</v>
+      <c r="C16" s="8">
+        <v>2.4979999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="8">
         <v>0</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-      <c r="C17">
-        <v>2.7961998837721332E-2</v>
+      <c r="C17" s="8">
+        <v>2.486E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="8">
         <v>0</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-      <c r="C18">
-        <v>2.8432307445889947E-2</v>
+      <c r="C18" s="8">
+        <v>2.4660000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="8">
         <v>0</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-      <c r="C19">
-        <v>2.8665104618739178E-2</v>
+      <c r="C19" s="8">
+        <v>2.4459999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="8">
         <v>0</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-      <c r="C20">
-        <v>2.8956926872526014E-2</v>
+      <c r="C20" s="8">
+        <v>2.427E-2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="8">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-      <c r="C21">
-        <v>2.9492299797021254E-2</v>
+      <c r="C21" s="8">
+        <v>2.4150000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="8">
         <v>0</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-      <c r="C22">
-        <v>3.0425194965994863E-2</v>
+      <c r="C22" s="8">
+        <v>2.409E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="8">
         <v>0</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-      <c r="C23">
-        <v>3.0899262864683863E-2</v>
+      <c r="C23" s="8">
+        <v>2.409E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="8">
         <v>0</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-      <c r="C24">
-        <v>3.1509179791222114E-2</v>
+      <c r="C24" s="8">
+        <v>2.4129999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="8">
         <v>0</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-      <c r="C25">
-        <v>3.2274458320078969E-2</v>
+      <c r="C25" s="8">
+        <v>2.4209999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>0</v>
+      <c r="A26" s="8">
+        <v>1</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-      <c r="C26">
-        <v>3.3004411020988313E-2</v>
+      <c r="C26" s="8">
+        <v>2.4309999999999998E-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="8">
         <v>0</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-      <c r="C27">
-        <v>3.349589889482734E-2</v>
+      <c r="C27" s="8">
+        <v>2.443E-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="8">
         <v>0</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-      <c r="C28">
-        <v>3.3780265686537352E-2</v>
+      <c r="C28" s="8">
+        <v>2.4570000000000002E-2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="8">
         <v>0</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-      <c r="C29">
-        <v>3.4466641415851526E-2</v>
+      <c r="C29" s="8">
+        <v>2.4719999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="8">
         <v>0</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-      <c r="C30">
-        <v>3.4588648213692223E-2</v>
+      <c r="C30" s="8">
+        <v>2.487E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>0</v>
+      <c r="A31" s="8">
+        <v>1</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-      <c r="C31">
-        <v>3.4633928585448177E-2</v>
+      <c r="C31" s="8">
+        <v>2.5020000000000001E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="8">
         <v>0</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-      <c r="C32">
-        <v>3.4923272597156385E-2</v>
+      <c r="C32" s="8">
+        <v>2.5180000000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="8">
         <v>0</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-      <c r="C33">
-        <v>3.541116892193058E-2</v>
+      <c r="C33" s="8">
+        <v>2.5340000000000001E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="8">
         <v>0</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-      <c r="C34">
-        <v>3.5713706153336522E-2</v>
+      <c r="C34" s="8">
+        <v>2.5499999999999998E-2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="8">
         <v>0</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-      <c r="C35">
-        <v>3.6297765136776385E-2</v>
+      <c r="C35" s="8">
+        <v>2.5659999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="8">
         <v>0</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-      <c r="C36">
-        <v>3.6464062868989157E-2</v>
+      <c r="C36" s="8">
+        <v>2.581E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="8">
         <v>0</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-      <c r="C37">
-        <v>3.6835715037200692E-2</v>
+      <c r="C37" s="8">
+        <v>2.596E-2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="8">
         <v>0</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-      <c r="C38">
-        <v>3.7061412798874274E-2</v>
+      <c r="C38" s="8">
+        <v>2.6110000000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="8">
         <v>0</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-      <c r="C39">
-        <v>3.7461684848288324E-2</v>
+      <c r="C39" s="8">
+        <v>2.6259999999999999E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="A40" s="8">
         <v>0</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-      <c r="C40">
-        <v>3.7774971723381533E-2</v>
+      <c r="C40" s="8">
+        <v>2.64E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>0</v>
+      <c r="A41" s="8">
+        <v>1</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-      <c r="C41">
-        <v>3.8056420537358172E-2</v>
+      <c r="C41" s="8">
+        <v>2.6540000000000001E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="A42" s="8">
         <v>0</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-      <c r="C42">
-        <v>3.8489913626744553E-2</v>
+      <c r="C42" s="8">
+        <v>2.6669999999999999E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="A43" s="8">
         <v>0</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-      <c r="C43">
-        <v>3.8828913271326211E-2</v>
+      <c r="C43" s="8">
+        <v>2.6800000000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="A44" s="8">
         <v>0</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-      <c r="C44">
-        <v>3.8915424852211743E-2</v>
+      <c r="C44" s="8">
+        <v>2.6929999999999999E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="A45" s="8">
         <v>0</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-      <c r="C45">
-        <v>3.9224144229902523E-2</v>
+      <c r="C45" s="8">
+        <v>2.7050000000000001E-2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="A46" s="8">
         <v>0</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-      <c r="C46">
-        <v>3.9421649415220895E-2</v>
+      <c r="C46" s="8">
+        <v>2.717E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="A47" s="8">
         <v>0</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-      <c r="C47">
-        <v>3.9495100727106977E-2</v>
+      <c r="C47" s="8">
+        <v>2.7279999999999999E-2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" s="8">
         <v>0</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-      <c r="C48">
-        <v>3.9679731487326481E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="C48" s="8">
+        <v>2.7390000000000001E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
         <v>0</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-      <c r="C49">
-        <v>3.980159479077483E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="C49" s="8">
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
         <v>0</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-      <c r="C50">
-        <v>4.0207915648931766E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>0</v>
+      <c r="C50" s="8">
+        <v>2.76E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>1</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-      <c r="C51">
-        <v>4.0221039434912016E-2</v>
-      </c>
+      <c r="C51" s="8">
+        <v>2.7709999999999999E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>0</v>
+      </c>
+      <c r="B52" s="8">
+        <v>51</v>
+      </c>
+      <c r="C52" s="8">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
+        <v>0</v>
+      </c>
+      <c r="B53" s="8">
+        <v>52</v>
+      </c>
+      <c r="C53" s="8">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>0</v>
+      </c>
+      <c r="B54" s="8">
+        <v>53</v>
+      </c>
+      <c r="C54" s="8">
+        <v>2.7990000000000001E-2</v>
+      </c>
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
+        <v>0</v>
+      </c>
+      <c r="B55" s="8">
+        <v>54</v>
+      </c>
+      <c r="C55" s="8">
+        <v>2.8080000000000001E-2</v>
+      </c>
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>0</v>
+      </c>
+      <c r="B56" s="8">
+        <v>55</v>
+      </c>
+      <c r="C56" s="8">
+        <v>2.8160000000000001E-2</v>
+      </c>
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
+        <v>0</v>
+      </c>
+      <c r="B57" s="8">
+        <v>56</v>
+      </c>
+      <c r="C57" s="8">
+        <v>2.8250000000000001E-2</v>
+      </c>
+      <c r="D57" s="8"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="8">
+        <v>0</v>
+      </c>
+      <c r="B58" s="8">
+        <v>57</v>
+      </c>
+      <c r="C58" s="8">
+        <v>2.8330000000000001E-2</v>
+      </c>
+      <c r="D58" s="8"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="8">
+        <v>0</v>
+      </c>
+      <c r="B59" s="8">
+        <v>58</v>
+      </c>
+      <c r="C59" s="8">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="D59" s="8"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>0</v>
+      </c>
+      <c r="B60" s="8">
+        <v>59</v>
+      </c>
+      <c r="C60" s="8">
+        <v>2.8479999999999998E-2</v>
+      </c>
+      <c r="D60" s="8"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>0</v>
+      </c>
+      <c r="B61" s="8">
+        <v>60</v>
+      </c>
+      <c r="C61" s="8">
+        <v>2.8549999999999999E-2</v>
+      </c>
+      <c r="D61" s="8"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
+        <v>0</v>
+      </c>
+      <c r="B62" s="8">
+        <v>61</v>
+      </c>
+      <c r="C62" s="8">
+        <v>2.862E-2</v>
+      </c>
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
+        <v>0</v>
+      </c>
+      <c r="B63" s="8">
+        <v>62</v>
+      </c>
+      <c r="C63" s="8">
+        <v>2.869E-2</v>
+      </c>
+      <c r="D63" s="8"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="8">
+        <v>0</v>
+      </c>
+      <c r="B64" s="8">
+        <v>63</v>
+      </c>
+      <c r="C64" s="8">
+        <v>2.8760000000000001E-2</v>
+      </c>
+      <c r="D64" s="8"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="8">
+        <v>0</v>
+      </c>
+      <c r="B65" s="8">
+        <v>64</v>
+      </c>
+      <c r="C65" s="8">
+        <v>2.8830000000000001E-2</v>
+      </c>
+      <c r="D65" s="8"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="8">
+        <v>0</v>
+      </c>
+      <c r="B66" s="8">
+        <v>65</v>
+      </c>
+      <c r="C66" s="8">
+        <v>2.8889999999999999E-2</v>
+      </c>
+      <c r="D66" s="8"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="8">
+        <v>0</v>
+      </c>
+      <c r="B67" s="8">
+        <v>66</v>
+      </c>
+      <c r="C67" s="8">
+        <v>2.895E-2</v>
+      </c>
+      <c r="D67" s="8"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="8">
+        <v>0</v>
+      </c>
+      <c r="B68" s="8">
+        <v>67</v>
+      </c>
+      <c r="C68" s="8">
+        <v>2.9010000000000001E-2</v>
+      </c>
+      <c r="D68" s="8"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="8">
+        <v>0</v>
+      </c>
+      <c r="B69" s="8">
+        <v>68</v>
+      </c>
+      <c r="C69" s="8">
+        <v>2.9069999999999999E-2</v>
+      </c>
+      <c r="D69" s="8"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="8">
+        <v>0</v>
+      </c>
+      <c r="B70" s="8">
+        <v>69</v>
+      </c>
+      <c r="C70" s="8">
+        <v>2.912E-2</v>
+      </c>
+      <c r="D70" s="8"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="8">
+        <v>0</v>
+      </c>
+      <c r="B71" s="8">
+        <v>70</v>
+      </c>
+      <c r="C71" s="8">
+        <v>2.9180000000000001E-2</v>
+      </c>
+      <c r="D71" s="8"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="8">
+        <v>0</v>
+      </c>
+      <c r="B72" s="8">
+        <v>71</v>
+      </c>
+      <c r="C72" s="8">
+        <v>2.9229999999999999E-2</v>
+      </c>
+      <c r="D72" s="8"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="8">
+        <v>0</v>
+      </c>
+      <c r="B73" s="8">
+        <v>72</v>
+      </c>
+      <c r="C73" s="8">
+        <v>2.928E-2</v>
+      </c>
+      <c r="D73" s="8"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
+        <v>0</v>
+      </c>
+      <c r="B74" s="8">
+        <v>73</v>
+      </c>
+      <c r="C74" s="8">
+        <v>2.9329999999999998E-2</v>
+      </c>
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="8">
+        <v>0</v>
+      </c>
+      <c r="B75" s="8">
+        <v>74</v>
+      </c>
+      <c r="C75" s="8">
+        <v>2.938E-2</v>
+      </c>
+      <c r="D75" s="8"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="8">
+        <v>0</v>
+      </c>
+      <c r="B76" s="8">
+        <v>75</v>
+      </c>
+      <c r="C76" s="8">
+        <v>2.9430000000000001E-2</v>
+      </c>
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="8">
+        <v>0</v>
+      </c>
+      <c r="B77" s="8">
+        <v>76</v>
+      </c>
+      <c r="C77" s="8">
+        <v>2.9479999999999999E-2</v>
+      </c>
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="8">
+        <v>0</v>
+      </c>
+      <c r="B78" s="8">
+        <v>77</v>
+      </c>
+      <c r="C78" s="8">
+        <v>2.9520000000000001E-2</v>
+      </c>
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="8">
+        <v>0</v>
+      </c>
+      <c r="B79" s="8">
+        <v>78</v>
+      </c>
+      <c r="C79" s="8">
+        <v>2.9569999999999999E-2</v>
+      </c>
+      <c r="D79" s="8"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="8">
+        <v>0</v>
+      </c>
+      <c r="B80" s="8">
+        <v>79</v>
+      </c>
+      <c r="C80" s="8">
+        <v>2.9610000000000001E-2</v>
+      </c>
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="8">
+        <v>0</v>
+      </c>
+      <c r="B81" s="8">
+        <v>80</v>
+      </c>
+      <c r="C81" s="8">
+        <v>2.9649999999999999E-2</v>
+      </c>
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="8">
+        <v>0</v>
+      </c>
+      <c r="B82" s="8">
+        <v>81</v>
+      </c>
+      <c r="C82" s="8">
+        <v>2.9690000000000001E-2</v>
+      </c>
+      <c r="D82" s="8"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="8">
+        <v>0</v>
+      </c>
+      <c r="B83" s="8">
+        <v>82</v>
+      </c>
+      <c r="C83" s="8">
+        <v>2.9729999999999999E-2</v>
+      </c>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="8">
+        <v>0</v>
+      </c>
+      <c r="B84" s="8">
+        <v>83</v>
+      </c>
+      <c r="C84" s="8">
+        <v>2.9770000000000001E-2</v>
+      </c>
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="8">
+        <v>0</v>
+      </c>
+      <c r="B85" s="8">
+        <v>84</v>
+      </c>
+      <c r="C85" s="8">
+        <v>2.981E-2</v>
+      </c>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="8">
+        <v>0</v>
+      </c>
+      <c r="B86" s="8">
+        <v>85</v>
+      </c>
+      <c r="C86" s="8">
+        <v>2.9850000000000002E-2</v>
+      </c>
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="8">
+        <v>0</v>
+      </c>
+      <c r="B87" s="8">
+        <v>86</v>
+      </c>
+      <c r="C87" s="8">
+        <v>2.989E-2</v>
+      </c>
+      <c r="D87" s="8"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="8">
+        <v>0</v>
+      </c>
+      <c r="B88" s="8">
+        <v>87</v>
+      </c>
+      <c r="C88" s="8">
+        <v>2.9919999999999999E-2</v>
+      </c>
+      <c r="D88" s="8"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="8">
+        <v>0</v>
+      </c>
+      <c r="B89" s="8">
+        <v>88</v>
+      </c>
+      <c r="C89" s="8">
+        <v>2.9960000000000001E-2</v>
+      </c>
+      <c r="D89" s="8"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="8">
+        <v>0</v>
+      </c>
+      <c r="B90" s="8">
+        <v>89</v>
+      </c>
+      <c r="C90" s="8">
+        <v>2.9989999999999999E-2</v>
+      </c>
+      <c r="D90" s="8"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="8">
+        <v>0</v>
+      </c>
+      <c r="B91" s="8">
+        <v>90</v>
+      </c>
+      <c r="C91" s="8">
+        <v>3.0020000000000002E-2</v>
+      </c>
+      <c r="D91" s="8"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="8">
+        <v>0</v>
+      </c>
+      <c r="B92" s="8">
+        <v>91</v>
+      </c>
+      <c r="C92" s="8">
+        <v>3.006E-2</v>
+      </c>
+      <c r="D92" s="8"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="8">
+        <v>0</v>
+      </c>
+      <c r="B93" s="8">
+        <v>92</v>
+      </c>
+      <c r="C93" s="8">
+        <v>3.0089999999999999E-2</v>
+      </c>
+      <c r="D93" s="8"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="8">
+        <v>0</v>
+      </c>
+      <c r="B94" s="8">
+        <v>93</v>
+      </c>
+      <c r="C94" s="8">
+        <v>3.0120000000000001E-2</v>
+      </c>
+      <c r="D94" s="8"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="8">
+        <v>0</v>
+      </c>
+      <c r="B95" s="8">
+        <v>94</v>
+      </c>
+      <c r="C95" s="8">
+        <v>3.015E-2</v>
+      </c>
+      <c r="D95" s="8"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="8">
+        <v>0</v>
+      </c>
+      <c r="B96" s="8">
+        <v>95</v>
+      </c>
+      <c r="C96" s="8">
+        <v>3.0179999999999998E-2</v>
+      </c>
+      <c r="D96" s="8"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="8">
+        <v>0</v>
+      </c>
+      <c r="B97" s="8">
+        <v>96</v>
+      </c>
+      <c r="C97" s="8">
+        <v>3.0210000000000001E-2</v>
+      </c>
+      <c r="D97" s="8"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="8">
+        <v>0</v>
+      </c>
+      <c r="B98" s="8">
+        <v>97</v>
+      </c>
+      <c r="C98" s="8">
+        <v>3.024E-2</v>
+      </c>
+      <c r="D98" s="8"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="8">
+        <v>0</v>
+      </c>
+      <c r="B99" s="8">
+        <v>98</v>
+      </c>
+      <c r="C99" s="8">
+        <v>3.0269999999999998E-2</v>
+      </c>
+      <c r="D99" s="8"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="8">
+        <v>0</v>
+      </c>
+      <c r="B100" s="8">
+        <v>99</v>
+      </c>
+      <c r="C100" s="8">
+        <v>3.0290000000000001E-2</v>
+      </c>
+      <c r="D100" s="8"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="8">
+        <v>0</v>
+      </c>
+      <c r="B101" s="8">
+        <v>100</v>
+      </c>
+      <c r="C101" s="8">
+        <v>3.032E-2</v>
+      </c>
+      <c r="D101" s="8"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="8">
+        <v>0</v>
+      </c>
+      <c r="B102" s="8">
+        <v>101</v>
+      </c>
+      <c r="C102" s="8">
+        <v>3.0349999999999999E-2</v>
+      </c>
+      <c r="D102" s="8"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="8">
+        <v>0</v>
+      </c>
+      <c r="B103" s="8">
+        <v>102</v>
+      </c>
+      <c r="C103" s="8">
+        <v>3.0370000000000001E-2</v>
+      </c>
+      <c r="D103" s="8"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="8">
+        <v>0</v>
+      </c>
+      <c r="B104" s="8">
+        <v>103</v>
+      </c>
+      <c r="C104" s="8">
+        <v>3.04E-2</v>
+      </c>
+      <c r="D104" s="8"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="8">
+        <v>0</v>
+      </c>
+      <c r="B105" s="8">
+        <v>104</v>
+      </c>
+      <c r="C105" s="8">
+        <v>3.0419999999999999E-2</v>
+      </c>
+      <c r="D105" s="8"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="8">
+        <v>0</v>
+      </c>
+      <c r="B106" s="8">
+        <v>105</v>
+      </c>
+      <c r="C106" s="8">
+        <v>3.0450000000000001E-2</v>
+      </c>
+      <c r="D106" s="8"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="8">
+        <v>0</v>
+      </c>
+      <c r="B107" s="8">
+        <v>106</v>
+      </c>
+      <c r="C107" s="8">
+        <v>3.0470000000000001E-2</v>
+      </c>
+      <c r="D107" s="8"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="8">
+        <v>0</v>
+      </c>
+      <c r="B108" s="8">
+        <v>107</v>
+      </c>
+      <c r="C108" s="8">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="D108" s="8"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="8">
+        <v>0</v>
+      </c>
+      <c r="B109" s="8">
+        <v>108</v>
+      </c>
+      <c r="C109" s="8">
+        <v>3.0519999999999999E-2</v>
+      </c>
+      <c r="D109" s="8"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="8">
+        <v>0</v>
+      </c>
+      <c r="B110" s="8">
+        <v>109</v>
+      </c>
+      <c r="C110" s="8">
+        <v>3.0540000000000001E-2</v>
+      </c>
+      <c r="D110" s="8"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="8">
+        <v>0</v>
+      </c>
+      <c r="B111" s="8">
+        <v>110</v>
+      </c>
+      <c r="C111" s="8">
+        <v>3.056E-2</v>
+      </c>
+      <c r="D111" s="8"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="8">
+        <v>0</v>
+      </c>
+      <c r="B112" s="8">
+        <v>111</v>
+      </c>
+      <c r="C112" s="8">
+        <v>3.0589999999999999E-2</v>
+      </c>
+      <c r="D112" s="8"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="8">
+        <v>0</v>
+      </c>
+      <c r="B113" s="8">
+        <v>112</v>
+      </c>
+      <c r="C113" s="8">
+        <v>3.0609999999999998E-2</v>
+      </c>
+      <c r="D113" s="8"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="8">
+        <v>0</v>
+      </c>
+      <c r="B114" s="8">
+        <v>113</v>
+      </c>
+      <c r="C114" s="8">
+        <v>3.0630000000000001E-2</v>
+      </c>
+      <c r="D114" s="8"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="8">
+        <v>0</v>
+      </c>
+      <c r="B115" s="8">
+        <v>114</v>
+      </c>
+      <c r="C115" s="8">
+        <v>3.065E-2</v>
+      </c>
+      <c r="D115" s="8"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="8">
+        <v>0</v>
+      </c>
+      <c r="B116" s="8">
+        <v>115</v>
+      </c>
+      <c r="C116" s="8">
+        <v>3.0669999999999999E-2</v>
+      </c>
+      <c r="D116" s="8"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="8">
+        <v>0</v>
+      </c>
+      <c r="B117" s="8">
+        <v>116</v>
+      </c>
+      <c r="C117" s="8">
+        <v>3.0689999999999999E-2</v>
+      </c>
+      <c r="D117" s="8"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="8">
+        <v>0</v>
+      </c>
+      <c r="B118" s="8">
+        <v>117</v>
+      </c>
+      <c r="C118" s="8">
+        <v>3.0710000000000001E-2</v>
+      </c>
+      <c r="D118" s="8"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="8">
+        <v>0</v>
+      </c>
+      <c r="B119" s="8">
+        <v>118</v>
+      </c>
+      <c r="C119" s="8">
+        <v>3.073E-2</v>
+      </c>
+      <c r="D119" s="8"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="8">
+        <v>0</v>
+      </c>
+      <c r="B120" s="8">
+        <v>119</v>
+      </c>
+      <c r="C120" s="8">
+        <v>3.075E-2</v>
+      </c>
+      <c r="D120" s="8"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="8">
+        <v>0</v>
+      </c>
+      <c r="B121" s="8">
+        <v>120</v>
+      </c>
+      <c r="C121" s="8">
+        <v>3.0769999999999999E-2</v>
+      </c>
+      <c r="D121" s="8"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="8">
+        <v>0</v>
+      </c>
+      <c r="B122" s="8">
+        <v>121</v>
+      </c>
+      <c r="C122" s="8">
+        <v>3.0790000000000001E-2</v>
+      </c>
+      <c r="D122" s="8"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="8">
+        <v>0</v>
+      </c>
+      <c r="B123" s="8">
+        <v>122</v>
+      </c>
+      <c r="C123" s="8">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="D123" s="8"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="8">
+        <v>0</v>
+      </c>
+      <c r="B124" s="8">
+        <v>123</v>
+      </c>
+      <c r="C124" s="8">
+        <v>3.082E-2</v>
+      </c>
+      <c r="D124" s="8"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="8">
+        <v>0</v>
+      </c>
+      <c r="B125" s="8">
+        <v>124</v>
+      </c>
+      <c r="C125" s="8">
+        <v>3.0839999999999999E-2</v>
+      </c>
+      <c r="D125" s="8"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="8">
+        <v>0</v>
+      </c>
+      <c r="B126" s="8">
+        <v>125</v>
+      </c>
+      <c r="C126" s="8">
+        <v>3.0859999999999999E-2</v>
+      </c>
+      <c r="D126" s="8"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="8">
+        <v>0</v>
+      </c>
+      <c r="B127" s="8">
+        <v>126</v>
+      </c>
+      <c r="C127" s="8">
+        <v>3.0870000000000002E-2</v>
+      </c>
+      <c r="D127" s="8"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="8">
+        <v>0</v>
+      </c>
+      <c r="B128" s="8">
+        <v>127</v>
+      </c>
+      <c r="C128" s="8">
+        <v>3.0890000000000001E-2</v>
+      </c>
+      <c r="D128" s="8"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="8">
+        <v>0</v>
+      </c>
+      <c r="B129" s="8">
+        <v>128</v>
+      </c>
+      <c r="C129" s="8">
+        <v>3.091E-2</v>
+      </c>
+      <c r="D129" s="8"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="8">
+        <v>0</v>
+      </c>
+      <c r="B130" s="8">
+        <v>129</v>
+      </c>
+      <c r="C130" s="8">
+        <v>3.092E-2</v>
+      </c>
+      <c r="D130" s="8"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="8">
+        <v>0</v>
+      </c>
+      <c r="B131" s="8">
+        <v>130</v>
+      </c>
+      <c r="C131" s="8">
+        <v>3.0939999999999999E-2</v>
+      </c>
+      <c r="D131" s="8"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="8">
+        <v>0</v>
+      </c>
+      <c r="B132" s="8">
+        <v>131</v>
+      </c>
+      <c r="C132" s="8">
+        <v>3.0949999999999998E-2</v>
+      </c>
+      <c r="D132" s="8"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="8">
+        <v>0</v>
+      </c>
+      <c r="B133" s="8">
+        <v>132</v>
+      </c>
+      <c r="C133" s="8">
+        <v>3.0970000000000001E-2</v>
+      </c>
+      <c r="D133" s="8"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="8">
+        <v>0</v>
+      </c>
+      <c r="B134" s="8">
+        <v>133</v>
+      </c>
+      <c r="C134" s="8">
+        <v>3.0980000000000001E-2</v>
+      </c>
+      <c r="D134" s="8"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="8">
+        <v>0</v>
+      </c>
+      <c r="B135" s="8">
+        <v>134</v>
+      </c>
+      <c r="C135" s="8">
+        <v>3.1E-2</v>
+      </c>
+      <c r="D135" s="8"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="8">
+        <v>0</v>
+      </c>
+      <c r="B136" s="8">
+        <v>135</v>
+      </c>
+      <c r="C136" s="8">
+        <v>3.1009999999999999E-2</v>
+      </c>
+      <c r="D136" s="8"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="8">
+        <v>0</v>
+      </c>
+      <c r="B137" s="8">
+        <v>136</v>
+      </c>
+      <c r="C137" s="8">
+        <v>3.1029999999999999E-2</v>
+      </c>
+      <c r="D137" s="8"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="8">
+        <v>0</v>
+      </c>
+      <c r="B138" s="8">
+        <v>137</v>
+      </c>
+      <c r="C138" s="8">
+        <v>3.1040000000000002E-2</v>
+      </c>
+      <c r="D138" s="8"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="8">
+        <v>0</v>
+      </c>
+      <c r="B139" s="8">
+        <v>138</v>
+      </c>
+      <c r="C139" s="8">
+        <v>3.1060000000000001E-2</v>
+      </c>
+      <c r="D139" s="8"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="8">
+        <v>0</v>
+      </c>
+      <c r="B140" s="8">
+        <v>139</v>
+      </c>
+      <c r="C140" s="8">
+        <v>3.107E-2</v>
+      </c>
+      <c r="D140" s="8"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="8">
+        <v>0</v>
+      </c>
+      <c r="B141" s="8">
+        <v>140</v>
+      </c>
+      <c r="C141" s="8">
+        <v>3.109E-2</v>
+      </c>
+      <c r="D141" s="8"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="8">
+        <v>0</v>
+      </c>
+      <c r="B142" s="8">
+        <v>141</v>
+      </c>
+      <c r="C142" s="8">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="D142" s="8"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="8">
+        <v>0</v>
+      </c>
+      <c r="B143" s="8">
+        <v>142</v>
+      </c>
+      <c r="C143" s="8">
+        <v>3.1109999999999999E-2</v>
+      </c>
+      <c r="D143" s="8"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="8">
+        <v>0</v>
+      </c>
+      <c r="B144" s="8">
+        <v>143</v>
+      </c>
+      <c r="C144" s="8">
+        <v>3.1130000000000001E-2</v>
+      </c>
+      <c r="D144" s="8"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="8">
+        <v>0</v>
+      </c>
+      <c r="B145" s="8">
+        <v>144</v>
+      </c>
+      <c r="C145" s="8">
+        <v>3.1140000000000001E-2</v>
+      </c>
+      <c r="D145" s="8"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="8">
+        <v>0</v>
+      </c>
+      <c r="B146" s="8">
+        <v>145</v>
+      </c>
+      <c r="C146" s="8">
+        <v>3.1150000000000001E-2</v>
+      </c>
+      <c r="D146" s="8"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="8">
+        <v>0</v>
+      </c>
+      <c r="B147" s="8">
+        <v>146</v>
+      </c>
+      <c r="C147" s="8">
+        <v>3.116E-2</v>
+      </c>
+      <c r="D147" s="8"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="8">
+        <v>0</v>
+      </c>
+      <c r="B148" s="8">
+        <v>147</v>
+      </c>
+      <c r="C148" s="8">
+        <v>3.1179999999999999E-2</v>
+      </c>
+      <c r="D148" s="8"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="8">
+        <v>0</v>
+      </c>
+      <c r="B149" s="8">
+        <v>148</v>
+      </c>
+      <c r="C149" s="8">
+        <v>3.1189999999999999E-2</v>
+      </c>
+      <c r="D149" s="8"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="8">
+        <v>0</v>
+      </c>
+      <c r="B150" s="8">
+        <v>149</v>
+      </c>
+      <c r="C150" s="8">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="D150" s="8"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="8">
+        <v>0</v>
+      </c>
+      <c r="B151" s="8">
+        <v>150</v>
+      </c>
+      <c r="C151" s="8">
+        <v>3.1210000000000002E-2</v>
+      </c>
+      <c r="D151" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6893,4 +8096,2712 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC8160D-A4B3-4DFE-91B4-C0068E44C09E}">
+  <dimension ref="A1:D151"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8">
+        <v>-4.449999999999843E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>-4.7492877139407863E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
+        <v>-4.8490311393776242E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8">
+        <v>4</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8">
+        <v>-4.6506939059682839E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8">
+        <v>-4.4523045769666592E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <v>-4.1548916903217936E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8">
+        <v>-3.8573434612039215E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8">
+        <v>-3.460578737007669E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <v>-3.0631946140144972E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-2.6651020891858002E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8">
+        <v>-2.3428351222567478E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>-1.8664394833945996E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>13</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <v>-1.5785481548286073E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>-1.2510909281734373E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-9.4192697808626047E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>0</v>
+      </c>
+      <c r="B17" s="8">
+        <v>16</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>-7.7497898425404887E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>0</v>
+      </c>
+      <c r="B18" s="8">
+        <v>17</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-6.276487632096428E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>0</v>
+      </c>
+      <c r="B19" s="8">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-4.9667033020839302E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>0</v>
+      </c>
+      <c r="B20" s="8">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0</v>
+      </c>
+      <c r="D20" s="8">
+        <v>-3.7946454996118373E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>1</v>
+      </c>
+      <c r="B21" s="8">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-2.7396759664655157E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>0</v>
+      </c>
+      <c r="B22" s="8">
+        <v>21</v>
+      </c>
+      <c r="C22" s="8">
+        <v>0</v>
+      </c>
+      <c r="D22" s="8">
+        <v>-1.9306145426889465E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>0</v>
+      </c>
+      <c r="B23" s="8">
+        <v>22</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <v>3.356441626500839E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>0</v>
+      </c>
+      <c r="B24" s="8">
+        <v>23</v>
+      </c>
+      <c r="C24" s="8">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8">
+        <v>3.7305572938839404E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>0</v>
+      </c>
+      <c r="B25" s="8">
+        <v>24</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <v>7.9932639103041936E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>1</v>
+      </c>
+      <c r="B26" s="8">
+        <v>25</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1.2915728598819065E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>0</v>
+      </c>
+      <c r="B27" s="8">
+        <v>26</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1.8331481078603939E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>0</v>
+      </c>
+      <c r="B28" s="8">
+        <v>27</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <v>2.4106989351067032E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>0</v>
+      </c>
+      <c r="B29" s="8">
+        <v>28</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>3.0134986404870556E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>0</v>
+      </c>
+      <c r="B30" s="8">
+        <v>29</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0</v>
+      </c>
+      <c r="D30" s="8">
+        <v>3.6329263050836058E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>1</v>
+      </c>
+      <c r="B31" s="8">
+        <v>30</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="D31" s="8">
+        <v>4.2620572835279091E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>0</v>
+      </c>
+      <c r="B32" s="8">
+        <v>31</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0</v>
+      </c>
+      <c r="D32" s="8">
+        <v>4.895338870999133E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>0</v>
+      </c>
+      <c r="B33" s="8">
+        <v>32</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>5.5283317896184236E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>0</v>
+      </c>
+      <c r="B34" s="8">
+        <v>33</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0</v>
+      </c>
+      <c r="D34" s="8">
+        <v>6.1575029522564773E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>0</v>
+      </c>
+      <c r="B35" s="8">
+        <v>34</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0</v>
+      </c>
+      <c r="D35" s="8">
+        <v>6.7800584737407465E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>0</v>
+      </c>
+      <c r="B36" s="8">
+        <v>35</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0</v>
+      </c>
+      <c r="D36" s="8">
+        <v>7.3938084889249023E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>0</v>
+      </c>
+      <c r="B37" s="8">
+        <v>36</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0</v>
+      </c>
+      <c r="D37" s="8">
+        <v>7.997057265482832E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>0</v>
+      </c>
+      <c r="B38" s="8">
+        <v>37</v>
+      </c>
+      <c r="C38" s="8">
+        <v>0</v>
+      </c>
+      <c r="D38" s="8">
+        <v>8.5885135487726583E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>0</v>
+      </c>
+      <c r="B39" s="8">
+        <v>38</v>
+      </c>
+      <c r="C39" s="8">
+        <v>0</v>
+      </c>
+      <c r="D39" s="8">
+        <v>9.1672171750911691E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>0</v>
+      </c>
+      <c r="B40" s="8">
+        <v>39</v>
+      </c>
+      <c r="C40" s="8">
+        <v>0</v>
+      </c>
+      <c r="D40" s="8">
+        <v>9.7324788296642151E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>1</v>
+      </c>
+      <c r="B41" s="8">
+        <v>40</v>
+      </c>
+      <c r="C41" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="D41" s="8">
+        <v>1.0283830472670896E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>0</v>
+      </c>
+      <c r="B42" s="8">
+        <v>41</v>
+      </c>
+      <c r="C42" s="8">
+        <v>0</v>
+      </c>
+      <c r="D42" s="8">
+        <v>1.0820984458427274E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
+        <v>0</v>
+      </c>
+      <c r="B43" s="8">
+        <v>42</v>
+      </c>
+      <c r="C43" s="8">
+        <v>0</v>
+      </c>
+      <c r="D43" s="8">
+        <v>1.1343799764694351E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="8">
+        <v>0</v>
+      </c>
+      <c r="B44" s="8">
+        <v>43</v>
+      </c>
+      <c r="C44" s="8">
+        <v>0</v>
+      </c>
+      <c r="D44" s="8">
+        <v>1.1852254056962552E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
+        <v>0</v>
+      </c>
+      <c r="B45" s="8">
+        <v>44</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0</v>
+      </c>
+      <c r="D45" s="8">
+        <v>1.234642055588786E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>0</v>
+      </c>
+      <c r="B46" s="8">
+        <v>45</v>
+      </c>
+      <c r="C46" s="8">
+        <v>0</v>
+      </c>
+      <c r="D46" s="8">
+        <v>1.2826448869438511E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>0</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46</v>
+      </c>
+      <c r="C47" s="8">
+        <v>0</v>
+      </c>
+      <c r="D47" s="8">
+        <v>1.3292549105763385E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>0</v>
+      </c>
+      <c r="B48" s="8">
+        <v>47</v>
+      </c>
+      <c r="C48" s="8">
+        <v>0</v>
+      </c>
+      <c r="D48" s="8">
+        <v>1.3744978706791366E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>0</v>
+      </c>
+      <c r="B49" s="8">
+        <v>48</v>
+      </c>
+      <c r="C49" s="8">
+        <v>0</v>
+      </c>
+      <c r="D49" s="8">
+        <v>1.4184031542527009E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>0</v>
+      </c>
+      <c r="B50" s="8">
+        <v>49</v>
+      </c>
+      <c r="C50" s="8">
+        <v>0</v>
+      </c>
+      <c r="D50" s="8">
+        <v>1.4610028886971271E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>1</v>
+      </c>
+      <c r="B51" s="8">
+        <v>50</v>
+      </c>
+      <c r="C51" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="D51" s="8">
+        <v>1.5023311962402364E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>0</v>
+      </c>
+      <c r="B52" s="8">
+        <v>51</v>
+      </c>
+      <c r="C52" s="8">
+        <v>0</v>
+      </c>
+      <c r="D52" s="8">
+        <v>1.542423579245833E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
+        <v>0</v>
+      </c>
+      <c r="B53" s="8">
+        <v>52</v>
+      </c>
+      <c r="C53" s="8">
+        <v>0</v>
+      </c>
+      <c r="D53" s="8">
+        <v>1.581316414844669E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>0</v>
+      </c>
+      <c r="B54" s="8">
+        <v>53</v>
+      </c>
+      <c r="C54" s="8">
+        <v>0</v>
+      </c>
+      <c r="D54" s="8">
+        <v>1.6190465409437804E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
+        <v>0</v>
+      </c>
+      <c r="B55" s="8">
+        <v>54</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0</v>
+      </c>
+      <c r="D55" s="8">
+        <v>1.6556509186476109E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>0</v>
+      </c>
+      <c r="B56" s="8">
+        <v>55</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0</v>
+      </c>
+      <c r="D56" s="8">
+        <v>1.691166358586238E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
+        <v>0</v>
+      </c>
+      <c r="B57" s="8">
+        <v>56</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0</v>
+      </c>
+      <c r="D57" s="8">
+        <v>1.7256293006847168E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="8">
+        <v>0</v>
+      </c>
+      <c r="B58" s="8">
+        <v>57</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0</v>
+      </c>
+      <c r="D58" s="8">
+        <v>1.759075638602825E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="8">
+        <v>0</v>
+      </c>
+      <c r="B59" s="8">
+        <v>58</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0</v>
+      </c>
+      <c r="D59" s="8">
+        <v>1.7915405814849628E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>0</v>
+      </c>
+      <c r="B60" s="8">
+        <v>59</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0</v>
+      </c>
+      <c r="D60" s="8">
+        <v>1.8230585468377525E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>0</v>
+      </c>
+      <c r="B61" s="8">
+        <v>60</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0</v>
+      </c>
+      <c r="D61" s="8">
+        <v>1.8536630793370756E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
+        <v>0</v>
+      </c>
+      <c r="B62" s="8">
+        <v>61</v>
+      </c>
+      <c r="C62" s="8">
+        <v>0</v>
+      </c>
+      <c r="D62" s="8">
+        <v>1.8833867911915103E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
+        <v>0</v>
+      </c>
+      <c r="B63" s="8">
+        <v>62</v>
+      </c>
+      <c r="C63" s="8">
+        <v>0</v>
+      </c>
+      <c r="D63" s="8">
+        <v>1.9122613203806038E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="8">
+        <v>0</v>
+      </c>
+      <c r="B64" s="8">
+        <v>63</v>
+      </c>
+      <c r="C64" s="8">
+        <v>0</v>
+      </c>
+      <c r="D64" s="8">
+        <v>1.9403173036683707E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="8">
+        <v>0</v>
+      </c>
+      <c r="B65" s="8">
+        <v>64</v>
+      </c>
+      <c r="C65" s="8">
+        <v>0</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1.9675843617816824E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="8">
+        <v>0</v>
+      </c>
+      <c r="B66" s="8">
+        <v>65</v>
+      </c>
+      <c r="C66" s="8">
+        <v>0</v>
+      </c>
+      <c r="D66" s="8">
+        <v>1.9940910945556833E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="8">
+        <v>0</v>
+      </c>
+      <c r="B67" s="8">
+        <v>66</v>
+      </c>
+      <c r="C67" s="8">
+        <v>0</v>
+      </c>
+      <c r="D67" s="8">
+        <v>2.019865084195871E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="8">
+        <v>0</v>
+      </c>
+      <c r="B68" s="8">
+        <v>67</v>
+      </c>
+      <c r="C68" s="8">
+        <v>0</v>
+      </c>
+      <c r="D68" s="8">
+        <v>2.0449329051009046E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="8">
+        <v>0</v>
+      </c>
+      <c r="B69" s="8">
+        <v>68</v>
+      </c>
+      <c r="C69" s="8">
+        <v>0</v>
+      </c>
+      <c r="D69" s="8">
+        <v>2.0693201389375693E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="8">
+        <v>0</v>
+      </c>
+      <c r="B70" s="8">
+        <v>69</v>
+      </c>
+      <c r="C70" s="8">
+        <v>0</v>
+      </c>
+      <c r="D70" s="8">
+        <v>2.0930513938697271E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="8">
+        <v>0</v>
+      </c>
+      <c r="B71" s="8">
+        <v>70</v>
+      </c>
+      <c r="C71" s="8">
+        <v>0</v>
+      </c>
+      <c r="D71" s="8">
+        <v>2.1161503270206383E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="8">
+        <v>0</v>
+      </c>
+      <c r="B72" s="8">
+        <v>71</v>
+      </c>
+      <c r="C72" s="8">
+        <v>0</v>
+      </c>
+      <c r="D72" s="8">
+        <v>2.1386396693980902E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="8">
+        <v>0</v>
+      </c>
+      <c r="B73" s="8">
+        <v>72</v>
+      </c>
+      <c r="C73" s="8">
+        <v>0</v>
+      </c>
+      <c r="D73" s="8">
+        <v>2.1605412526390921E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
+        <v>0</v>
+      </c>
+      <c r="B74" s="8">
+        <v>73</v>
+      </c>
+      <c r="C74" s="8">
+        <v>0</v>
+      </c>
+      <c r="D74" s="8">
+        <v>2.1818760370390544E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="8">
+        <v>0</v>
+      </c>
+      <c r="B75" s="8">
+        <v>74</v>
+      </c>
+      <c r="C75" s="8">
+        <v>0</v>
+      </c>
+      <c r="D75" s="8">
+        <v>2.2026641404207181E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="8">
+        <v>0</v>
+      </c>
+      <c r="B76" s="8">
+        <v>75</v>
+      </c>
+      <c r="C76" s="8">
+        <v>0</v>
+      </c>
+      <c r="D76" s="8">
+        <v>2.2229248674763724E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="8">
+        <v>0</v>
+      </c>
+      <c r="B77" s="8">
+        <v>76</v>
+      </c>
+      <c r="C77" s="8">
+        <v>0</v>
+      </c>
+      <c r="D77" s="8">
+        <v>2.2426767392813352E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="8">
+        <v>0</v>
+      </c>
+      <c r="B78" s="8">
+        <v>77</v>
+      </c>
+      <c r="C78" s="8">
+        <v>0</v>
+      </c>
+      <c r="D78" s="8">
+        <v>2.2619375227323602E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="8">
+        <v>0</v>
+      </c>
+      <c r="B79" s="8">
+        <v>78</v>
+      </c>
+      <c r="C79" s="8">
+        <v>0</v>
+      </c>
+      <c r="D79" s="8">
+        <v>2.2807242597112198E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="8">
+        <v>0</v>
+      </c>
+      <c r="B80" s="8">
+        <v>79</v>
+      </c>
+      <c r="C80" s="8">
+        <v>0</v>
+      </c>
+      <c r="D80" s="8">
+        <v>2.2990532958129695E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="8">
+        <v>0</v>
+      </c>
+      <c r="B81" s="8">
+        <v>80</v>
+      </c>
+      <c r="C81" s="8">
+        <v>0</v>
+      </c>
+      <c r="D81" s="8">
+        <v>2.3169403085117946E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="8">
+        <v>0</v>
+      </c>
+      <c r="B82" s="8">
+        <v>81</v>
+      </c>
+      <c r="C82" s="8">
+        <v>0</v>
+      </c>
+      <c r="D82" s="8">
+        <v>2.3344003346649211E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="8">
+        <v>0</v>
+      </c>
+      <c r="B83" s="8">
+        <v>82</v>
+      </c>
+      <c r="C83" s="8">
+        <v>0</v>
+      </c>
+      <c r="D83" s="8">
+        <v>2.3514477972788494E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="8">
+        <v>0</v>
+      </c>
+      <c r="B84" s="8">
+        <v>83</v>
+      </c>
+      <c r="C84" s="8">
+        <v>0</v>
+      </c>
+      <c r="D84" s="8">
+        <v>2.3680965314814229E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="8">
+        <v>0</v>
+      </c>
+      <c r="B85" s="8">
+        <v>84</v>
+      </c>
+      <c r="C85" s="8">
+        <v>0</v>
+      </c>
+      <c r="D85" s="8">
+        <v>2.3843598096600749E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="8">
+        <v>0</v>
+      </c>
+      <c r="B86" s="8">
+        <v>85</v>
+      </c>
+      <c r="C86" s="8">
+        <v>0</v>
+      </c>
+      <c r="D86" s="8">
+        <v>2.4002503657397423E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="8">
+        <v>0</v>
+      </c>
+      <c r="B87" s="8">
+        <v>86</v>
+      </c>
+      <c r="C87" s="8">
+        <v>0</v>
+      </c>
+      <c r="D87" s="8">
+        <v>2.4157804185853005E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="8">
+        <v>0</v>
+      </c>
+      <c r="B88" s="8">
+        <v>87</v>
+      </c>
+      <c r="C88" s="8">
+        <v>0</v>
+      </c>
+      <c r="D88" s="8">
+        <v>2.4309616945233259E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="8">
+        <v>0</v>
+      </c>
+      <c r="B89" s="8">
+        <v>88</v>
+      </c>
+      <c r="C89" s="8">
+        <v>0</v>
+      </c>
+      <c r="D89" s="8">
+        <v>2.4458054489842951E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="8">
+        <v>0</v>
+      </c>
+      <c r="B90" s="8">
+        <v>89</v>
+      </c>
+      <c r="C90" s="8">
+        <v>0</v>
+      </c>
+      <c r="D90" s="8">
+        <v>2.4603224872740137E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="8">
+        <v>0</v>
+      </c>
+      <c r="B91" s="8">
+        <v>90</v>
+      </c>
+      <c r="C91" s="8">
+        <v>0</v>
+      </c>
+      <c r="D91" s="8">
+        <v>2.4745231844867099E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="8">
+        <v>0</v>
+      </c>
+      <c r="B92" s="8">
+        <v>91</v>
+      </c>
+      <c r="C92" s="8">
+        <v>0</v>
+      </c>
+      <c r="D92" s="8">
+        <v>2.4884175045773116E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="8">
+        <v>0</v>
+      </c>
+      <c r="B93" s="8">
+        <v>92</v>
+      </c>
+      <c r="C93" s="8">
+        <v>0</v>
+      </c>
+      <c r="D93" s="8">
+        <v>2.5020150186124246E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="8">
+        <v>0</v>
+      </c>
+      <c r="B94" s="8">
+        <v>93</v>
+      </c>
+      <c r="C94" s="8">
+        <v>0</v>
+      </c>
+      <c r="D94" s="8">
+        <v>2.5153249222228835E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="8">
+        <v>0</v>
+      </c>
+      <c r="B95" s="8">
+        <v>94</v>
+      </c>
+      <c r="C95" s="8">
+        <v>0</v>
+      </c>
+      <c r="D95" s="8">
+        <v>2.5283560522819881E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="8">
+        <v>0</v>
+      </c>
+      <c r="B96" s="8">
+        <v>95</v>
+      </c>
+      <c r="C96" s="8">
+        <v>0</v>
+      </c>
+      <c r="D96" s="8">
+        <v>2.5411169028346281E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="8">
+        <v>0</v>
+      </c>
+      <c r="B97" s="8">
+        <v>96</v>
+      </c>
+      <c r="C97" s="8">
+        <v>0</v>
+      </c>
+      <c r="D97" s="8">
+        <v>2.5536156403038746E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="8">
+        <v>0</v>
+      </c>
+      <c r="B98" s="8">
+        <v>97</v>
+      </c>
+      <c r="C98" s="8">
+        <v>0</v>
+      </c>
+      <c r="D98" s="8">
+        <v>2.5658601180016616E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="8">
+        <v>0</v>
+      </c>
+      <c r="B99" s="8">
+        <v>98</v>
+      </c>
+      <c r="C99" s="8">
+        <v>0</v>
+      </c>
+      <c r="D99" s="8">
+        <v>2.5778578899704474E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="8">
+        <v>0</v>
+      </c>
+      <c r="B100" s="8">
+        <v>99</v>
+      </c>
+      <c r="C100" s="8">
+        <v>0</v>
+      </c>
+      <c r="D100" s="8">
+        <v>2.5896162241828113E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="8">
+        <v>0</v>
+      </c>
+      <c r="B101" s="8">
+        <v>100</v>
+      </c>
+      <c r="C101" s="8">
+        <v>0</v>
+      </c>
+      <c r="D101" s="8">
+        <v>2.6011421151256098E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="8">
+        <v>0</v>
+      </c>
+      <c r="B102" s="8">
+        <v>101</v>
+      </c>
+      <c r="C102" s="8">
+        <v>0</v>
+      </c>
+      <c r="D102" s="8">
+        <v>2.6124422957949811E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="8">
+        <v>0</v>
+      </c>
+      <c r="B103" s="8">
+        <v>102</v>
+      </c>
+      <c r="C103" s="8">
+        <v>0</v>
+      </c>
+      <c r="D103" s="8">
+        <v>2.6235232491277127E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="8">
+        <v>0</v>
+      </c>
+      <c r="B104" s="8">
+        <v>103</v>
+      </c>
+      <c r="C104" s="8">
+        <v>0</v>
+      </c>
+      <c r="D104" s="8">
+        <v>2.6343912188943941E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="8">
+        <v>0</v>
+      </c>
+      <c r="B105" s="8">
+        <v>104</v>
+      </c>
+      <c r="C105" s="8">
+        <v>0</v>
+      </c>
+      <c r="D105" s="8">
+        <v>2.64505222007827E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="8">
+        <v>0</v>
+      </c>
+      <c r="B106" s="8">
+        <v>105</v>
+      </c>
+      <c r="C106" s="8">
+        <v>0</v>
+      </c>
+      <c r="D106" s="8">
+        <v>2.6555120487640194E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="8">
+        <v>0</v>
+      </c>
+      <c r="B107" s="8">
+        <v>106</v>
+      </c>
+      <c r="C107" s="8">
+        <v>0</v>
+      </c>
+      <c r="D107" s="8">
+        <v>2.665776291558819E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="8">
+        <v>0</v>
+      </c>
+      <c r="B108" s="8">
+        <v>107</v>
+      </c>
+      <c r="C108" s="8">
+        <v>0</v>
+      </c>
+      <c r="D108" s="8">
+        <v>2.6758503345678752E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="8">
+        <v>0</v>
+      </c>
+      <c r="B109" s="8">
+        <v>108</v>
+      </c>
+      <c r="C109" s="8">
+        <v>0</v>
+      </c>
+      <c r="D109" s="8">
+        <v>2.6857393719457612E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="8">
+        <v>0</v>
+      </c>
+      <c r="B110" s="8">
+        <v>109</v>
+      </c>
+      <c r="C110" s="8">
+        <v>0</v>
+      </c>
+      <c r="D110" s="8">
+        <v>2.6954484140437218E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="8">
+        <v>0</v>
+      </c>
+      <c r="B111" s="8">
+        <v>110</v>
+      </c>
+      <c r="C111" s="8">
+        <v>0</v>
+      </c>
+      <c r="D111" s="8">
+        <v>2.7049822951725311E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="8">
+        <v>0</v>
+      </c>
+      <c r="B112" s="8">
+        <v>111</v>
+      </c>
+      <c r="C112" s="8">
+        <v>0</v>
+      </c>
+      <c r="D112" s="8">
+        <v>2.7143456809996191E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="8">
+        <v>0</v>
+      </c>
+      <c r="B113" s="8">
+        <v>112</v>
+      </c>
+      <c r="C113" s="8">
+        <v>0</v>
+      </c>
+      <c r="D113" s="8">
+        <v>2.7235430755983003E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="8">
+        <v>0</v>
+      </c>
+      <c r="B114" s="8">
+        <v>113</v>
+      </c>
+      <c r="C114" s="8">
+        <v>0</v>
+      </c>
+      <c r="D114" s="8">
+        <v>2.7325788281662433E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="8">
+        <v>0</v>
+      </c>
+      <c r="B115" s="8">
+        <v>114</v>
+      </c>
+      <c r="C115" s="8">
+        <v>0</v>
+      </c>
+      <c r="D115" s="8">
+        <v>2.7414571394293707E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="8">
+        <v>0</v>
+      </c>
+      <c r="B116" s="8">
+        <v>115</v>
+      </c>
+      <c r="C116" s="8">
+        <v>0</v>
+      </c>
+      <c r="D116" s="8">
+        <v>2.7501820677467759E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="8">
+        <v>0</v>
+      </c>
+      <c r="B117" s="8">
+        <v>116</v>
+      </c>
+      <c r="C117" s="8">
+        <v>0</v>
+      </c>
+      <c r="D117" s="8">
+        <v>2.7587575349314886E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="8">
+        <v>0</v>
+      </c>
+      <c r="B118" s="8">
+        <v>117</v>
+      </c>
+      <c r="C118" s="8">
+        <v>0</v>
+      </c>
+      <c r="D118" s="8">
+        <v>2.7671873318010798E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="8">
+        <v>0</v>
+      </c>
+      <c r="B119" s="8">
+        <v>118</v>
+      </c>
+      <c r="C119" s="8">
+        <v>0</v>
+      </c>
+      <c r="D119" s="8">
+        <v>2.7754751234716935E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="8">
+        <v>0</v>
+      </c>
+      <c r="B120" s="8">
+        <v>119</v>
+      </c>
+      <c r="C120" s="8">
+        <v>0</v>
+      </c>
+      <c r="D120" s="8">
+        <v>2.7836244544079847E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="8">
+        <v>0</v>
+      </c>
+      <c r="B121" s="8">
+        <v>120</v>
+      </c>
+      <c r="C121" s="8">
+        <v>0</v>
+      </c>
+      <c r="D121" s="8">
+        <v>2.7916387532413101E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="8">
+        <v>0</v>
+      </c>
+      <c r="B122" s="8">
+        <v>121</v>
+      </c>
+      <c r="C122" s="8">
+        <v>0</v>
+      </c>
+      <c r="D122" s="8">
+        <v>2.7995213373676275E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="8">
+        <v>0</v>
+      </c>
+      <c r="B123" s="8">
+        <v>122</v>
+      </c>
+      <c r="C123" s="8">
+        <v>0</v>
+      </c>
+      <c r="D123" s="8">
+        <v>2.8072754173359415E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="8">
+        <v>0</v>
+      </c>
+      <c r="B124" s="8">
+        <v>123</v>
+      </c>
+      <c r="C124" s="8">
+        <v>0</v>
+      </c>
+      <c r="D124" s="8">
+        <v>2.8149041010377518E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="8">
+        <v>0</v>
+      </c>
+      <c r="B125" s="8">
+        <v>124</v>
+      </c>
+      <c r="C125" s="8">
+        <v>0</v>
+      </c>
+      <c r="D125" s="8">
+        <v>2.8224103977074533E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="8">
+        <v>0</v>
+      </c>
+      <c r="B126" s="8">
+        <v>125</v>
+      </c>
+      <c r="C126" s="8">
+        <v>0</v>
+      </c>
+      <c r="D126" s="8">
+        <v>2.8297972217427692E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="8">
+        <v>0</v>
+      </c>
+      <c r="B127" s="8">
+        <v>126</v>
+      </c>
+      <c r="C127" s="8">
+        <v>0</v>
+      </c>
+      <c r="D127" s="8">
+        <v>2.8370673963544757E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="8">
+        <v>0</v>
+      </c>
+      <c r="B128" s="8">
+        <v>127</v>
+      </c>
+      <c r="C128" s="8">
+        <v>0</v>
+      </c>
+      <c r="D128" s="8">
+        <v>2.8442236570533463E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="8">
+        <v>0</v>
+      </c>
+      <c r="B129" s="8">
+        <v>128</v>
+      </c>
+      <c r="C129" s="8">
+        <v>0</v>
+      </c>
+      <c r="D129" s="8">
+        <v>2.8512686549828858E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="8">
+        <v>0</v>
+      </c>
+      <c r="B130" s="8">
+        <v>129</v>
+      </c>
+      <c r="C130" s="8">
+        <v>0</v>
+      </c>
+      <c r="D130" s="8">
+        <v>2.8582049601048487E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="8">
+        <v>0</v>
+      </c>
+      <c r="B131" s="8">
+        <v>130</v>
+      </c>
+      <c r="C131" s="8">
+        <v>0</v>
+      </c>
+      <c r="D131" s="8">
+        <v>2.8650350642451139E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="8">
+        <v>0</v>
+      </c>
+      <c r="B132" s="8">
+        <v>131</v>
+      </c>
+      <c r="C132" s="8">
+        <v>0</v>
+      </c>
+      <c r="D132" s="8">
+        <v>2.871761384006688E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="8">
+        <v>0</v>
+      </c>
+      <c r="B133" s="8">
+        <v>132</v>
+      </c>
+      <c r="C133" s="8">
+        <v>0</v>
+      </c>
+      <c r="D133" s="8">
+        <v>2.8783862635559432E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="8">
+        <v>0</v>
+      </c>
+      <c r="B134" s="8">
+        <v>133</v>
+      </c>
+      <c r="C134" s="8">
+        <v>0</v>
+      </c>
+      <c r="D134" s="8">
+        <v>2.8849119772888399E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="8">
+        <v>0</v>
+      </c>
+      <c r="B135" s="8">
+        <v>134</v>
+      </c>
+      <c r="C135" s="8">
+        <v>0</v>
+      </c>
+      <c r="D135" s="8">
+        <v>2.8913407323822193E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="8">
+        <v>0</v>
+      </c>
+      <c r="B136" s="8">
+        <v>135</v>
+      </c>
+      <c r="C136" s="8">
+        <v>0</v>
+      </c>
+      <c r="D136" s="8">
+        <v>2.8976746712363832E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="8">
+        <v>0</v>
+      </c>
+      <c r="B137" s="8">
+        <v>136</v>
+      </c>
+      <c r="C137" s="8">
+        <v>0</v>
+      </c>
+      <c r="D137" s="8">
+        <v>2.9039158738135784E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="8">
+        <v>0</v>
+      </c>
+      <c r="B138" s="8">
+        <v>137</v>
+      </c>
+      <c r="C138" s="8">
+        <v>0</v>
+      </c>
+      <c r="D138" s="8">
+        <v>2.9100663598777388E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="8">
+        <v>0</v>
+      </c>
+      <c r="B139" s="8">
+        <v>138</v>
+      </c>
+      <c r="C139" s="8">
+        <v>0</v>
+      </c>
+      <c r="D139" s="8">
+        <v>2.9161280911400578E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="8">
+        <v>0</v>
+      </c>
+      <c r="B140" s="8">
+        <v>139</v>
+      </c>
+      <c r="C140" s="8">
+        <v>0</v>
+      </c>
+      <c r="D140" s="8">
+        <v>2.9221029733147441E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="8">
+        <v>0</v>
+      </c>
+      <c r="B141" s="8">
+        <v>140</v>
+      </c>
+      <c r="C141" s="8">
+        <v>0</v>
+      </c>
+      <c r="D141" s="8">
+        <v>2.927992858089401E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="8">
+        <v>0</v>
+      </c>
+      <c r="B142" s="8">
+        <v>141</v>
+      </c>
+      <c r="C142" s="8">
+        <v>0</v>
+      </c>
+      <c r="D142" s="8">
+        <v>2.9337995450139154E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="8">
+        <v>0</v>
+      </c>
+      <c r="B143" s="8">
+        <v>142</v>
+      </c>
+      <c r="C143" s="8">
+        <v>0</v>
+      </c>
+      <c r="D143" s="8">
+        <v>2.9395247833115423E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="8">
+        <v>0</v>
+      </c>
+      <c r="B144" s="8">
+        <v>143</v>
+      </c>
+      <c r="C144" s="8">
+        <v>0</v>
+      </c>
+      <c r="D144" s="8">
+        <v>2.9451702736162044E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="8">
+        <v>0</v>
+      </c>
+      <c r="B145" s="8">
+        <v>144</v>
+      </c>
+      <c r="C145" s="8">
+        <v>0</v>
+      </c>
+      <c r="D145" s="8">
+        <v>2.9507376696388254E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="8">
+        <v>0</v>
+      </c>
+      <c r="B146" s="8">
+        <v>145</v>
+      </c>
+      <c r="C146" s="8">
+        <v>0</v>
+      </c>
+      <c r="D146" s="8">
+        <v>2.9562285797666732E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="8">
+        <v>0</v>
+      </c>
+      <c r="B147" s="8">
+        <v>146</v>
+      </c>
+      <c r="C147" s="8">
+        <v>0</v>
+      </c>
+      <c r="D147" s="8">
+        <v>2.9616445685981319E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="8">
+        <v>0</v>
+      </c>
+      <c r="B148" s="8">
+        <v>147</v>
+      </c>
+      <c r="C148" s="8">
+        <v>0</v>
+      </c>
+      <c r="D148" s="8">
+        <v>2.9669871584162344E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="8">
+        <v>0</v>
+      </c>
+      <c r="B149" s="8">
+        <v>148</v>
+      </c>
+      <c r="C149" s="8">
+        <v>0</v>
+      </c>
+      <c r="D149" s="8">
+        <v>2.9722578306037306E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="8">
+        <v>0</v>
+      </c>
+      <c r="B150" s="8">
+        <v>149</v>
+      </c>
+      <c r="C150" s="8">
+        <v>0</v>
+      </c>
+      <c r="D150" s="8">
+        <v>2.9774580270021778E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="8">
+        <v>0</v>
+      </c>
+      <c r="B151" s="8">
+        <v>150</v>
+      </c>
+      <c r="C151" s="8">
+        <v>0</v>
+      </c>
+      <c r="D151" s="8">
+        <v>2.9825891512175629E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE47FA15-E43F-4DFC-8DA2-6C359667E5B8}">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="12" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8">
+        <v>9.2496718772093669E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1.0589694258098003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.1032270549913577E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8">
+        <v>4</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1.1044292518813812E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1.3788334788232146E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.6944242364738148E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.8429378313447282E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.8642466810056619E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.0102347240970622E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2.1872288777203999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>0</v>
+      </c>
+      <c r="B12" s="8">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2.2981233811356312E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2.4615215165166154E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>0</v>
+      </c>
+      <c r="B14" s="8">
+        <v>13</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2.5867811793301054E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>0</v>
+      </c>
+      <c r="B15" s="8">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.6940024191389973E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.7786457864007751E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>0</v>
+      </c>
+      <c r="B17" s="8">
+        <v>16</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.7961998837721332E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>0</v>
+      </c>
+      <c r="B18" s="8">
+        <v>17</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.8432307445889947E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>0</v>
+      </c>
+      <c r="B19" s="8">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2.8665104618739178E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>0</v>
+      </c>
+      <c r="B20" s="8">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2.8956926872526014E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>1</v>
+      </c>
+      <c r="B21" s="8">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.9492299797021254E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>0</v>
+      </c>
+      <c r="B22" s="8">
+        <v>21</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3.0425194965994863E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>0</v>
+      </c>
+      <c r="B23" s="8">
+        <v>22</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3.0899262864683863E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>0</v>
+      </c>
+      <c r="B24" s="8">
+        <v>23</v>
+      </c>
+      <c r="C24" s="8">
+        <v>3.1509179791222114E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>0</v>
+      </c>
+      <c r="B25" s="8">
+        <v>24</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3.2274458320078969E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>0</v>
+      </c>
+      <c r="B26" s="8">
+        <v>25</v>
+      </c>
+      <c r="C26" s="8">
+        <v>3.3004411020988313E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>0</v>
+      </c>
+      <c r="B27" s="8">
+        <v>26</v>
+      </c>
+      <c r="C27" s="8">
+        <v>3.349589889482734E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>0</v>
+      </c>
+      <c r="B28" s="8">
+        <v>27</v>
+      </c>
+      <c r="C28" s="8">
+        <v>3.3780265686537352E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>0</v>
+      </c>
+      <c r="B29" s="8">
+        <v>28</v>
+      </c>
+      <c r="C29" s="8">
+        <v>3.4466641415851526E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>0</v>
+      </c>
+      <c r="B30" s="8">
+        <v>29</v>
+      </c>
+      <c r="C30" s="8">
+        <v>3.4588648213692223E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>0</v>
+      </c>
+      <c r="B31" s="8">
+        <v>30</v>
+      </c>
+      <c r="C31" s="8">
+        <v>3.4633928585448177E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>0</v>
+      </c>
+      <c r="B32" s="8">
+        <v>31</v>
+      </c>
+      <c r="C32" s="8">
+        <v>3.4923272597156385E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>0</v>
+      </c>
+      <c r="B33" s="8">
+        <v>32</v>
+      </c>
+      <c r="C33" s="8">
+        <v>3.541116892193058E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>0</v>
+      </c>
+      <c r="B34" s="8">
+        <v>33</v>
+      </c>
+      <c r="C34" s="8">
+        <v>3.5713706153336522E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>0</v>
+      </c>
+      <c r="B35" s="8">
+        <v>34</v>
+      </c>
+      <c r="C35" s="8">
+        <v>3.6297765136776385E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>0</v>
+      </c>
+      <c r="B36" s="8">
+        <v>35</v>
+      </c>
+      <c r="C36" s="8">
+        <v>3.6464062868989157E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>0</v>
+      </c>
+      <c r="B37" s="8">
+        <v>36</v>
+      </c>
+      <c r="C37" s="8">
+        <v>3.6835715037200692E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>0</v>
+      </c>
+      <c r="B38" s="8">
+        <v>37</v>
+      </c>
+      <c r="C38" s="8">
+        <v>3.7061412798874274E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>0</v>
+      </c>
+      <c r="B39" s="8">
+        <v>38</v>
+      </c>
+      <c r="C39" s="8">
+        <v>3.7461684848288324E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>0</v>
+      </c>
+      <c r="B40" s="8">
+        <v>39</v>
+      </c>
+      <c r="C40" s="8">
+        <v>3.7774971723381533E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>0</v>
+      </c>
+      <c r="B41" s="8">
+        <v>40</v>
+      </c>
+      <c r="C41" s="8">
+        <v>3.8056420537358172E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>0</v>
+      </c>
+      <c r="B42" s="8">
+        <v>41</v>
+      </c>
+      <c r="C42" s="8">
+        <v>3.8489913626744553E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
+        <v>0</v>
+      </c>
+      <c r="B43" s="8">
+        <v>42</v>
+      </c>
+      <c r="C43" s="8">
+        <v>3.8828913271326211E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="8">
+        <v>0</v>
+      </c>
+      <c r="B44" s="8">
+        <v>43</v>
+      </c>
+      <c r="C44" s="8">
+        <v>3.8915424852211743E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
+        <v>0</v>
+      </c>
+      <c r="B45" s="8">
+        <v>44</v>
+      </c>
+      <c r="C45" s="8">
+        <v>3.9224144229902523E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>0</v>
+      </c>
+      <c r="B46" s="8">
+        <v>45</v>
+      </c>
+      <c r="C46" s="8">
+        <v>3.9421649415220895E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>0</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46</v>
+      </c>
+      <c r="C47" s="8">
+        <v>3.9495100727106977E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>0</v>
+      </c>
+      <c r="B48" s="8">
+        <v>47</v>
+      </c>
+      <c r="C48" s="8">
+        <v>3.9679731487326481E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>0</v>
+      </c>
+      <c r="B49" s="8">
+        <v>48</v>
+      </c>
+      <c r="C49" s="8">
+        <v>3.980159479077483E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>0</v>
+      </c>
+      <c r="B50" s="8">
+        <v>49</v>
+      </c>
+      <c r="C50" s="8">
+        <v>4.0207915648931766E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>0</v>
+      </c>
+      <c r="B51" s="8">
+        <v>50</v>
+      </c>
+      <c r="C51" s="8">
+        <v>4.0221039434912016E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5F7ECE-E0A8-4E67-81F8-91C13364AC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8E182A-8F93-4563-A0BE-F5AE984E7498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,8 +226,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -308,12 +309,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -325,21 +329,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="6">
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{3A7A80FC-34FF-4A37-BE34-F1FEA3B360CA}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{FC3F0600-1ADB-4CCA-919E-B4E70E91DB81}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{2351E727-7914-4128-83BF-CE6273F2D9EE}"/>
     <cellStyle name="Percent 2" xfId="2" xr:uid="{8E3C7290-F3EB-4F4F-810B-1E8706B54683}"/>
+    <cellStyle name="Percent 3" xfId="4" xr:uid="{DE1BBB0C-560F-4DE4-9E6F-6FB9EE7FD47F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -369,9 +370,9 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3">
         <row r="6">
           <cell r="A6">
@@ -387,8 +388,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -691,7 +692,7 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>3.5139999999999998E-2</v>
       </c>
     </row>
@@ -705,7 +706,7 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>3.0349999999999999E-2</v>
       </c>
     </row>
@@ -719,7 +720,7 @@
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>2.7830000000000001E-2</v>
       </c>
     </row>
@@ -733,7 +734,7 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>2.6370000000000001E-2</v>
       </c>
     </row>
@@ -747,7 +748,7 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>2.5489999999999999E-2</v>
       </c>
     </row>
@@ -761,7 +762,7 @@
       <c r="C7">
         <v>0</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>2.5020000000000001E-2</v>
       </c>
     </row>
@@ -775,7 +776,7 @@
       <c r="C8">
         <v>0</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>2.477E-2</v>
       </c>
     </row>
@@ -789,7 +790,7 @@
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>2.4660000000000001E-2</v>
       </c>
     </row>
@@ -803,7 +804,7 @@
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>2.4639999999999999E-2</v>
       </c>
     </row>
@@ -817,7 +818,7 @@
       <c r="C11">
         <v>0</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>2.47E-2</v>
       </c>
     </row>
@@ -831,7 +832,7 @@
       <c r="C12">
         <v>0</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>2.487E-2</v>
       </c>
     </row>
@@ -845,7 +846,7 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>2.487E-2</v>
       </c>
     </row>
@@ -859,7 +860,7 @@
       <c r="C14">
         <v>0</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>2.4920000000000001E-2</v>
       </c>
     </row>
@@ -873,7 +874,7 @@
       <c r="C15">
         <v>0</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>2.4989999999999998E-2</v>
       </c>
     </row>
@@ -887,7 +888,7 @@
       <c r="C16">
         <v>0</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>2.4979999999999999E-2</v>
       </c>
     </row>
@@ -901,7 +902,7 @@
       <c r="C17">
         <v>0</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>2.486E-2</v>
       </c>
     </row>
@@ -915,7 +916,7 @@
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>2.4660000000000001E-2</v>
       </c>
     </row>
@@ -929,7 +930,7 @@
       <c r="C19">
         <v>0</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="6">
         <v>2.4459999999999999E-2</v>
       </c>
     </row>
@@ -943,7 +944,7 @@
       <c r="C20">
         <v>0</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="6">
         <v>2.427E-2</v>
       </c>
     </row>
@@ -957,7 +958,7 @@
       <c r="C21">
         <v>0.33</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="6">
         <v>2.4150000000000001E-2</v>
       </c>
     </row>
@@ -971,7 +972,7 @@
       <c r="C22">
         <v>0</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>2.409E-2</v>
       </c>
     </row>
@@ -985,7 +986,7 @@
       <c r="C23">
         <v>0</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="6">
         <v>2.409E-2</v>
       </c>
     </row>
@@ -999,7 +1000,7 @@
       <c r="C24">
         <v>0</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="6">
         <v>2.4129999999999999E-2</v>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
       <c r="C25">
         <v>0</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>2.4209999999999999E-2</v>
       </c>
     </row>
@@ -1027,7 +1028,7 @@
       <c r="C26">
         <v>0.12</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <v>2.4309999999999998E-2</v>
       </c>
     </row>
@@ -1041,7 +1042,7 @@
       <c r="C27">
         <v>0</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="6">
         <v>2.443E-2</v>
       </c>
     </row>
@@ -1055,7 +1056,7 @@
       <c r="C28">
         <v>0</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="6">
         <v>2.4570000000000002E-2</v>
       </c>
     </row>
@@ -1069,7 +1070,7 @@
       <c r="C29">
         <v>0</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>2.4719999999999999E-2</v>
       </c>
     </row>
@@ -1083,7 +1084,7 @@
       <c r="C30">
         <v>0</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="6">
         <v>2.487E-2</v>
       </c>
     </row>
@@ -1097,7 +1098,7 @@
       <c r="C31">
         <v>0.48</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="6">
         <v>2.5020000000000001E-2</v>
       </c>
     </row>
@@ -1111,7 +1112,7 @@
       <c r="C32">
         <v>0</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="6">
         <v>2.5180000000000001E-2</v>
       </c>
     </row>
@@ -1125,7 +1126,7 @@
       <c r="C33">
         <v>0</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="6">
         <v>2.5340000000000001E-2</v>
       </c>
     </row>
@@ -1139,7 +1140,7 @@
       <c r="C34">
         <v>0</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="6">
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
@@ -1153,7 +1154,7 @@
       <c r="C35">
         <v>0</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="6">
         <v>2.5659999999999999E-2</v>
       </c>
     </row>
@@ -1167,7 +1168,7 @@
       <c r="C36">
         <v>0</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="6">
         <v>2.581E-2</v>
       </c>
     </row>
@@ -1181,7 +1182,7 @@
       <c r="C37">
         <v>0</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="6">
         <v>2.596E-2</v>
       </c>
     </row>
@@ -1195,7 +1196,7 @@
       <c r="C38">
         <v>0</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="6">
         <v>2.6110000000000001E-2</v>
       </c>
     </row>
@@ -1209,7 +1210,7 @@
       <c r="C39">
         <v>0</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="6">
         <v>2.6259999999999999E-2</v>
       </c>
     </row>
@@ -1223,7 +1224,7 @@
       <c r="C40">
         <v>0</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="6">
         <v>2.64E-2</v>
       </c>
     </row>
@@ -1237,7 +1238,7 @@
       <c r="C41">
         <v>0.04</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="6">
         <v>2.6540000000000001E-2</v>
       </c>
     </row>
@@ -1251,7 +1252,7 @@
       <c r="C42">
         <v>0</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="6">
         <v>2.6669999999999999E-2</v>
       </c>
     </row>
@@ -1265,7 +1266,7 @@
       <c r="C43">
         <v>0</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="6">
         <v>2.6800000000000001E-2</v>
       </c>
     </row>
@@ -1279,7 +1280,7 @@
       <c r="C44">
         <v>0</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="6">
         <v>2.6929999999999999E-2</v>
       </c>
     </row>
@@ -1293,7 +1294,7 @@
       <c r="C45">
         <v>0</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="6">
         <v>2.7050000000000001E-2</v>
       </c>
     </row>
@@ -1307,7 +1308,7 @@
       <c r="C46">
         <v>0</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="6">
         <v>2.717E-2</v>
       </c>
     </row>
@@ -1321,7 +1322,7 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="6">
         <v>2.7279999999999999E-2</v>
       </c>
     </row>
@@ -1335,7 +1336,7 @@
       <c r="C48">
         <v>0</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="6">
         <v>2.7390000000000001E-2</v>
       </c>
     </row>
@@ -1349,7 +1350,7 @@
       <c r="C49">
         <v>0</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="6">
         <v>2.75E-2</v>
       </c>
     </row>
@@ -1363,7 +1364,7 @@
       <c r="C50">
         <v>0</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="6">
         <v>2.76E-2</v>
       </c>
     </row>
@@ -1377,7 +1378,7 @@
       <c r="C51">
         <v>0.03</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="6">
         <v>2.7709999999999999E-2</v>
       </c>
     </row>
@@ -1391,7 +1392,7 @@
       <c r="C52">
         <v>0</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="6">
         <v>2.7799999999999998E-2</v>
       </c>
     </row>
@@ -1405,7 +1406,7 @@
       <c r="C53">
         <v>0</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="6">
         <v>2.7900000000000001E-2</v>
       </c>
     </row>
@@ -1419,7 +1420,7 @@
       <c r="C54">
         <v>0</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="6">
         <v>2.7990000000000001E-2</v>
       </c>
     </row>
@@ -1433,7 +1434,7 @@
       <c r="C55">
         <v>0</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="6">
         <v>2.8080000000000001E-2</v>
       </c>
     </row>
@@ -1447,7 +1448,7 @@
       <c r="C56">
         <v>0</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="6">
         <v>2.8160000000000001E-2</v>
       </c>
     </row>
@@ -1461,7 +1462,7 @@
       <c r="C57">
         <v>0</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="6">
         <v>2.8250000000000001E-2</v>
       </c>
     </row>
@@ -1475,7 +1476,7 @@
       <c r="C58">
         <v>0</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="6">
         <v>2.8330000000000001E-2</v>
       </c>
     </row>
@@ -1489,7 +1490,7 @@
       <c r="C59">
         <v>0</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="6">
         <v>2.8400000000000002E-2</v>
       </c>
     </row>
@@ -1503,7 +1504,7 @@
       <c r="C60">
         <v>0</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="6">
         <v>2.8479999999999998E-2</v>
       </c>
     </row>
@@ -1517,7 +1518,7 @@
       <c r="C61">
         <v>0</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="6">
         <v>2.8549999999999999E-2</v>
       </c>
     </row>
@@ -1531,7 +1532,7 @@
       <c r="C62">
         <v>0</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="6">
         <v>2.862E-2</v>
       </c>
     </row>
@@ -1545,7 +1546,7 @@
       <c r="C63">
         <v>0</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="6">
         <v>2.869E-2</v>
       </c>
     </row>
@@ -1559,7 +1560,7 @@
       <c r="C64">
         <v>0</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="6">
         <v>2.8760000000000001E-2</v>
       </c>
     </row>
@@ -1573,7 +1574,7 @@
       <c r="C65">
         <v>0</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="6">
         <v>2.8830000000000001E-2</v>
       </c>
     </row>
@@ -1587,7 +1588,7 @@
       <c r="C66">
         <v>0</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="6">
         <v>2.8889999999999999E-2</v>
       </c>
     </row>
@@ -1601,7 +1602,7 @@
       <c r="C67">
         <v>0</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="6">
         <v>2.895E-2</v>
       </c>
     </row>
@@ -1615,7 +1616,7 @@
       <c r="C68">
         <v>0</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="6">
         <v>2.9010000000000001E-2</v>
       </c>
     </row>
@@ -1629,7 +1630,7 @@
       <c r="C69">
         <v>0</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="6">
         <v>2.9069999999999999E-2</v>
       </c>
     </row>
@@ -1643,7 +1644,7 @@
       <c r="C70">
         <v>0</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="6">
         <v>2.912E-2</v>
       </c>
     </row>
@@ -1657,7 +1658,7 @@
       <c r="C71">
         <v>0</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="6">
         <v>2.9180000000000001E-2</v>
       </c>
     </row>
@@ -1671,7 +1672,7 @@
       <c r="C72">
         <v>0</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="6">
         <v>2.9229999999999999E-2</v>
       </c>
     </row>
@@ -1685,7 +1686,7 @@
       <c r="C73">
         <v>0</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="6">
         <v>2.928E-2</v>
       </c>
     </row>
@@ -1699,7 +1700,7 @@
       <c r="C74">
         <v>0</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="6">
         <v>2.9329999999999998E-2</v>
       </c>
     </row>
@@ -1713,7 +1714,7 @@
       <c r="C75">
         <v>0</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="6">
         <v>2.938E-2</v>
       </c>
     </row>
@@ -1727,7 +1728,7 @@
       <c r="C76">
         <v>0</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="6">
         <v>2.9430000000000001E-2</v>
       </c>
     </row>
@@ -1741,7 +1742,7 @@
       <c r="C77">
         <v>0</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="6">
         <v>2.9479999999999999E-2</v>
       </c>
     </row>
@@ -1755,7 +1756,7 @@
       <c r="C78">
         <v>0</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="6">
         <v>2.9520000000000001E-2</v>
       </c>
     </row>
@@ -1769,7 +1770,7 @@
       <c r="C79">
         <v>0</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="6">
         <v>2.9569999999999999E-2</v>
       </c>
     </row>
@@ -1783,7 +1784,7 @@
       <c r="C80">
         <v>0</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="6">
         <v>2.9610000000000001E-2</v>
       </c>
     </row>
@@ -1797,7 +1798,7 @@
       <c r="C81">
         <v>0</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="6">
         <v>2.9649999999999999E-2</v>
       </c>
     </row>
@@ -1811,7 +1812,7 @@
       <c r="C82">
         <v>0</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="6">
         <v>2.9690000000000001E-2</v>
       </c>
     </row>
@@ -1825,7 +1826,7 @@
       <c r="C83">
         <v>0</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="6">
         <v>2.9729999999999999E-2</v>
       </c>
     </row>
@@ -1839,7 +1840,7 @@
       <c r="C84">
         <v>0</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="6">
         <v>2.9770000000000001E-2</v>
       </c>
     </row>
@@ -1853,7 +1854,7 @@
       <c r="C85">
         <v>0</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="6">
         <v>2.981E-2</v>
       </c>
     </row>
@@ -1867,7 +1868,7 @@
       <c r="C86">
         <v>0</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="6">
         <v>2.9850000000000002E-2</v>
       </c>
     </row>
@@ -1881,7 +1882,7 @@
       <c r="C87">
         <v>0</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="6">
         <v>2.989E-2</v>
       </c>
     </row>
@@ -1895,7 +1896,7 @@
       <c r="C88">
         <v>0</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="6">
         <v>2.9919999999999999E-2</v>
       </c>
     </row>
@@ -1909,7 +1910,7 @@
       <c r="C89">
         <v>0</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="6">
         <v>2.9960000000000001E-2</v>
       </c>
     </row>
@@ -1923,7 +1924,7 @@
       <c r="C90">
         <v>0</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="6">
         <v>2.9989999999999999E-2</v>
       </c>
     </row>
@@ -1937,7 +1938,7 @@
       <c r="C91">
         <v>0</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="6">
         <v>3.0020000000000002E-2</v>
       </c>
     </row>
@@ -1951,7 +1952,7 @@
       <c r="C92">
         <v>0</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="6">
         <v>3.006E-2</v>
       </c>
     </row>
@@ -1965,7 +1966,7 @@
       <c r="C93">
         <v>0</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="6">
         <v>3.0089999999999999E-2</v>
       </c>
     </row>
@@ -1979,7 +1980,7 @@
       <c r="C94">
         <v>0</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="6">
         <v>3.0120000000000001E-2</v>
       </c>
     </row>
@@ -1993,7 +1994,7 @@
       <c r="C95">
         <v>0</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="6">
         <v>3.015E-2</v>
       </c>
     </row>
@@ -2007,7 +2008,7 @@
       <c r="C96">
         <v>0</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="6">
         <v>3.0179999999999998E-2</v>
       </c>
     </row>
@@ -2021,7 +2022,7 @@
       <c r="C97">
         <v>0</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="6">
         <v>3.0210000000000001E-2</v>
       </c>
     </row>
@@ -2035,7 +2036,7 @@
       <c r="C98">
         <v>0</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="6">
         <v>3.024E-2</v>
       </c>
     </row>
@@ -2049,7 +2050,7 @@
       <c r="C99">
         <v>0</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="6">
         <v>3.0269999999999998E-2</v>
       </c>
     </row>
@@ -2063,7 +2064,7 @@
       <c r="C100">
         <v>0</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="6">
         <v>3.0290000000000001E-2</v>
       </c>
     </row>
@@ -2077,7 +2078,7 @@
       <c r="C101">
         <v>0</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="6">
         <v>3.032E-2</v>
       </c>
     </row>
@@ -2091,7 +2092,7 @@
       <c r="C102">
         <v>0</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="6">
         <v>3.0349999999999999E-2</v>
       </c>
     </row>
@@ -2105,7 +2106,7 @@
       <c r="C103">
         <v>0</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="6">
         <v>3.0370000000000001E-2</v>
       </c>
     </row>
@@ -2119,7 +2120,7 @@
       <c r="C104">
         <v>0</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D104" s="6">
         <v>3.04E-2</v>
       </c>
     </row>
@@ -2133,7 +2134,7 @@
       <c r="C105">
         <v>0</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="6">
         <v>3.0419999999999999E-2</v>
       </c>
     </row>
@@ -2147,7 +2148,7 @@
       <c r="C106">
         <v>0</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="6">
         <v>3.0450000000000001E-2</v>
       </c>
     </row>
@@ -2161,7 +2162,7 @@
       <c r="C107">
         <v>0</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="6">
         <v>3.0470000000000001E-2</v>
       </c>
     </row>
@@ -2175,7 +2176,7 @@
       <c r="C108">
         <v>0</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="6">
         <v>3.0499999999999999E-2</v>
       </c>
     </row>
@@ -2189,7 +2190,7 @@
       <c r="C109">
         <v>0</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="6">
         <v>3.0519999999999999E-2</v>
       </c>
     </row>
@@ -2203,7 +2204,7 @@
       <c r="C110">
         <v>0</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="6">
         <v>3.0540000000000001E-2</v>
       </c>
     </row>
@@ -2217,7 +2218,7 @@
       <c r="C111">
         <v>0</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="6">
         <v>3.056E-2</v>
       </c>
     </row>
@@ -2231,7 +2232,7 @@
       <c r="C112">
         <v>0</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="6">
         <v>3.0589999999999999E-2</v>
       </c>
     </row>
@@ -2245,7 +2246,7 @@
       <c r="C113">
         <v>0</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="6">
         <v>3.0609999999999998E-2</v>
       </c>
     </row>
@@ -2259,7 +2260,7 @@
       <c r="C114">
         <v>0</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="6">
         <v>3.0630000000000001E-2</v>
       </c>
     </row>
@@ -2273,7 +2274,7 @@
       <c r="C115">
         <v>0</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="6">
         <v>3.065E-2</v>
       </c>
     </row>
@@ -2287,7 +2288,7 @@
       <c r="C116">
         <v>0</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D116" s="6">
         <v>3.0669999999999999E-2</v>
       </c>
     </row>
@@ -2301,7 +2302,7 @@
       <c r="C117">
         <v>0</v>
       </c>
-      <c r="D117" s="8">
+      <c r="D117" s="6">
         <v>3.0689999999999999E-2</v>
       </c>
     </row>
@@ -2315,7 +2316,7 @@
       <c r="C118">
         <v>0</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D118" s="6">
         <v>3.0710000000000001E-2</v>
       </c>
     </row>
@@ -2329,7 +2330,7 @@
       <c r="C119">
         <v>0</v>
       </c>
-      <c r="D119" s="8">
+      <c r="D119" s="6">
         <v>3.073E-2</v>
       </c>
     </row>
@@ -2343,7 +2344,7 @@
       <c r="C120">
         <v>0</v>
       </c>
-      <c r="D120" s="8">
+      <c r="D120" s="6">
         <v>3.075E-2</v>
       </c>
     </row>
@@ -2357,7 +2358,7 @@
       <c r="C121">
         <v>0</v>
       </c>
-      <c r="D121" s="8">
+      <c r="D121" s="6">
         <v>3.0769999999999999E-2</v>
       </c>
     </row>
@@ -2371,7 +2372,7 @@
       <c r="C122">
         <v>0</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D122" s="6">
         <v>3.0790000000000001E-2</v>
       </c>
     </row>
@@ -2385,7 +2386,7 @@
       <c r="C123">
         <v>0</v>
       </c>
-      <c r="D123" s="8">
+      <c r="D123" s="6">
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
@@ -2399,7 +2400,7 @@
       <c r="C124">
         <v>0</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D124" s="6">
         <v>3.082E-2</v>
       </c>
     </row>
@@ -2413,7 +2414,7 @@
       <c r="C125">
         <v>0</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="6">
         <v>3.0839999999999999E-2</v>
       </c>
     </row>
@@ -2427,7 +2428,7 @@
       <c r="C126">
         <v>0</v>
       </c>
-      <c r="D126" s="8">
+      <c r="D126" s="6">
         <v>3.0859999999999999E-2</v>
       </c>
     </row>
@@ -2441,7 +2442,7 @@
       <c r="C127">
         <v>0</v>
       </c>
-      <c r="D127" s="8">
+      <c r="D127" s="6">
         <v>3.0870000000000002E-2</v>
       </c>
     </row>
@@ -2455,7 +2456,7 @@
       <c r="C128">
         <v>0</v>
       </c>
-      <c r="D128" s="8">
+      <c r="D128" s="6">
         <v>3.0890000000000001E-2</v>
       </c>
     </row>
@@ -2469,7 +2470,7 @@
       <c r="C129">
         <v>0</v>
       </c>
-      <c r="D129" s="8">
+      <c r="D129" s="6">
         <v>3.091E-2</v>
       </c>
     </row>
@@ -2483,7 +2484,7 @@
       <c r="C130">
         <v>0</v>
       </c>
-      <c r="D130" s="8">
+      <c r="D130" s="6">
         <v>3.092E-2</v>
       </c>
     </row>
@@ -2497,7 +2498,7 @@
       <c r="C131">
         <v>0</v>
       </c>
-      <c r="D131" s="8">
+      <c r="D131" s="6">
         <v>3.0939999999999999E-2</v>
       </c>
     </row>
@@ -2511,7 +2512,7 @@
       <c r="C132">
         <v>0</v>
       </c>
-      <c r="D132" s="8">
+      <c r="D132" s="6">
         <v>3.0949999999999998E-2</v>
       </c>
     </row>
@@ -2525,7 +2526,7 @@
       <c r="C133">
         <v>0</v>
       </c>
-      <c r="D133" s="8">
+      <c r="D133" s="6">
         <v>3.0970000000000001E-2</v>
       </c>
     </row>
@@ -2539,7 +2540,7 @@
       <c r="C134">
         <v>0</v>
       </c>
-      <c r="D134" s="8">
+      <c r="D134" s="6">
         <v>3.0980000000000001E-2</v>
       </c>
     </row>
@@ -2553,7 +2554,7 @@
       <c r="C135">
         <v>0</v>
       </c>
-      <c r="D135" s="8">
+      <c r="D135" s="6">
         <v>3.1E-2</v>
       </c>
     </row>
@@ -2567,7 +2568,7 @@
       <c r="C136">
         <v>0</v>
       </c>
-      <c r="D136" s="8">
+      <c r="D136" s="6">
         <v>3.1009999999999999E-2</v>
       </c>
     </row>
@@ -2581,7 +2582,7 @@
       <c r="C137">
         <v>0</v>
       </c>
-      <c r="D137" s="8">
+      <c r="D137" s="6">
         <v>3.1029999999999999E-2</v>
       </c>
     </row>
@@ -2595,7 +2596,7 @@
       <c r="C138">
         <v>0</v>
       </c>
-      <c r="D138" s="8">
+      <c r="D138" s="6">
         <v>3.1040000000000002E-2</v>
       </c>
     </row>
@@ -2609,7 +2610,7 @@
       <c r="C139">
         <v>0</v>
       </c>
-      <c r="D139" s="8">
+      <c r="D139" s="6">
         <v>3.1060000000000001E-2</v>
       </c>
     </row>
@@ -2623,7 +2624,7 @@
       <c r="C140">
         <v>0</v>
       </c>
-      <c r="D140" s="8">
+      <c r="D140" s="6">
         <v>3.107E-2</v>
       </c>
     </row>
@@ -2637,7 +2638,7 @@
       <c r="C141">
         <v>0</v>
       </c>
-      <c r="D141" s="8">
+      <c r="D141" s="6">
         <v>3.109E-2</v>
       </c>
     </row>
@@ -2651,7 +2652,7 @@
       <c r="C142">
         <v>0</v>
       </c>
-      <c r="D142" s="8">
+      <c r="D142" s="6">
         <v>3.1099999999999999E-2</v>
       </c>
     </row>
@@ -2665,7 +2666,7 @@
       <c r="C143">
         <v>0</v>
       </c>
-      <c r="D143" s="8">
+      <c r="D143" s="6">
         <v>3.1109999999999999E-2</v>
       </c>
     </row>
@@ -2679,7 +2680,7 @@
       <c r="C144">
         <v>0</v>
       </c>
-      <c r="D144" s="8">
+      <c r="D144" s="6">
         <v>3.1130000000000001E-2</v>
       </c>
     </row>
@@ -2693,7 +2694,7 @@
       <c r="C145">
         <v>0</v>
       </c>
-      <c r="D145" s="8">
+      <c r="D145" s="6">
         <v>3.1140000000000001E-2</v>
       </c>
     </row>
@@ -2707,7 +2708,7 @@
       <c r="C146">
         <v>0</v>
       </c>
-      <c r="D146" s="8">
+      <c r="D146" s="6">
         <v>3.1150000000000001E-2</v>
       </c>
     </row>
@@ -2721,7 +2722,7 @@
       <c r="C147">
         <v>0</v>
       </c>
-      <c r="D147" s="8">
+      <c r="D147" s="6">
         <v>3.116E-2</v>
       </c>
     </row>
@@ -2735,7 +2736,7 @@
       <c r="C148">
         <v>0</v>
       </c>
-      <c r="D148" s="8">
+      <c r="D148" s="6">
         <v>3.1179999999999999E-2</v>
       </c>
     </row>
@@ -2749,7 +2750,7 @@
       <c r="C149">
         <v>0</v>
       </c>
-      <c r="D149" s="8">
+      <c r="D149" s="6">
         <v>3.1189999999999999E-2</v>
       </c>
     </row>
@@ -2763,7 +2764,7 @@
       <c r="C150">
         <v>0</v>
       </c>
-      <c r="D150" s="8">
+      <c r="D150" s="6">
         <v>3.1199999999999999E-2</v>
       </c>
     </row>
@@ -2777,7 +2778,7 @@
       <c r="C151">
         <v>0</v>
       </c>
-      <c r="D151" s="8">
+      <c r="D151" s="6">
         <v>3.1210000000000002E-2</v>
       </c>
     </row>
@@ -2809,1754 +2810,1754 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>3.5139999999999998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>3.0349999999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>2.7830000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>2.6370000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <v>1</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>2.5489999999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <v>1</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>2.5020000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>1</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>2.477E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>1</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>2.4660000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>1</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>2.4639999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <v>2.47E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>1</v>
+      <c r="A12" s="6">
+        <v>0</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <v>2.487E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>1</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="6">
         <v>2.487E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>1</v>
+      <c r="A14" s="6">
+        <v>0</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>2.4920000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>1</v>
+      <c r="A15" s="6">
+        <v>0</v>
       </c>
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <v>2.4989999999999998E-2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>1</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>2.4979999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="6">
         <v>0</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>2.486E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+      <c r="A18" s="6">
         <v>0</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
         <v>2.4660000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="A19" s="6">
         <v>0</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="6">
         <v>2.4459999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+      <c r="A20" s="6">
         <v>0</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="6">
         <v>2.427E-2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <v>1</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="6">
         <v>2.4150000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+      <c r="A22" s="6">
         <v>0</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>2.409E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+      <c r="A23" s="6">
         <v>0</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="6">
         <v>2.409E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+      <c r="A24" s="6">
         <v>0</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="6">
         <v>2.4129999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+      <c r="A25" s="6">
         <v>0</v>
       </c>
       <c r="B25">
         <v>24</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>2.4209999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>1</v>
+      <c r="A26" s="6">
+        <v>0</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <v>2.4309999999999998E-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+      <c r="A27" s="6">
         <v>0</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="6">
         <v>2.443E-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
+      <c r="A28" s="6">
         <v>0</v>
       </c>
       <c r="B28">
         <v>27</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="6">
         <v>2.4570000000000002E-2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+      <c r="A29" s="6">
         <v>0</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="6">
         <v>2.4719999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
+      <c r="A30" s="6">
         <v>0</v>
       </c>
       <c r="B30">
         <v>29</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="6">
         <v>2.487E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
-        <v>1</v>
+      <c r="A31" s="6">
+        <v>0</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="6">
         <v>2.5020000000000001E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
+      <c r="A32" s="6">
         <v>0</v>
       </c>
       <c r="B32">
         <v>31</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="6">
         <v>2.5180000000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
+      <c r="A33" s="6">
         <v>0</v>
       </c>
       <c r="B33">
         <v>32</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="6">
         <v>2.5340000000000001E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
+      <c r="A34" s="6">
         <v>0</v>
       </c>
       <c r="B34">
         <v>33</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="6">
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
+      <c r="A35" s="6">
         <v>0</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="6">
         <v>2.5659999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
+      <c r="A36" s="6">
         <v>0</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="6">
         <v>2.581E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
+      <c r="A37" s="6">
         <v>0</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="6">
         <v>2.596E-2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
+      <c r="A38" s="6">
         <v>0</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="6">
         <v>2.6110000000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
+      <c r="A39" s="6">
         <v>0</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="6">
         <v>2.6259999999999999E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="8">
+      <c r="A40" s="6">
         <v>0</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="6">
         <v>2.64E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="8">
-        <v>1</v>
+      <c r="A41" s="6">
+        <v>0</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="6">
         <v>2.6540000000000001E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="8">
+      <c r="A42" s="6">
         <v>0</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="6">
         <v>2.6669999999999999E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
+      <c r="A43" s="6">
         <v>0</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="6">
         <v>2.6800000000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
+      <c r="A44" s="6">
         <v>0</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="6">
         <v>2.6929999999999999E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
+      <c r="A45" s="6">
         <v>0</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="6">
         <v>2.7050000000000001E-2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="8">
+      <c r="A46" s="6">
         <v>0</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="6">
         <v>2.717E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="8">
+      <c r="A47" s="6">
         <v>0</v>
       </c>
       <c r="B47">
         <v>46</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="6">
         <v>2.7279999999999999E-2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="8">
+      <c r="A48" s="6">
         <v>0</v>
       </c>
       <c r="B48">
         <v>47</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="6">
         <v>2.7390000000000001E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
+      <c r="A49" s="6">
         <v>0</v>
       </c>
       <c r="B49">
         <v>48</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="6">
         <v>2.75E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="8">
+      <c r="A50" s="6">
         <v>0</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="6">
         <v>2.76E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
-        <v>1</v>
+      <c r="A51" s="6">
+        <v>0</v>
       </c>
       <c r="B51">
         <v>50</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="6">
         <v>2.7709999999999999E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="8">
-        <v>0</v>
-      </c>
-      <c r="B52" s="8">
+      <c r="A52" s="6">
+        <v>0</v>
+      </c>
+      <c r="B52" s="6">
         <v>51</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="6">
         <v>2.7799999999999998E-2</v>
       </c>
-      <c r="D52" s="8"/>
+      <c r="D52" s="6"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
-        <v>0</v>
-      </c>
-      <c r="B53" s="8">
+      <c r="A53" s="6">
+        <v>0</v>
+      </c>
+      <c r="B53" s="6">
         <v>52</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="6">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="D53" s="8"/>
+      <c r="D53" s="6"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="8">
-        <v>0</v>
-      </c>
-      <c r="B54" s="8">
+      <c r="A54" s="6">
+        <v>0</v>
+      </c>
+      <c r="B54" s="6">
         <v>53</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="6">
         <v>2.7990000000000001E-2</v>
       </c>
-      <c r="D54" s="8"/>
+      <c r="D54" s="6"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="8">
-        <v>0</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="6">
+        <v>0</v>
+      </c>
+      <c r="B55" s="6">
         <v>54</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="6">
         <v>2.8080000000000001E-2</v>
       </c>
-      <c r="D55" s="8"/>
+      <c r="D55" s="6"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="8">
-        <v>0</v>
-      </c>
-      <c r="B56" s="8">
+      <c r="A56" s="6">
+        <v>0</v>
+      </c>
+      <c r="B56" s="6">
         <v>55</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="6">
         <v>2.8160000000000001E-2</v>
       </c>
-      <c r="D56" s="8"/>
+      <c r="D56" s="6"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="8">
-        <v>0</v>
-      </c>
-      <c r="B57" s="8">
+      <c r="A57" s="6">
+        <v>0</v>
+      </c>
+      <c r="B57" s="6">
         <v>56</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="6">
         <v>2.8250000000000001E-2</v>
       </c>
-      <c r="D57" s="8"/>
+      <c r="D57" s="6"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="8">
-        <v>0</v>
-      </c>
-      <c r="B58" s="8">
+      <c r="A58" s="6">
+        <v>0</v>
+      </c>
+      <c r="B58" s="6">
         <v>57</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="6">
         <v>2.8330000000000001E-2</v>
       </c>
-      <c r="D58" s="8"/>
+      <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="8">
-        <v>0</v>
-      </c>
-      <c r="B59" s="8">
+      <c r="A59" s="6">
+        <v>0</v>
+      </c>
+      <c r="B59" s="6">
         <v>58</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="6">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="D59" s="8"/>
+      <c r="D59" s="6"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="8">
-        <v>0</v>
-      </c>
-      <c r="B60" s="8">
+      <c r="A60" s="6">
+        <v>0</v>
+      </c>
+      <c r="B60" s="6">
         <v>59</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="6">
         <v>2.8479999999999998E-2</v>
       </c>
-      <c r="D60" s="8"/>
+      <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="8">
-        <v>0</v>
-      </c>
-      <c r="B61" s="8">
+      <c r="A61" s="6">
+        <v>0</v>
+      </c>
+      <c r="B61" s="6">
         <v>60</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="6">
         <v>2.8549999999999999E-2</v>
       </c>
-      <c r="D61" s="8"/>
+      <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="8">
-        <v>0</v>
-      </c>
-      <c r="B62" s="8">
+      <c r="A62" s="6">
+        <v>0</v>
+      </c>
+      <c r="B62" s="6">
         <v>61</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="6">
         <v>2.862E-2</v>
       </c>
-      <c r="D62" s="8"/>
+      <c r="D62" s="6"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="8">
-        <v>0</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="6">
+        <v>0</v>
+      </c>
+      <c r="B63" s="6">
         <v>62</v>
       </c>
-      <c r="C63" s="8">
+      <c r="C63" s="6">
         <v>2.869E-2</v>
       </c>
-      <c r="D63" s="8"/>
+      <c r="D63" s="6"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="8">
-        <v>0</v>
-      </c>
-      <c r="B64" s="8">
+      <c r="A64" s="6">
+        <v>0</v>
+      </c>
+      <c r="B64" s="6">
         <v>63</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="6">
         <v>2.8760000000000001E-2</v>
       </c>
-      <c r="D64" s="8"/>
+      <c r="D64" s="6"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="8">
-        <v>0</v>
-      </c>
-      <c r="B65" s="8">
+      <c r="A65" s="6">
+        <v>0</v>
+      </c>
+      <c r="B65" s="6">
         <v>64</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="6">
         <v>2.8830000000000001E-2</v>
       </c>
-      <c r="D65" s="8"/>
+      <c r="D65" s="6"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="8">
-        <v>0</v>
-      </c>
-      <c r="B66" s="8">
+      <c r="A66" s="6">
+        <v>0</v>
+      </c>
+      <c r="B66" s="6">
         <v>65</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="6">
         <v>2.8889999999999999E-2</v>
       </c>
-      <c r="D66" s="8"/>
+      <c r="D66" s="6"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="8">
-        <v>0</v>
-      </c>
-      <c r="B67" s="8">
+      <c r="A67" s="6">
+        <v>0</v>
+      </c>
+      <c r="B67" s="6">
         <v>66</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="6">
         <v>2.895E-2</v>
       </c>
-      <c r="D67" s="8"/>
+      <c r="D67" s="6"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="8">
-        <v>0</v>
-      </c>
-      <c r="B68" s="8">
+      <c r="A68" s="6">
+        <v>0</v>
+      </c>
+      <c r="B68" s="6">
         <v>67</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="6">
         <v>2.9010000000000001E-2</v>
       </c>
-      <c r="D68" s="8"/>
+      <c r="D68" s="6"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="8">
-        <v>0</v>
-      </c>
-      <c r="B69" s="8">
+      <c r="A69" s="6">
+        <v>0</v>
+      </c>
+      <c r="B69" s="6">
         <v>68</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="6">
         <v>2.9069999999999999E-2</v>
       </c>
-      <c r="D69" s="8"/>
+      <c r="D69" s="6"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="8">
-        <v>0</v>
-      </c>
-      <c r="B70" s="8">
+      <c r="A70" s="6">
+        <v>0</v>
+      </c>
+      <c r="B70" s="6">
         <v>69</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="6">
         <v>2.912E-2</v>
       </c>
-      <c r="D70" s="8"/>
+      <c r="D70" s="6"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="8">
-        <v>0</v>
-      </c>
-      <c r="B71" s="8">
+      <c r="A71" s="6">
+        <v>0</v>
+      </c>
+      <c r="B71" s="6">
         <v>70</v>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="6">
         <v>2.9180000000000001E-2</v>
       </c>
-      <c r="D71" s="8"/>
+      <c r="D71" s="6"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="8">
-        <v>0</v>
-      </c>
-      <c r="B72" s="8">
+      <c r="A72" s="6">
+        <v>0</v>
+      </c>
+      <c r="B72" s="6">
         <v>71</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="6">
         <v>2.9229999999999999E-2</v>
       </c>
-      <c r="D72" s="8"/>
+      <c r="D72" s="6"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="8">
-        <v>0</v>
-      </c>
-      <c r="B73" s="8">
+      <c r="A73" s="6">
+        <v>0</v>
+      </c>
+      <c r="B73" s="6">
         <v>72</v>
       </c>
-      <c r="C73" s="8">
+      <c r="C73" s="6">
         <v>2.928E-2</v>
       </c>
-      <c r="D73" s="8"/>
+      <c r="D73" s="6"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="8">
-        <v>0</v>
-      </c>
-      <c r="B74" s="8">
+      <c r="A74" s="6">
+        <v>0</v>
+      </c>
+      <c r="B74" s="6">
         <v>73</v>
       </c>
-      <c r="C74" s="8">
+      <c r="C74" s="6">
         <v>2.9329999999999998E-2</v>
       </c>
-      <c r="D74" s="8"/>
+      <c r="D74" s="6"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="8">
-        <v>0</v>
-      </c>
-      <c r="B75" s="8">
+      <c r="A75" s="6">
+        <v>0</v>
+      </c>
+      <c r="B75" s="6">
         <v>74</v>
       </c>
-      <c r="C75" s="8">
+      <c r="C75" s="6">
         <v>2.938E-2</v>
       </c>
-      <c r="D75" s="8"/>
+      <c r="D75" s="6"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="8">
-        <v>0</v>
-      </c>
-      <c r="B76" s="8">
+      <c r="A76" s="6">
+        <v>0</v>
+      </c>
+      <c r="B76" s="6">
         <v>75</v>
       </c>
-      <c r="C76" s="8">
+      <c r="C76" s="6">
         <v>2.9430000000000001E-2</v>
       </c>
-      <c r="D76" s="8"/>
+      <c r="D76" s="6"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="8">
-        <v>0</v>
-      </c>
-      <c r="B77" s="8">
+      <c r="A77" s="6">
+        <v>0</v>
+      </c>
+      <c r="B77" s="6">
         <v>76</v>
       </c>
-      <c r="C77" s="8">
+      <c r="C77" s="6">
         <v>2.9479999999999999E-2</v>
       </c>
-      <c r="D77" s="8"/>
+      <c r="D77" s="6"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="8">
-        <v>0</v>
-      </c>
-      <c r="B78" s="8">
+      <c r="A78" s="6">
+        <v>0</v>
+      </c>
+      <c r="B78" s="6">
         <v>77</v>
       </c>
-      <c r="C78" s="8">
+      <c r="C78" s="6">
         <v>2.9520000000000001E-2</v>
       </c>
-      <c r="D78" s="8"/>
+      <c r="D78" s="6"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="8">
-        <v>0</v>
-      </c>
-      <c r="B79" s="8">
+      <c r="A79" s="6">
+        <v>0</v>
+      </c>
+      <c r="B79" s="6">
         <v>78</v>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="6">
         <v>2.9569999999999999E-2</v>
       </c>
-      <c r="D79" s="8"/>
+      <c r="D79" s="6"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="8">
-        <v>0</v>
-      </c>
-      <c r="B80" s="8">
+      <c r="A80" s="6">
+        <v>0</v>
+      </c>
+      <c r="B80" s="6">
         <v>79</v>
       </c>
-      <c r="C80" s="8">
+      <c r="C80" s="6">
         <v>2.9610000000000001E-2</v>
       </c>
-      <c r="D80" s="8"/>
+      <c r="D80" s="6"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="8">
-        <v>0</v>
-      </c>
-      <c r="B81" s="8">
+      <c r="A81" s="6">
+        <v>0</v>
+      </c>
+      <c r="B81" s="6">
         <v>80</v>
       </c>
-      <c r="C81" s="8">
+      <c r="C81" s="6">
         <v>2.9649999999999999E-2</v>
       </c>
-      <c r="D81" s="8"/>
+      <c r="D81" s="6"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="8">
-        <v>0</v>
-      </c>
-      <c r="B82" s="8">
+      <c r="A82" s="6">
+        <v>0</v>
+      </c>
+      <c r="B82" s="6">
         <v>81</v>
       </c>
-      <c r="C82" s="8">
+      <c r="C82" s="6">
         <v>2.9690000000000001E-2</v>
       </c>
-      <c r="D82" s="8"/>
+      <c r="D82" s="6"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="8">
-        <v>0</v>
-      </c>
-      <c r="B83" s="8">
+      <c r="A83" s="6">
+        <v>0</v>
+      </c>
+      <c r="B83" s="6">
         <v>82</v>
       </c>
-      <c r="C83" s="8">
+      <c r="C83" s="6">
         <v>2.9729999999999999E-2</v>
       </c>
-      <c r="D83" s="8"/>
+      <c r="D83" s="6"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="8">
-        <v>0</v>
-      </c>
-      <c r="B84" s="8">
+      <c r="A84" s="6">
+        <v>0</v>
+      </c>
+      <c r="B84" s="6">
         <v>83</v>
       </c>
-      <c r="C84" s="8">
+      <c r="C84" s="6">
         <v>2.9770000000000001E-2</v>
       </c>
-      <c r="D84" s="8"/>
+      <c r="D84" s="6"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="8">
-        <v>0</v>
-      </c>
-      <c r="B85" s="8">
+      <c r="A85" s="6">
+        <v>0</v>
+      </c>
+      <c r="B85" s="6">
         <v>84</v>
       </c>
-      <c r="C85" s="8">
+      <c r="C85" s="6">
         <v>2.981E-2</v>
       </c>
-      <c r="D85" s="8"/>
+      <c r="D85" s="6"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="8">
-        <v>0</v>
-      </c>
-      <c r="B86" s="8">
+      <c r="A86" s="6">
+        <v>0</v>
+      </c>
+      <c r="B86" s="6">
         <v>85</v>
       </c>
-      <c r="C86" s="8">
+      <c r="C86" s="6">
         <v>2.9850000000000002E-2</v>
       </c>
-      <c r="D86" s="8"/>
+      <c r="D86" s="6"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="8">
-        <v>0</v>
-      </c>
-      <c r="B87" s="8">
+      <c r="A87" s="6">
+        <v>0</v>
+      </c>
+      <c r="B87" s="6">
         <v>86</v>
       </c>
-      <c r="C87" s="8">
+      <c r="C87" s="6">
         <v>2.989E-2</v>
       </c>
-      <c r="D87" s="8"/>
+      <c r="D87" s="6"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="8">
-        <v>0</v>
-      </c>
-      <c r="B88" s="8">
+      <c r="A88" s="6">
+        <v>0</v>
+      </c>
+      <c r="B88" s="6">
         <v>87</v>
       </c>
-      <c r="C88" s="8">
+      <c r="C88" s="6">
         <v>2.9919999999999999E-2</v>
       </c>
-      <c r="D88" s="8"/>
+      <c r="D88" s="6"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="8">
-        <v>0</v>
-      </c>
-      <c r="B89" s="8">
+      <c r="A89" s="6">
+        <v>0</v>
+      </c>
+      <c r="B89" s="6">
         <v>88</v>
       </c>
-      <c r="C89" s="8">
+      <c r="C89" s="6">
         <v>2.9960000000000001E-2</v>
       </c>
-      <c r="D89" s="8"/>
+      <c r="D89" s="6"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="8">
-        <v>0</v>
-      </c>
-      <c r="B90" s="8">
+      <c r="A90" s="6">
+        <v>0</v>
+      </c>
+      <c r="B90" s="6">
         <v>89</v>
       </c>
-      <c r="C90" s="8">
+      <c r="C90" s="6">
         <v>2.9989999999999999E-2</v>
       </c>
-      <c r="D90" s="8"/>
+      <c r="D90" s="6"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="8">
-        <v>0</v>
-      </c>
-      <c r="B91" s="8">
+      <c r="A91" s="6">
+        <v>0</v>
+      </c>
+      <c r="B91" s="6">
         <v>90</v>
       </c>
-      <c r="C91" s="8">
+      <c r="C91" s="6">
         <v>3.0020000000000002E-2</v>
       </c>
-      <c r="D91" s="8"/>
+      <c r="D91" s="6"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="8">
-        <v>0</v>
-      </c>
-      <c r="B92" s="8">
+      <c r="A92" s="6">
+        <v>0</v>
+      </c>
+      <c r="B92" s="6">
         <v>91</v>
       </c>
-      <c r="C92" s="8">
+      <c r="C92" s="6">
         <v>3.006E-2</v>
       </c>
-      <c r="D92" s="8"/>
+      <c r="D92" s="6"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="8">
-        <v>0</v>
-      </c>
-      <c r="B93" s="8">
+      <c r="A93" s="6">
+        <v>0</v>
+      </c>
+      <c r="B93" s="6">
         <v>92</v>
       </c>
-      <c r="C93" s="8">
+      <c r="C93" s="6">
         <v>3.0089999999999999E-2</v>
       </c>
-      <c r="D93" s="8"/>
+      <c r="D93" s="6"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="8">
-        <v>0</v>
-      </c>
-      <c r="B94" s="8">
+      <c r="A94" s="6">
+        <v>0</v>
+      </c>
+      <c r="B94" s="6">
         <v>93</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="6">
         <v>3.0120000000000001E-2</v>
       </c>
-      <c r="D94" s="8"/>
+      <c r="D94" s="6"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="8">
-        <v>0</v>
-      </c>
-      <c r="B95" s="8">
+      <c r="A95" s="6">
+        <v>0</v>
+      </c>
+      <c r="B95" s="6">
         <v>94</v>
       </c>
-      <c r="C95" s="8">
+      <c r="C95" s="6">
         <v>3.015E-2</v>
       </c>
-      <c r="D95" s="8"/>
+      <c r="D95" s="6"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="8">
-        <v>0</v>
-      </c>
-      <c r="B96" s="8">
+      <c r="A96" s="6">
+        <v>0</v>
+      </c>
+      <c r="B96" s="6">
         <v>95</v>
       </c>
-      <c r="C96" s="8">
+      <c r="C96" s="6">
         <v>3.0179999999999998E-2</v>
       </c>
-      <c r="D96" s="8"/>
+      <c r="D96" s="6"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="8">
-        <v>0</v>
-      </c>
-      <c r="B97" s="8">
+      <c r="A97" s="6">
+        <v>0</v>
+      </c>
+      <c r="B97" s="6">
         <v>96</v>
       </c>
-      <c r="C97" s="8">
+      <c r="C97" s="6">
         <v>3.0210000000000001E-2</v>
       </c>
-      <c r="D97" s="8"/>
+      <c r="D97" s="6"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="8">
-        <v>0</v>
-      </c>
-      <c r="B98" s="8">
+      <c r="A98" s="6">
+        <v>0</v>
+      </c>
+      <c r="B98" s="6">
         <v>97</v>
       </c>
-      <c r="C98" s="8">
+      <c r="C98" s="6">
         <v>3.024E-2</v>
       </c>
-      <c r="D98" s="8"/>
+      <c r="D98" s="6"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="8">
-        <v>0</v>
-      </c>
-      <c r="B99" s="8">
+      <c r="A99" s="6">
+        <v>0</v>
+      </c>
+      <c r="B99" s="6">
         <v>98</v>
       </c>
-      <c r="C99" s="8">
+      <c r="C99" s="6">
         <v>3.0269999999999998E-2</v>
       </c>
-      <c r="D99" s="8"/>
+      <c r="D99" s="6"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="8">
-        <v>0</v>
-      </c>
-      <c r="B100" s="8">
+      <c r="A100" s="6">
+        <v>0</v>
+      </c>
+      <c r="B100" s="6">
         <v>99</v>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="6">
         <v>3.0290000000000001E-2</v>
       </c>
-      <c r="D100" s="8"/>
+      <c r="D100" s="6"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="8">
-        <v>0</v>
-      </c>
-      <c r="B101" s="8">
+      <c r="A101" s="6">
+        <v>0</v>
+      </c>
+      <c r="B101" s="6">
         <v>100</v>
       </c>
-      <c r="C101" s="8">
+      <c r="C101" s="6">
         <v>3.032E-2</v>
       </c>
-      <c r="D101" s="8"/>
+      <c r="D101" s="6"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="8">
-        <v>0</v>
-      </c>
-      <c r="B102" s="8">
+      <c r="A102" s="6">
+        <v>0</v>
+      </c>
+      <c r="B102" s="6">
         <v>101</v>
       </c>
-      <c r="C102" s="8">
+      <c r="C102" s="6">
         <v>3.0349999999999999E-2</v>
       </c>
-      <c r="D102" s="8"/>
+      <c r="D102" s="6"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="8">
-        <v>0</v>
-      </c>
-      <c r="B103" s="8">
+      <c r="A103" s="6">
+        <v>0</v>
+      </c>
+      <c r="B103" s="6">
         <v>102</v>
       </c>
-      <c r="C103" s="8">
+      <c r="C103" s="6">
         <v>3.0370000000000001E-2</v>
       </c>
-      <c r="D103" s="8"/>
+      <c r="D103" s="6"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="8">
-        <v>0</v>
-      </c>
-      <c r="B104" s="8">
+      <c r="A104" s="6">
+        <v>0</v>
+      </c>
+      <c r="B104" s="6">
         <v>103</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C104" s="6">
         <v>3.04E-2</v>
       </c>
-      <c r="D104" s="8"/>
+      <c r="D104" s="6"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="8">
-        <v>0</v>
-      </c>
-      <c r="B105" s="8">
+      <c r="A105" s="6">
+        <v>0</v>
+      </c>
+      <c r="B105" s="6">
         <v>104</v>
       </c>
-      <c r="C105" s="8">
+      <c r="C105" s="6">
         <v>3.0419999999999999E-2</v>
       </c>
-      <c r="D105" s="8"/>
+      <c r="D105" s="6"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="8">
-        <v>0</v>
-      </c>
-      <c r="B106" s="8">
+      <c r="A106" s="6">
+        <v>0</v>
+      </c>
+      <c r="B106" s="6">
         <v>105</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="6">
         <v>3.0450000000000001E-2</v>
       </c>
-      <c r="D106" s="8"/>
+      <c r="D106" s="6"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="8">
-        <v>0</v>
-      </c>
-      <c r="B107" s="8">
+      <c r="A107" s="6">
+        <v>0</v>
+      </c>
+      <c r="B107" s="6">
         <v>106</v>
       </c>
-      <c r="C107" s="8">
+      <c r="C107" s="6">
         <v>3.0470000000000001E-2</v>
       </c>
-      <c r="D107" s="8"/>
+      <c r="D107" s="6"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="8">
-        <v>0</v>
-      </c>
-      <c r="B108" s="8">
+      <c r="A108" s="6">
+        <v>0</v>
+      </c>
+      <c r="B108" s="6">
         <v>107</v>
       </c>
-      <c r="C108" s="8">
+      <c r="C108" s="6">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="D108" s="8"/>
+      <c r="D108" s="6"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="8">
-        <v>0</v>
-      </c>
-      <c r="B109" s="8">
+      <c r="A109" s="6">
+        <v>0</v>
+      </c>
+      <c r="B109" s="6">
         <v>108</v>
       </c>
-      <c r="C109" s="8">
+      <c r="C109" s="6">
         <v>3.0519999999999999E-2</v>
       </c>
-      <c r="D109" s="8"/>
+      <c r="D109" s="6"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="8">
-        <v>0</v>
-      </c>
-      <c r="B110" s="8">
+      <c r="A110" s="6">
+        <v>0</v>
+      </c>
+      <c r="B110" s="6">
         <v>109</v>
       </c>
-      <c r="C110" s="8">
+      <c r="C110" s="6">
         <v>3.0540000000000001E-2</v>
       </c>
-      <c r="D110" s="8"/>
+      <c r="D110" s="6"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="8">
-        <v>0</v>
-      </c>
-      <c r="B111" s="8">
+      <c r="A111" s="6">
+        <v>0</v>
+      </c>
+      <c r="B111" s="6">
         <v>110</v>
       </c>
-      <c r="C111" s="8">
+      <c r="C111" s="6">
         <v>3.056E-2</v>
       </c>
-      <c r="D111" s="8"/>
+      <c r="D111" s="6"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="8">
-        <v>0</v>
-      </c>
-      <c r="B112" s="8">
+      <c r="A112" s="6">
+        <v>0</v>
+      </c>
+      <c r="B112" s="6">
         <v>111</v>
       </c>
-      <c r="C112" s="8">
+      <c r="C112" s="6">
         <v>3.0589999999999999E-2</v>
       </c>
-      <c r="D112" s="8"/>
+      <c r="D112" s="6"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="8">
-        <v>0</v>
-      </c>
-      <c r="B113" s="8">
+      <c r="A113" s="6">
+        <v>0</v>
+      </c>
+      <c r="B113" s="6">
         <v>112</v>
       </c>
-      <c r="C113" s="8">
+      <c r="C113" s="6">
         <v>3.0609999999999998E-2</v>
       </c>
-      <c r="D113" s="8"/>
+      <c r="D113" s="6"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="8">
-        <v>0</v>
-      </c>
-      <c r="B114" s="8">
+      <c r="A114" s="6">
+        <v>0</v>
+      </c>
+      <c r="B114" s="6">
         <v>113</v>
       </c>
-      <c r="C114" s="8">
+      <c r="C114" s="6">
         <v>3.0630000000000001E-2</v>
       </c>
-      <c r="D114" s="8"/>
+      <c r="D114" s="6"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="8">
-        <v>0</v>
-      </c>
-      <c r="B115" s="8">
+      <c r="A115" s="6">
+        <v>0</v>
+      </c>
+      <c r="B115" s="6">
         <v>114</v>
       </c>
-      <c r="C115" s="8">
+      <c r="C115" s="6">
         <v>3.065E-2</v>
       </c>
-      <c r="D115" s="8"/>
+      <c r="D115" s="6"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="8">
-        <v>0</v>
-      </c>
-      <c r="B116" s="8">
+      <c r="A116" s="6">
+        <v>0</v>
+      </c>
+      <c r="B116" s="6">
         <v>115</v>
       </c>
-      <c r="C116" s="8">
+      <c r="C116" s="6">
         <v>3.0669999999999999E-2</v>
       </c>
-      <c r="D116" s="8"/>
+      <c r="D116" s="6"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="8">
-        <v>0</v>
-      </c>
-      <c r="B117" s="8">
+      <c r="A117" s="6">
+        <v>0</v>
+      </c>
+      <c r="B117" s="6">
         <v>116</v>
       </c>
-      <c r="C117" s="8">
+      <c r="C117" s="6">
         <v>3.0689999999999999E-2</v>
       </c>
-      <c r="D117" s="8"/>
+      <c r="D117" s="6"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="8">
-        <v>0</v>
-      </c>
-      <c r="B118" s="8">
+      <c r="A118" s="6">
+        <v>0</v>
+      </c>
+      <c r="B118" s="6">
         <v>117</v>
       </c>
-      <c r="C118" s="8">
+      <c r="C118" s="6">
         <v>3.0710000000000001E-2</v>
       </c>
-      <c r="D118" s="8"/>
+      <c r="D118" s="6"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="8">
-        <v>0</v>
-      </c>
-      <c r="B119" s="8">
+      <c r="A119" s="6">
+        <v>0</v>
+      </c>
+      <c r="B119" s="6">
         <v>118</v>
       </c>
-      <c r="C119" s="8">
+      <c r="C119" s="6">
         <v>3.073E-2</v>
       </c>
-      <c r="D119" s="8"/>
+      <c r="D119" s="6"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="8">
-        <v>0</v>
-      </c>
-      <c r="B120" s="8">
+      <c r="A120" s="6">
+        <v>0</v>
+      </c>
+      <c r="B120" s="6">
         <v>119</v>
       </c>
-      <c r="C120" s="8">
+      <c r="C120" s="6">
         <v>3.075E-2</v>
       </c>
-      <c r="D120" s="8"/>
+      <c r="D120" s="6"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="8">
-        <v>0</v>
-      </c>
-      <c r="B121" s="8">
+      <c r="A121" s="6">
+        <v>0</v>
+      </c>
+      <c r="B121" s="6">
         <v>120</v>
       </c>
-      <c r="C121" s="8">
+      <c r="C121" s="6">
         <v>3.0769999999999999E-2</v>
       </c>
-      <c r="D121" s="8"/>
+      <c r="D121" s="6"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="8">
-        <v>0</v>
-      </c>
-      <c r="B122" s="8">
+      <c r="A122" s="6">
+        <v>0</v>
+      </c>
+      <c r="B122" s="6">
         <v>121</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C122" s="6">
         <v>3.0790000000000001E-2</v>
       </c>
-      <c r="D122" s="8"/>
+      <c r="D122" s="6"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="8">
-        <v>0</v>
-      </c>
-      <c r="B123" s="8">
+      <c r="A123" s="6">
+        <v>0</v>
+      </c>
+      <c r="B123" s="6">
         <v>122</v>
       </c>
-      <c r="C123" s="8">
+      <c r="C123" s="6">
         <v>3.0800000000000001E-2</v>
       </c>
-      <c r="D123" s="8"/>
+      <c r="D123" s="6"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="8">
-        <v>0</v>
-      </c>
-      <c r="B124" s="8">
+      <c r="A124" s="6">
+        <v>0</v>
+      </c>
+      <c r="B124" s="6">
         <v>123</v>
       </c>
-      <c r="C124" s="8">
+      <c r="C124" s="6">
         <v>3.082E-2</v>
       </c>
-      <c r="D124" s="8"/>
+      <c r="D124" s="6"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="8">
-        <v>0</v>
-      </c>
-      <c r="B125" s="8">
+      <c r="A125" s="6">
+        <v>0</v>
+      </c>
+      <c r="B125" s="6">
         <v>124</v>
       </c>
-      <c r="C125" s="8">
+      <c r="C125" s="6">
         <v>3.0839999999999999E-2</v>
       </c>
-      <c r="D125" s="8"/>
+      <c r="D125" s="6"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="8">
-        <v>0</v>
-      </c>
-      <c r="B126" s="8">
+      <c r="A126" s="6">
+        <v>0</v>
+      </c>
+      <c r="B126" s="6">
         <v>125</v>
       </c>
-      <c r="C126" s="8">
+      <c r="C126" s="6">
         <v>3.0859999999999999E-2</v>
       </c>
-      <c r="D126" s="8"/>
+      <c r="D126" s="6"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="8">
-        <v>0</v>
-      </c>
-      <c r="B127" s="8">
+      <c r="A127" s="6">
+        <v>0</v>
+      </c>
+      <c r="B127" s="6">
         <v>126</v>
       </c>
-      <c r="C127" s="8">
+      <c r="C127" s="6">
         <v>3.0870000000000002E-2</v>
       </c>
-      <c r="D127" s="8"/>
+      <c r="D127" s="6"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="8">
-        <v>0</v>
-      </c>
-      <c r="B128" s="8">
+      <c r="A128" s="6">
+        <v>0</v>
+      </c>
+      <c r="B128" s="6">
         <v>127</v>
       </c>
-      <c r="C128" s="8">
+      <c r="C128" s="6">
         <v>3.0890000000000001E-2</v>
       </c>
-      <c r="D128" s="8"/>
+      <c r="D128" s="6"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="8">
-        <v>0</v>
-      </c>
-      <c r="B129" s="8">
+      <c r="A129" s="6">
+        <v>0</v>
+      </c>
+      <c r="B129" s="6">
         <v>128</v>
       </c>
-      <c r="C129" s="8">
+      <c r="C129" s="6">
         <v>3.091E-2</v>
       </c>
-      <c r="D129" s="8"/>
+      <c r="D129" s="6"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="8">
-        <v>0</v>
-      </c>
-      <c r="B130" s="8">
+      <c r="A130" s="6">
+        <v>0</v>
+      </c>
+      <c r="B130" s="6">
         <v>129</v>
       </c>
-      <c r="C130" s="8">
+      <c r="C130" s="6">
         <v>3.092E-2</v>
       </c>
-      <c r="D130" s="8"/>
+      <c r="D130" s="6"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="8">
-        <v>0</v>
-      </c>
-      <c r="B131" s="8">
+      <c r="A131" s="6">
+        <v>0</v>
+      </c>
+      <c r="B131" s="6">
         <v>130</v>
       </c>
-      <c r="C131" s="8">
+      <c r="C131" s="6">
         <v>3.0939999999999999E-2</v>
       </c>
-      <c r="D131" s="8"/>
+      <c r="D131" s="6"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="8">
-        <v>0</v>
-      </c>
-      <c r="B132" s="8">
+      <c r="A132" s="6">
+        <v>0</v>
+      </c>
+      <c r="B132" s="6">
         <v>131</v>
       </c>
-      <c r="C132" s="8">
+      <c r="C132" s="6">
         <v>3.0949999999999998E-2</v>
       </c>
-      <c r="D132" s="8"/>
+      <c r="D132" s="6"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="8">
-        <v>0</v>
-      </c>
-      <c r="B133" s="8">
+      <c r="A133" s="6">
+        <v>0</v>
+      </c>
+      <c r="B133" s="6">
         <v>132</v>
       </c>
-      <c r="C133" s="8">
+      <c r="C133" s="6">
         <v>3.0970000000000001E-2</v>
       </c>
-      <c r="D133" s="8"/>
+      <c r="D133" s="6"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="8">
-        <v>0</v>
-      </c>
-      <c r="B134" s="8">
+      <c r="A134" s="6">
+        <v>0</v>
+      </c>
+      <c r="B134" s="6">
         <v>133</v>
       </c>
-      <c r="C134" s="8">
+      <c r="C134" s="6">
         <v>3.0980000000000001E-2</v>
       </c>
-      <c r="D134" s="8"/>
+      <c r="D134" s="6"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="8">
-        <v>0</v>
-      </c>
-      <c r="B135" s="8">
+      <c r="A135" s="6">
+        <v>0</v>
+      </c>
+      <c r="B135" s="6">
         <v>134</v>
       </c>
-      <c r="C135" s="8">
+      <c r="C135" s="6">
         <v>3.1E-2</v>
       </c>
-      <c r="D135" s="8"/>
+      <c r="D135" s="6"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="8">
-        <v>0</v>
-      </c>
-      <c r="B136" s="8">
+      <c r="A136" s="6">
+        <v>0</v>
+      </c>
+      <c r="B136" s="6">
         <v>135</v>
       </c>
-      <c r="C136" s="8">
+      <c r="C136" s="6">
         <v>3.1009999999999999E-2</v>
       </c>
-      <c r="D136" s="8"/>
+      <c r="D136" s="6"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="8">
-        <v>0</v>
-      </c>
-      <c r="B137" s="8">
+      <c r="A137" s="6">
+        <v>0</v>
+      </c>
+      <c r="B137" s="6">
         <v>136</v>
       </c>
-      <c r="C137" s="8">
+      <c r="C137" s="6">
         <v>3.1029999999999999E-2</v>
       </c>
-      <c r="D137" s="8"/>
+      <c r="D137" s="6"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="8">
-        <v>0</v>
-      </c>
-      <c r="B138" s="8">
+      <c r="A138" s="6">
+        <v>0</v>
+      </c>
+      <c r="B138" s="6">
         <v>137</v>
       </c>
-      <c r="C138" s="8">
+      <c r="C138" s="6">
         <v>3.1040000000000002E-2</v>
       </c>
-      <c r="D138" s="8"/>
+      <c r="D138" s="6"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="8">
-        <v>0</v>
-      </c>
-      <c r="B139" s="8">
+      <c r="A139" s="6">
+        <v>0</v>
+      </c>
+      <c r="B139" s="6">
         <v>138</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="6">
         <v>3.1060000000000001E-2</v>
       </c>
-      <c r="D139" s="8"/>
+      <c r="D139" s="6"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="8">
-        <v>0</v>
-      </c>
-      <c r="B140" s="8">
+      <c r="A140" s="6">
+        <v>0</v>
+      </c>
+      <c r="B140" s="6">
         <v>139</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C140" s="6">
         <v>3.107E-2</v>
       </c>
-      <c r="D140" s="8"/>
+      <c r="D140" s="6"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="8">
-        <v>0</v>
-      </c>
-      <c r="B141" s="8">
+      <c r="A141" s="6">
+        <v>0</v>
+      </c>
+      <c r="B141" s="6">
         <v>140</v>
       </c>
-      <c r="C141" s="8">
+      <c r="C141" s="6">
         <v>3.109E-2</v>
       </c>
-      <c r="D141" s="8"/>
+      <c r="D141" s="6"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="8">
-        <v>0</v>
-      </c>
-      <c r="B142" s="8">
+      <c r="A142" s="6">
+        <v>0</v>
+      </c>
+      <c r="B142" s="6">
         <v>141</v>
       </c>
-      <c r="C142" s="8">
+      <c r="C142" s="6">
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="D142" s="8"/>
+      <c r="D142" s="6"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="8">
-        <v>0</v>
-      </c>
-      <c r="B143" s="8">
+      <c r="A143" s="6">
+        <v>0</v>
+      </c>
+      <c r="B143" s="6">
         <v>142</v>
       </c>
-      <c r="C143" s="8">
+      <c r="C143" s="6">
         <v>3.1109999999999999E-2</v>
       </c>
-      <c r="D143" s="8"/>
+      <c r="D143" s="6"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="8">
-        <v>0</v>
-      </c>
-      <c r="B144" s="8">
+      <c r="A144" s="6">
+        <v>0</v>
+      </c>
+      <c r="B144" s="6">
         <v>143</v>
       </c>
-      <c r="C144" s="8">
+      <c r="C144" s="6">
         <v>3.1130000000000001E-2</v>
       </c>
-      <c r="D144" s="8"/>
+      <c r="D144" s="6"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="8">
-        <v>0</v>
-      </c>
-      <c r="B145" s="8">
+      <c r="A145" s="6">
+        <v>0</v>
+      </c>
+      <c r="B145" s="6">
         <v>144</v>
       </c>
-      <c r="C145" s="8">
+      <c r="C145" s="6">
         <v>3.1140000000000001E-2</v>
       </c>
-      <c r="D145" s="8"/>
+      <c r="D145" s="6"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="8">
-        <v>0</v>
-      </c>
-      <c r="B146" s="8">
+      <c r="A146" s="6">
+        <v>0</v>
+      </c>
+      <c r="B146" s="6">
         <v>145</v>
       </c>
-      <c r="C146" s="8">
+      <c r="C146" s="6">
         <v>3.1150000000000001E-2</v>
       </c>
-      <c r="D146" s="8"/>
+      <c r="D146" s="6"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="8">
-        <v>0</v>
-      </c>
-      <c r="B147" s="8">
+      <c r="A147" s="6">
+        <v>0</v>
+      </c>
+      <c r="B147" s="6">
         <v>146</v>
       </c>
-      <c r="C147" s="8">
+      <c r="C147" s="6">
         <v>3.116E-2</v>
       </c>
-      <c r="D147" s="8"/>
+      <c r="D147" s="6"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="8">
-        <v>0</v>
-      </c>
-      <c r="B148" s="8">
+      <c r="A148" s="6">
+        <v>0</v>
+      </c>
+      <c r="B148" s="6">
         <v>147</v>
       </c>
-      <c r="C148" s="8">
+      <c r="C148" s="6">
         <v>3.1179999999999999E-2</v>
       </c>
-      <c r="D148" s="8"/>
+      <c r="D148" s="6"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="8">
-        <v>0</v>
-      </c>
-      <c r="B149" s="8">
+      <c r="A149" s="6">
+        <v>0</v>
+      </c>
+      <c r="B149" s="6">
         <v>148</v>
       </c>
-      <c r="C149" s="8">
+      <c r="C149" s="6">
         <v>3.1189999999999999E-2</v>
       </c>
-      <c r="D149" s="8"/>
+      <c r="D149" s="6"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="8">
-        <v>0</v>
-      </c>
-      <c r="B150" s="8">
+      <c r="A150" s="6">
+        <v>0</v>
+      </c>
+      <c r="B150" s="6">
         <v>149</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C150" s="6">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="D150" s="8"/>
+      <c r="D150" s="6"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="8">
-        <v>0</v>
-      </c>
-      <c r="B151" s="8">
+      <c r="A151" s="6">
+        <v>0</v>
+      </c>
+      <c r="B151" s="6">
         <v>150</v>
       </c>
-      <c r="C151" s="8">
+      <c r="C151" s="6">
         <v>3.1210000000000002E-2</v>
       </c>
-      <c r="D151" s="8"/>
+      <c r="D151" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4565,7 +4566,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E398A87-82CA-4B50-B75F-313C6B1D2BBE}">
-  <dimension ref="A1:AB54"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:AB71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -4640,64 +4642,64 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="6">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="6">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="6">
         <v>2.8E-3</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="6">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="6">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="6">
         <v>3.2499999999999999E-3</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="6">
         <v>3.3E-3</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="6">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="6">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="6">
         <v>3.4499999999999999E-3</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="6">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="6">
         <v>3.5500000000000002E-3</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="6">
         <v>3.65E-3</v>
       </c>
-      <c r="U2" s="8">
+      <c r="U2" s="6">
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
@@ -5160,64 +5162,64 @@
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="6">
         <v>2.8E-3</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="6">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="6">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="6">
         <v>3.2499999999999999E-3</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="6">
         <v>3.3E-3</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="6">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="6">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="6">
         <v>3.4499999999999999E-3</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q10" s="6">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="R10" s="8">
+      <c r="R10" s="6">
         <v>3.5500000000000002E-3</v>
       </c>
-      <c r="S10" s="8">
+      <c r="S10" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="T10" s="8">
+      <c r="T10" s="6">
         <v>3.65E-3</v>
       </c>
-      <c r="U10" s="8">
+      <c r="U10" s="6">
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
@@ -5225,64 +5227,64 @@
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>1.20625E-2</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <v>1.2437500000000001E-2</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>1.257638888888889E-2</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="6">
         <v>1.271527777777778E-2</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="6">
         <v>1.285416666666667E-2</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="6">
         <v>1.30125E-2</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6">
         <v>1.317083333333333E-2</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="6">
         <v>1.332916666666667E-2</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="6">
         <v>1.3487499999999999E-2</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="6">
         <v>1.3645833333333329E-2</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="6">
         <v>1.3724999999999999E-2</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="6">
         <v>1.3804166666666669E-2</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="6">
         <v>1.3883333333333331E-2</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="6">
         <v>1.3962499999999999E-2</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="6">
         <v>1.4041666666666669E-2</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="6">
         <v>1.4120833333333331E-2</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="6">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="6">
         <v>1.4279166666666669E-2</v>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="6">
         <v>1.4358333333333331E-2</v>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="6">
         <v>1.4437500000000001E-2</v>
       </c>
     </row>
@@ -5296,58 +5298,58 @@
       <c r="C12">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>3.0000000000000003E-4</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="6">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="6">
         <v>6.0000000000000006E-4</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="6">
         <v>7.000000000000001E-4</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="6">
         <v>8.0000000000000015E-4</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="6">
         <v>9.0000000000000019E-4</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="6">
         <v>1.0000000000000002E-3</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="6">
         <v>1.1000000000000003E-3</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="6">
         <v>1.2000000000000003E-3</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="6">
         <v>1.3000000000000004E-3</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="6">
         <v>1.4000000000000004E-3</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="6">
         <v>1.5000000000000005E-3</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q12" s="6">
         <v>1.6000000000000005E-3</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="6">
         <v>1.7000000000000006E-3</v>
       </c>
-      <c r="S12" s="8">
+      <c r="S12" s="6">
         <v>1.8000000000000006E-3</v>
       </c>
-      <c r="T12" s="8">
+      <c r="T12" s="6">
         <v>1.9000000000000006E-3</v>
       </c>
-      <c r="U12" s="8">
+      <c r="U12" s="6">
         <v>2.0000000000000005E-3</v>
       </c>
     </row>
@@ -6002,7 +6004,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B23">
@@ -6132,72 +6134,72 @@
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="6">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="6">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="6">
         <v>2.8E-3</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="6">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="6">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="6">
         <v>3.2499999999999999E-3</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="6">
         <v>3.3E-3</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="6">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="6">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="6">
         <v>3.4499999999999999E-3</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="Q25" s="6">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="R25" s="8">
+      <c r="R25" s="6">
         <v>3.5500000000000002E-3</v>
       </c>
-      <c r="S25" s="8">
+      <c r="S25" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="T25" s="8">
+      <c r="T25" s="6">
         <v>3.65E-3</v>
       </c>
-      <c r="U25" s="8">
+      <c r="U25" s="6">
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B26">
@@ -6327,137 +6329,137 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="6">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="6">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="6">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="6">
         <v>2.8E-3</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="6">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="6">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="6">
         <v>3.2499999999999999E-3</v>
       </c>
-      <c r="M28" s="8">
+      <c r="M28" s="6">
         <v>3.3E-3</v>
       </c>
-      <c r="N28" s="8">
+      <c r="N28" s="6">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="O28" s="8">
+      <c r="O28" s="6">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="6">
         <v>3.4499999999999999E-3</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="Q28" s="6">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="6">
         <v>3.5500000000000002E-3</v>
       </c>
-      <c r="S28" s="8">
+      <c r="S28" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="T28" s="8">
+      <c r="T28" s="6">
         <v>3.65E-3</v>
       </c>
-      <c r="U28" s="8">
+      <c r="U28" s="6">
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="6">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="6">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="6">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="6">
         <v>2.8E-3</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="6">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="6">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="6">
         <v>3.2499999999999999E-3</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="6">
         <v>3.3E-3</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="6">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="O29" s="8">
+      <c r="O29" s="6">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="6">
         <v>3.4499999999999999E-3</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="Q29" s="6">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="6">
         <v>3.5500000000000002E-3</v>
       </c>
-      <c r="S29" s="8">
+      <c r="S29" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="T29" s="8">
+      <c r="T29" s="6">
         <v>3.65E-3</v>
       </c>
-      <c r="U29" s="8">
+      <c r="U29" s="6">
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B30">
@@ -6652,7 +6654,7 @@
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B33">
@@ -6717,7 +6719,7 @@
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B34">
@@ -6782,132 +6784,132 @@
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="6">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="6">
         <v>2.12E-2</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="6">
         <v>2.1299999999999999E-2</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="6">
         <v>2.1399999999999999E-2</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="6">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="6">
         <v>2.1600000000000001E-2</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="6">
         <v>2.1700000000000001E-2</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="6">
         <v>2.18E-2</v>
       </c>
-      <c r="J35" s="8">
+      <c r="J35" s="6">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="6">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="L35" s="8">
+      <c r="L35" s="6">
         <v>2.205E-2</v>
       </c>
-      <c r="M35" s="8">
+      <c r="M35" s="6">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="N35" s="8">
+      <c r="N35" s="6">
         <v>2.215E-2</v>
       </c>
-      <c r="O35" s="8">
+      <c r="O35" s="6">
         <v>2.2200000000000001E-2</v>
       </c>
-      <c r="P35" s="8">
+      <c r="P35" s="6">
         <v>2.2249999999999999E-2</v>
       </c>
-      <c r="Q35" s="8">
+      <c r="Q35" s="6">
         <v>2.23E-2</v>
       </c>
-      <c r="R35" s="8">
+      <c r="R35" s="6">
         <v>2.2349999999999998E-2</v>
       </c>
-      <c r="S35" s="8">
+      <c r="S35" s="6">
         <v>2.24E-2</v>
       </c>
-      <c r="T35" s="8">
+      <c r="T35" s="6">
         <v>2.2450000000000001E-2</v>
       </c>
-      <c r="U35" s="8">
+      <c r="U35" s="6">
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="6">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="6">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="6">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="6">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="6">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="6">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="6">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="6">
         <v>7.4000000000000003E-3</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="6">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="6">
         <v>7.5500000000000003E-3</v>
       </c>
-      <c r="M36" s="8">
+      <c r="M36" s="6">
         <v>7.6E-3</v>
       </c>
-      <c r="N36" s="8">
+      <c r="N36" s="6">
         <v>7.6499999999999997E-3</v>
       </c>
-      <c r="O36" s="8">
+      <c r="O36" s="6">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="P36" s="8">
+      <c r="P36" s="6">
         <v>7.7499999999999999E-3</v>
       </c>
-      <c r="Q36" s="8">
+      <c r="Q36" s="6">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="R36" s="8">
+      <c r="R36" s="6">
         <v>7.8499999999999993E-3</v>
       </c>
-      <c r="S36" s="8">
+      <c r="S36" s="6">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="T36" s="8">
+      <c r="T36" s="6">
         <v>7.9500000000000005E-3</v>
       </c>
-      <c r="U36" s="8">
+      <c r="U36" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
@@ -6977,7 +6979,7 @@
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B38">
@@ -7042,7 +7044,7 @@
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B39">
@@ -7107,7 +7109,7 @@
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B40">
@@ -7172,7 +7174,7 @@
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B41">
@@ -7235,15 +7237,15 @@
       <c r="U41">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="W41" s="7"/>
-      <c r="X41" s="7"/>
-      <c r="Y41" s="7"/>
-      <c r="Z41" s="7"/>
-      <c r="AA41" s="7"/>
-      <c r="AB41" s="7"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5"/>
+      <c r="AA41" s="5"/>
+      <c r="AB41" s="5"/>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B42">
@@ -7306,15 +7308,15 @@
       <c r="U42">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="W42" s="7"/>
-      <c r="X42" s="7"/>
-      <c r="Y42" s="7"/>
-      <c r="Z42" s="7"/>
-      <c r="AA42" s="7"/>
-      <c r="AB42" s="7"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5"/>
+      <c r="Z42" s="5"/>
+      <c r="AA42" s="5"/>
+      <c r="AB42" s="5"/>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B43">
@@ -7377,15 +7379,15 @@
       <c r="U43">
         <v>1.9E-2</v>
       </c>
-      <c r="W43" s="7"/>
-      <c r="X43" s="7"/>
-      <c r="Y43" s="7"/>
-      <c r="Z43" s="7"/>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="7"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="5"/>
+      <c r="AA43" s="5"/>
+      <c r="AB43" s="5"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B44">
@@ -7448,15 +7450,15 @@
       <c r="U44">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="W44" s="7"/>
-      <c r="X44" s="7"/>
-      <c r="Y44" s="7"/>
-      <c r="Z44" s="7"/>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="7"/>
+      <c r="W44" s="5"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5"/>
+      <c r="Z44" s="5"/>
+      <c r="AA44" s="5"/>
+      <c r="AB44" s="5"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="4">
@@ -7519,15 +7521,15 @@
       <c r="U45" s="4">
         <v>2.3E-2</v>
       </c>
-      <c r="W45" s="7"/>
-      <c r="X45" s="7"/>
-      <c r="Y45" s="7"/>
-      <c r="Z45" s="7"/>
-      <c r="AA45" s="7"/>
-      <c r="AB45" s="7"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="5"/>
+      <c r="AB45" s="5"/>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="4">
@@ -7590,15 +7592,15 @@
       <c r="U46" s="4">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="W46" s="7"/>
-      <c r="X46" s="7"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="7"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="5"/>
+      <c r="AA46" s="5"/>
+      <c r="AB46" s="5"/>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B47">
@@ -7661,10 +7663,10 @@
       <c r="U47">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="W47" s="7"/>
+      <c r="W47" s="5"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B48">
@@ -7727,15 +7729,15 @@
       <c r="U48">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="W48" s="7"/>
-      <c r="X48" s="7"/>
-      <c r="Y48" s="7"/>
-      <c r="Z48" s="7"/>
-      <c r="AA48" s="7"/>
-      <c r="AB48" s="7"/>
+      <c r="W48" s="5"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5"/>
+      <c r="Z48" s="5"/>
+      <c r="AA48" s="5"/>
+      <c r="AB48" s="5"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B49">
@@ -7798,15 +7800,15 @@
       <c r="U49">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="W49" s="7"/>
-      <c r="X49" s="7"/>
-      <c r="Y49" s="7"/>
-      <c r="Z49" s="7"/>
-      <c r="AA49" s="7"/>
-      <c r="AB49" s="7"/>
+      <c r="W49" s="5"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5"/>
+      <c r="Z49" s="5"/>
+      <c r="AA49" s="5"/>
+      <c r="AB49" s="5"/>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B50">
@@ -7869,15 +7871,15 @@
       <c r="U50">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="W50" s="7"/>
-      <c r="X50" s="7"/>
-      <c r="Y50" s="7"/>
-      <c r="Z50" s="7"/>
-      <c r="AA50" s="7"/>
-      <c r="AB50" s="7"/>
+      <c r="W50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="5"/>
+      <c r="AB50" s="5"/>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B51">
@@ -7940,14 +7942,14 @@
       <c r="U51">
         <v>1.9E-2</v>
       </c>
-      <c r="X51" s="7"/>
-      <c r="Y51" s="7"/>
-      <c r="Z51" s="7"/>
-      <c r="AA51" s="7"/>
-      <c r="AB51" s="7"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5"/>
+      <c r="Z51" s="5"/>
+      <c r="AA51" s="5"/>
+      <c r="AB51" s="5"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="4">
@@ -8010,14 +8012,14 @@
       <c r="U52" s="4">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="X52" s="7"/>
-      <c r="Y52" s="7"/>
-      <c r="Z52" s="7"/>
-      <c r="AA52" s="7"/>
-      <c r="AB52" s="7"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
+      <c r="Z52" s="5"/>
+      <c r="AA52" s="5"/>
+      <c r="AB52" s="5"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="4">
@@ -8080,18 +8082,53 @@
       <c r="U53" s="4">
         <v>2.3E-2</v>
       </c>
-      <c r="X53" s="7"/>
-      <c r="Y53" s="7"/>
-      <c r="Z53" s="7"/>
-      <c r="AA53" s="7"/>
-      <c r="AB53" s="7"/>
-    </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="X54" s="7"/>
-      <c r="Y54" s="7"/>
-      <c r="Z54" s="7"/>
-      <c r="AA54" s="7"/>
-      <c r="AB54" s="7"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
+      <c r="Z53" s="5"/>
+      <c r="AA53" s="5"/>
+      <c r="AB53" s="5"/>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A58" s="6"/>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A59" s="6"/>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A60" s="6"/>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A62" s="6"/>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A63" s="6"/>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A64" s="6"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="6"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="6"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="6"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="6"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8100,2127 +8137,2128 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC8160D-A4B3-4DFE-91B4-C0068E44C09E}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.21875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="1" width="7.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="C2" s="6">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
         <v>-4.449999999999843E-3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8">
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
         <v>-4.7492877139407863E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
         <v>-4.8490311393776242E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6">
         <v>-4.6506939059682839E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <v>1</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="8">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
         <v>-4.4523045769666592E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <v>1</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>6</v>
       </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
         <v>-4.1548916903217936E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>1</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>7</v>
       </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
         <v>-3.8573434612039215E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>1</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>8</v>
       </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
         <v>-3.460578737007669E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>9</v>
       </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
         <v>-3.0631946140144972E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>10</v>
       </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
         <v>-2.6651020891858002E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="6">
         <v>1</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>11</v>
       </c>
-      <c r="C12" s="8">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
         <v>-2.3428351222567478E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>1</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>12</v>
       </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
         <v>-1.8664394833945996E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="6">
         <v>1</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>13</v>
       </c>
-      <c r="C14" s="8">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="6">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
         <v>-1.5785481548286073E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="6">
         <v>1</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>14</v>
       </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="C15" s="6">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6">
         <v>-1.2510909281734373E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>1</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>15</v>
       </c>
-      <c r="C16" s="8">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
+      <c r="C16" s="6">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
         <v>-9.4192697808626047E-4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>0</v>
-      </c>
-      <c r="B17" s="8">
+      <c r="A17" s="6">
+        <v>0</v>
+      </c>
+      <c r="B17" s="6">
         <v>16</v>
       </c>
-      <c r="C17" s="8">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
         <v>-7.7497898425404887E-4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>0</v>
-      </c>
-      <c r="B18" s="8">
+      <c r="A18" s="6">
+        <v>0</v>
+      </c>
+      <c r="B18" s="6">
         <v>17</v>
       </c>
-      <c r="C18" s="8">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="C18" s="6">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6">
         <v>-6.276487632096428E-4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>0</v>
-      </c>
-      <c r="B19" s="8">
+      <c r="A19" s="6">
+        <v>0</v>
+      </c>
+      <c r="B19" s="6">
         <v>18</v>
       </c>
-      <c r="C19" s="8">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
         <v>-4.9667033020839302E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>0</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="A20" s="6">
+        <v>0</v>
+      </c>
+      <c r="B20" s="6">
         <v>19</v>
       </c>
-      <c r="C20" s="8">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
         <v>-3.7946454996118373E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <v>1</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="6">
         <v>20</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="6">
         <v>0.33</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="6">
         <v>-2.7396759664655157E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>0</v>
-      </c>
-      <c r="B22" s="8">
+      <c r="A22" s="6">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6">
         <v>21</v>
       </c>
-      <c r="C22" s="8">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C22" s="6">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6">
         <v>-1.9306145426889465E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>0</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="6">
+        <v>0</v>
+      </c>
+      <c r="B23" s="6">
         <v>22</v>
       </c>
-      <c r="C23" s="8">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
         <v>3.356441626500839E-5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
-        <v>0</v>
-      </c>
-      <c r="B24" s="8">
+      <c r="A24" s="6">
+        <v>0</v>
+      </c>
+      <c r="B24" s="6">
         <v>23</v>
       </c>
-      <c r="C24" s="8">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8">
+      <c r="C24" s="6">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6">
         <v>3.7305572938839404E-4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
-        <v>0</v>
-      </c>
-      <c r="B25" s="8">
+      <c r="A25" s="6">
+        <v>0</v>
+      </c>
+      <c r="B25" s="6">
         <v>24</v>
       </c>
-      <c r="C25" s="8">
-        <v>0</v>
-      </c>
-      <c r="D25" s="8">
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
         <v>7.9932639103041936E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
+      <c r="A26" s="6">
         <v>1</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>25</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <v>0.12</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <v>1.2915728598819065E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
-        <v>0</v>
-      </c>
-      <c r="B27" s="8">
+      <c r="A27" s="6">
+        <v>0</v>
+      </c>
+      <c r="B27" s="6">
         <v>26</v>
       </c>
-      <c r="C27" s="8">
-        <v>0</v>
-      </c>
-      <c r="D27" s="8">
+      <c r="C27" s="6">
+        <v>0</v>
+      </c>
+      <c r="D27" s="6">
         <v>1.8331481078603939E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
-        <v>0</v>
-      </c>
-      <c r="B28" s="8">
+      <c r="A28" s="6">
+        <v>0</v>
+      </c>
+      <c r="B28" s="6">
         <v>27</v>
       </c>
-      <c r="C28" s="8">
-        <v>0</v>
-      </c>
-      <c r="D28" s="8">
+      <c r="C28" s="6">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6">
         <v>2.4106989351067032E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>0</v>
-      </c>
-      <c r="B29" s="8">
+      <c r="A29" s="6">
+        <v>0</v>
+      </c>
+      <c r="B29" s="6">
         <v>28</v>
       </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8">
+      <c r="C29" s="6">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6">
         <v>3.0134986404870556E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>0</v>
-      </c>
-      <c r="B30" s="8">
+      <c r="A30" s="6">
+        <v>0</v>
+      </c>
+      <c r="B30" s="6">
         <v>29</v>
       </c>
-      <c r="C30" s="8">
-        <v>0</v>
-      </c>
-      <c r="D30" s="8">
+      <c r="C30" s="6">
+        <v>0</v>
+      </c>
+      <c r="D30" s="6">
         <v>3.6329263050836058E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
+      <c r="A31" s="6">
         <v>1</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="6">
         <v>30</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="6">
         <v>0.48</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="6">
         <v>4.2620572835279091E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
-        <v>0</v>
-      </c>
-      <c r="B32" s="8">
+      <c r="A32" s="6">
+        <v>0</v>
+      </c>
+      <c r="B32" s="6">
         <v>31</v>
       </c>
-      <c r="C32" s="8">
-        <v>0</v>
-      </c>
-      <c r="D32" s="8">
+      <c r="C32" s="6">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6">
         <v>4.895338870999133E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
-        <v>0</v>
-      </c>
-      <c r="B33" s="8">
+      <c r="A33" s="6">
+        <v>0</v>
+      </c>
+      <c r="B33" s="6">
         <v>32</v>
       </c>
-      <c r="C33" s="8">
-        <v>0</v>
-      </c>
-      <c r="D33" s="8">
+      <c r="C33" s="6">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6">
         <v>5.5283317896184236E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
-        <v>0</v>
-      </c>
-      <c r="B34" s="8">
+      <c r="A34" s="6">
+        <v>0</v>
+      </c>
+      <c r="B34" s="6">
         <v>33</v>
       </c>
-      <c r="C34" s="8">
-        <v>0</v>
-      </c>
-      <c r="D34" s="8">
+      <c r="C34" s="6">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6">
         <v>6.1575029522564773E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
-        <v>0</v>
-      </c>
-      <c r="B35" s="8">
+      <c r="A35" s="6">
+        <v>0</v>
+      </c>
+      <c r="B35" s="6">
         <v>34</v>
       </c>
-      <c r="C35" s="8">
-        <v>0</v>
-      </c>
-      <c r="D35" s="8">
+      <c r="C35" s="6">
+        <v>0</v>
+      </c>
+      <c r="D35" s="6">
         <v>6.7800584737407465E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
-        <v>0</v>
-      </c>
-      <c r="B36" s="8">
+      <c r="A36" s="6">
+        <v>0</v>
+      </c>
+      <c r="B36" s="6">
         <v>35</v>
       </c>
-      <c r="C36" s="8">
-        <v>0</v>
-      </c>
-      <c r="D36" s="8">
+      <c r="C36" s="6">
+        <v>0</v>
+      </c>
+      <c r="D36" s="6">
         <v>7.3938084889249023E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
-        <v>0</v>
-      </c>
-      <c r="B37" s="8">
+      <c r="A37" s="6">
+        <v>0</v>
+      </c>
+      <c r="B37" s="6">
         <v>36</v>
       </c>
-      <c r="C37" s="8">
-        <v>0</v>
-      </c>
-      <c r="D37" s="8">
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
         <v>7.997057265482832E-3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
-        <v>0</v>
-      </c>
-      <c r="B38" s="8">
+      <c r="A38" s="6">
+        <v>0</v>
+      </c>
+      <c r="B38" s="6">
         <v>37</v>
       </c>
-      <c r="C38" s="8">
-        <v>0</v>
-      </c>
-      <c r="D38" s="8">
+      <c r="C38" s="6">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6">
         <v>8.5885135487726583E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
-        <v>0</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="6">
+        <v>0</v>
+      </c>
+      <c r="B39" s="6">
         <v>38</v>
       </c>
-      <c r="C39" s="8">
-        <v>0</v>
-      </c>
-      <c r="D39" s="8">
+      <c r="C39" s="6">
+        <v>0</v>
+      </c>
+      <c r="D39" s="6">
         <v>9.1672171750911691E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="8">
-        <v>0</v>
-      </c>
-      <c r="B40" s="8">
+      <c r="A40" s="6">
+        <v>0</v>
+      </c>
+      <c r="B40" s="6">
         <v>39</v>
       </c>
-      <c r="C40" s="8">
-        <v>0</v>
-      </c>
-      <c r="D40" s="8">
+      <c r="C40" s="6">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6">
         <v>9.7324788296642151E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="8">
+      <c r="A41" s="6">
         <v>1</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="6">
         <v>40</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="6">
         <v>0.04</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="6">
         <v>1.0283830472670896E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="8">
-        <v>0</v>
-      </c>
-      <c r="B42" s="8">
+      <c r="A42" s="6">
+        <v>0</v>
+      </c>
+      <c r="B42" s="6">
         <v>41</v>
       </c>
-      <c r="C42" s="8">
-        <v>0</v>
-      </c>
-      <c r="D42" s="8">
+      <c r="C42" s="6">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
         <v>1.0820984458427274E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
-        <v>0</v>
-      </c>
-      <c r="B43" s="8">
+      <c r="A43" s="6">
+        <v>0</v>
+      </c>
+      <c r="B43" s="6">
         <v>42</v>
       </c>
-      <c r="C43" s="8">
-        <v>0</v>
-      </c>
-      <c r="D43" s="8">
+      <c r="C43" s="6">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6">
         <v>1.1343799764694351E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
-        <v>0</v>
-      </c>
-      <c r="B44" s="8">
+      <c r="A44" s="6">
+        <v>0</v>
+      </c>
+      <c r="B44" s="6">
         <v>43</v>
       </c>
-      <c r="C44" s="8">
-        <v>0</v>
-      </c>
-      <c r="D44" s="8">
+      <c r="C44" s="6">
+        <v>0</v>
+      </c>
+      <c r="D44" s="6">
         <v>1.1852254056962552E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
-        <v>0</v>
-      </c>
-      <c r="B45" s="8">
+      <c r="A45" s="6">
+        <v>0</v>
+      </c>
+      <c r="B45" s="6">
         <v>44</v>
       </c>
-      <c r="C45" s="8">
-        <v>0</v>
-      </c>
-      <c r="D45" s="8">
+      <c r="C45" s="6">
+        <v>0</v>
+      </c>
+      <c r="D45" s="6">
         <v>1.234642055588786E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="8">
-        <v>0</v>
-      </c>
-      <c r="B46" s="8">
+      <c r="A46" s="6">
+        <v>0</v>
+      </c>
+      <c r="B46" s="6">
         <v>45</v>
       </c>
-      <c r="C46" s="8">
-        <v>0</v>
-      </c>
-      <c r="D46" s="8">
+      <c r="C46" s="6">
+        <v>0</v>
+      </c>
+      <c r="D46" s="6">
         <v>1.2826448869438511E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="8">
-        <v>0</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="6">
+        <v>0</v>
+      </c>
+      <c r="B47" s="6">
         <v>46</v>
       </c>
-      <c r="C47" s="8">
-        <v>0</v>
-      </c>
-      <c r="D47" s="8">
+      <c r="C47" s="6">
+        <v>0</v>
+      </c>
+      <c r="D47" s="6">
         <v>1.3292549105763385E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="8">
-        <v>0</v>
-      </c>
-      <c r="B48" s="8">
+      <c r="A48" s="6">
+        <v>0</v>
+      </c>
+      <c r="B48" s="6">
         <v>47</v>
       </c>
-      <c r="C48" s="8">
-        <v>0</v>
-      </c>
-      <c r="D48" s="8">
+      <c r="C48" s="6">
+        <v>0</v>
+      </c>
+      <c r="D48" s="6">
         <v>1.3744978706791366E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
-        <v>0</v>
-      </c>
-      <c r="B49" s="8">
+      <c r="A49" s="6">
+        <v>0</v>
+      </c>
+      <c r="B49" s="6">
         <v>48</v>
       </c>
-      <c r="C49" s="8">
-        <v>0</v>
-      </c>
-      <c r="D49" s="8">
+      <c r="C49" s="6">
+        <v>0</v>
+      </c>
+      <c r="D49" s="6">
         <v>1.4184031542527009E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="8">
-        <v>0</v>
-      </c>
-      <c r="B50" s="8">
+      <c r="A50" s="6">
+        <v>0</v>
+      </c>
+      <c r="B50" s="6">
         <v>49</v>
       </c>
-      <c r="C50" s="8">
-        <v>0</v>
-      </c>
-      <c r="D50" s="8">
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6">
         <v>1.4610028886971271E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
+      <c r="A51" s="6">
         <v>1</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="6">
         <v>50</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="6">
         <v>0.03</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="6">
         <v>1.5023311962402364E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="8">
-        <v>0</v>
-      </c>
-      <c r="B52" s="8">
+      <c r="A52" s="6">
+        <v>0</v>
+      </c>
+      <c r="B52" s="6">
         <v>51</v>
       </c>
-      <c r="C52" s="8">
-        <v>0</v>
-      </c>
-      <c r="D52" s="8">
+      <c r="C52" s="6">
+        <v>0</v>
+      </c>
+      <c r="D52" s="6">
         <v>1.542423579245833E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
-        <v>0</v>
-      </c>
-      <c r="B53" s="8">
+      <c r="A53" s="6">
+        <v>0</v>
+      </c>
+      <c r="B53" s="6">
         <v>52</v>
       </c>
-      <c r="C53" s="8">
-        <v>0</v>
-      </c>
-      <c r="D53" s="8">
+      <c r="C53" s="6">
+        <v>0</v>
+      </c>
+      <c r="D53" s="6">
         <v>1.581316414844669E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="8">
-        <v>0</v>
-      </c>
-      <c r="B54" s="8">
+      <c r="A54" s="6">
+        <v>0</v>
+      </c>
+      <c r="B54" s="6">
         <v>53</v>
       </c>
-      <c r="C54" s="8">
-        <v>0</v>
-      </c>
-      <c r="D54" s="8">
+      <c r="C54" s="6">
+        <v>0</v>
+      </c>
+      <c r="D54" s="6">
         <v>1.6190465409437804E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="8">
-        <v>0</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="6">
+        <v>0</v>
+      </c>
+      <c r="B55" s="6">
         <v>54</v>
       </c>
-      <c r="C55" s="8">
-        <v>0</v>
-      </c>
-      <c r="D55" s="8">
+      <c r="C55" s="6">
+        <v>0</v>
+      </c>
+      <c r="D55" s="6">
         <v>1.6556509186476109E-2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="8">
-        <v>0</v>
-      </c>
-      <c r="B56" s="8">
+      <c r="A56" s="6">
+        <v>0</v>
+      </c>
+      <c r="B56" s="6">
         <v>55</v>
       </c>
-      <c r="C56" s="8">
-        <v>0</v>
-      </c>
-      <c r="D56" s="8">
+      <c r="C56" s="6">
+        <v>0</v>
+      </c>
+      <c r="D56" s="6">
         <v>1.691166358586238E-2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="8">
-        <v>0</v>
-      </c>
-      <c r="B57" s="8">
+      <c r="A57" s="6">
+        <v>0</v>
+      </c>
+      <c r="B57" s="6">
         <v>56</v>
       </c>
-      <c r="C57" s="8">
-        <v>0</v>
-      </c>
-      <c r="D57" s="8">
+      <c r="C57" s="6">
+        <v>0</v>
+      </c>
+      <c r="D57" s="6">
         <v>1.7256293006847168E-2</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="8">
-        <v>0</v>
-      </c>
-      <c r="B58" s="8">
+      <c r="A58" s="6">
+        <v>0</v>
+      </c>
+      <c r="B58" s="6">
         <v>57</v>
       </c>
-      <c r="C58" s="8">
-        <v>0</v>
-      </c>
-      <c r="D58" s="8">
+      <c r="C58" s="6">
+        <v>0</v>
+      </c>
+      <c r="D58" s="6">
         <v>1.759075638602825E-2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="8">
-        <v>0</v>
-      </c>
-      <c r="B59" s="8">
+      <c r="A59" s="6">
+        <v>0</v>
+      </c>
+      <c r="B59" s="6">
         <v>58</v>
       </c>
-      <c r="C59" s="8">
-        <v>0</v>
-      </c>
-      <c r="D59" s="8">
+      <c r="C59" s="6">
+        <v>0</v>
+      </c>
+      <c r="D59" s="6">
         <v>1.7915405814849628E-2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="8">
-        <v>0</v>
-      </c>
-      <c r="B60" s="8">
+      <c r="A60" s="6">
+        <v>0</v>
+      </c>
+      <c r="B60" s="6">
         <v>59</v>
       </c>
-      <c r="C60" s="8">
-        <v>0</v>
-      </c>
-      <c r="D60" s="8">
+      <c r="C60" s="6">
+        <v>0</v>
+      </c>
+      <c r="D60" s="6">
         <v>1.8230585468377525E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="8">
-        <v>0</v>
-      </c>
-      <c r="B61" s="8">
+      <c r="A61" s="6">
+        <v>0</v>
+      </c>
+      <c r="B61" s="6">
         <v>60</v>
       </c>
-      <c r="C61" s="8">
-        <v>0</v>
-      </c>
-      <c r="D61" s="8">
+      <c r="C61" s="6">
+        <v>0</v>
+      </c>
+      <c r="D61" s="6">
         <v>1.8536630793370756E-2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="8">
-        <v>0</v>
-      </c>
-      <c r="B62" s="8">
+      <c r="A62" s="6">
+        <v>0</v>
+      </c>
+      <c r="B62" s="6">
         <v>61</v>
       </c>
-      <c r="C62" s="8">
-        <v>0</v>
-      </c>
-      <c r="D62" s="8">
+      <c r="C62" s="6">
+        <v>0</v>
+      </c>
+      <c r="D62" s="6">
         <v>1.8833867911915103E-2</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="8">
-        <v>0</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="6">
+        <v>0</v>
+      </c>
+      <c r="B63" s="6">
         <v>62</v>
       </c>
-      <c r="C63" s="8">
-        <v>0</v>
-      </c>
-      <c r="D63" s="8">
+      <c r="C63" s="6">
+        <v>0</v>
+      </c>
+      <c r="D63" s="6">
         <v>1.9122613203806038E-2</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="8">
-        <v>0</v>
-      </c>
-      <c r="B64" s="8">
+      <c r="A64" s="6">
+        <v>0</v>
+      </c>
+      <c r="B64" s="6">
         <v>63</v>
       </c>
-      <c r="C64" s="8">
-        <v>0</v>
-      </c>
-      <c r="D64" s="8">
+      <c r="C64" s="6">
+        <v>0</v>
+      </c>
+      <c r="D64" s="6">
         <v>1.9403173036683707E-2</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="8">
-        <v>0</v>
-      </c>
-      <c r="B65" s="8">
+      <c r="A65" s="6">
+        <v>0</v>
+      </c>
+      <c r="B65" s="6">
         <v>64</v>
       </c>
-      <c r="C65" s="8">
-        <v>0</v>
-      </c>
-      <c r="D65" s="8">
+      <c r="C65" s="6">
+        <v>0</v>
+      </c>
+      <c r="D65" s="6">
         <v>1.9675843617816824E-2</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="8">
-        <v>0</v>
-      </c>
-      <c r="B66" s="8">
+      <c r="A66" s="6">
+        <v>0</v>
+      </c>
+      <c r="B66" s="6">
         <v>65</v>
       </c>
-      <c r="C66" s="8">
-        <v>0</v>
-      </c>
-      <c r="D66" s="8">
+      <c r="C66" s="6">
+        <v>0</v>
+      </c>
+      <c r="D66" s="6">
         <v>1.9940910945556833E-2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="8">
-        <v>0</v>
-      </c>
-      <c r="B67" s="8">
+      <c r="A67" s="6">
+        <v>0</v>
+      </c>
+      <c r="B67" s="6">
         <v>66</v>
       </c>
-      <c r="C67" s="8">
-        <v>0</v>
-      </c>
-      <c r="D67" s="8">
+      <c r="C67" s="6">
+        <v>0</v>
+      </c>
+      <c r="D67" s="6">
         <v>2.019865084195871E-2</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="8">
-        <v>0</v>
-      </c>
-      <c r="B68" s="8">
+      <c r="A68" s="6">
+        <v>0</v>
+      </c>
+      <c r="B68" s="6">
         <v>67</v>
       </c>
-      <c r="C68" s="8">
-        <v>0</v>
-      </c>
-      <c r="D68" s="8">
+      <c r="C68" s="6">
+        <v>0</v>
+      </c>
+      <c r="D68" s="6">
         <v>2.0449329051009046E-2</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="8">
-        <v>0</v>
-      </c>
-      <c r="B69" s="8">
+      <c r="A69" s="6">
+        <v>0</v>
+      </c>
+      <c r="B69" s="6">
         <v>68</v>
       </c>
-      <c r="C69" s="8">
-        <v>0</v>
-      </c>
-      <c r="D69" s="8">
+      <c r="C69" s="6">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6">
         <v>2.0693201389375693E-2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="8">
-        <v>0</v>
-      </c>
-      <c r="B70" s="8">
+      <c r="A70" s="6">
+        <v>0</v>
+      </c>
+      <c r="B70" s="6">
         <v>69</v>
       </c>
-      <c r="C70" s="8">
-        <v>0</v>
-      </c>
-      <c r="D70" s="8">
+      <c r="C70" s="6">
+        <v>0</v>
+      </c>
+      <c r="D70" s="6">
         <v>2.0930513938697271E-2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="8">
-        <v>0</v>
-      </c>
-      <c r="B71" s="8">
+      <c r="A71" s="6">
+        <v>0</v>
+      </c>
+      <c r="B71" s="6">
         <v>70</v>
       </c>
-      <c r="C71" s="8">
-        <v>0</v>
-      </c>
-      <c r="D71" s="8">
+      <c r="C71" s="6">
+        <v>0</v>
+      </c>
+      <c r="D71" s="6">
         <v>2.1161503270206383E-2</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="8">
-        <v>0</v>
-      </c>
-      <c r="B72" s="8">
+      <c r="A72" s="6">
+        <v>0</v>
+      </c>
+      <c r="B72" s="6">
         <v>71</v>
       </c>
-      <c r="C72" s="8">
-        <v>0</v>
-      </c>
-      <c r="D72" s="8">
+      <c r="C72" s="6">
+        <v>0</v>
+      </c>
+      <c r="D72" s="6">
         <v>2.1386396693980902E-2</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="8">
-        <v>0</v>
-      </c>
-      <c r="B73" s="8">
+      <c r="A73" s="6">
+        <v>0</v>
+      </c>
+      <c r="B73" s="6">
         <v>72</v>
       </c>
-      <c r="C73" s="8">
-        <v>0</v>
-      </c>
-      <c r="D73" s="8">
+      <c r="C73" s="6">
+        <v>0</v>
+      </c>
+      <c r="D73" s="6">
         <v>2.1605412526390921E-2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="8">
-        <v>0</v>
-      </c>
-      <c r="B74" s="8">
+      <c r="A74" s="6">
+        <v>0</v>
+      </c>
+      <c r="B74" s="6">
         <v>73</v>
       </c>
-      <c r="C74" s="8">
-        <v>0</v>
-      </c>
-      <c r="D74" s="8">
+      <c r="C74" s="6">
+        <v>0</v>
+      </c>
+      <c r="D74" s="6">
         <v>2.1818760370390544E-2</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="8">
-        <v>0</v>
-      </c>
-      <c r="B75" s="8">
+      <c r="A75" s="6">
+        <v>0</v>
+      </c>
+      <c r="B75" s="6">
         <v>74</v>
       </c>
-      <c r="C75" s="8">
-        <v>0</v>
-      </c>
-      <c r="D75" s="8">
+      <c r="C75" s="6">
+        <v>0</v>
+      </c>
+      <c r="D75" s="6">
         <v>2.2026641404207181E-2</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="8">
-        <v>0</v>
-      </c>
-      <c r="B76" s="8">
+      <c r="A76" s="6">
+        <v>0</v>
+      </c>
+      <c r="B76" s="6">
         <v>75</v>
       </c>
-      <c r="C76" s="8">
-        <v>0</v>
-      </c>
-      <c r="D76" s="8">
+      <c r="C76" s="6">
+        <v>0</v>
+      </c>
+      <c r="D76" s="6">
         <v>2.2229248674763724E-2</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="8">
-        <v>0</v>
-      </c>
-      <c r="B77" s="8">
+      <c r="A77" s="6">
+        <v>0</v>
+      </c>
+      <c r="B77" s="6">
         <v>76</v>
       </c>
-      <c r="C77" s="8">
-        <v>0</v>
-      </c>
-      <c r="D77" s="8">
+      <c r="C77" s="6">
+        <v>0</v>
+      </c>
+      <c r="D77" s="6">
         <v>2.2426767392813352E-2</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="8">
-        <v>0</v>
-      </c>
-      <c r="B78" s="8">
+      <c r="A78" s="6">
+        <v>0</v>
+      </c>
+      <c r="B78" s="6">
         <v>77</v>
       </c>
-      <c r="C78" s="8">
-        <v>0</v>
-      </c>
-      <c r="D78" s="8">
+      <c r="C78" s="6">
+        <v>0</v>
+      </c>
+      <c r="D78" s="6">
         <v>2.2619375227323602E-2</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="8">
-        <v>0</v>
-      </c>
-      <c r="B79" s="8">
+      <c r="A79" s="6">
+        <v>0</v>
+      </c>
+      <c r="B79" s="6">
         <v>78</v>
       </c>
-      <c r="C79" s="8">
-        <v>0</v>
-      </c>
-      <c r="D79" s="8">
+      <c r="C79" s="6">
+        <v>0</v>
+      </c>
+      <c r="D79" s="6">
         <v>2.2807242597112198E-2</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="8">
-        <v>0</v>
-      </c>
-      <c r="B80" s="8">
+      <c r="A80" s="6">
+        <v>0</v>
+      </c>
+      <c r="B80" s="6">
         <v>79</v>
       </c>
-      <c r="C80" s="8">
-        <v>0</v>
-      </c>
-      <c r="D80" s="8">
+      <c r="C80" s="6">
+        <v>0</v>
+      </c>
+      <c r="D80" s="6">
         <v>2.2990532958129695E-2</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="8">
-        <v>0</v>
-      </c>
-      <c r="B81" s="8">
+      <c r="A81" s="6">
+        <v>0</v>
+      </c>
+      <c r="B81" s="6">
         <v>80</v>
       </c>
-      <c r="C81" s="8">
-        <v>0</v>
-      </c>
-      <c r="D81" s="8">
+      <c r="C81" s="6">
+        <v>0</v>
+      </c>
+      <c r="D81" s="6">
         <v>2.3169403085117946E-2</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="8">
-        <v>0</v>
-      </c>
-      <c r="B82" s="8">
+      <c r="A82" s="6">
+        <v>0</v>
+      </c>
+      <c r="B82" s="6">
         <v>81</v>
       </c>
-      <c r="C82" s="8">
-        <v>0</v>
-      </c>
-      <c r="D82" s="8">
+      <c r="C82" s="6">
+        <v>0</v>
+      </c>
+      <c r="D82" s="6">
         <v>2.3344003346649211E-2</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="8">
-        <v>0</v>
-      </c>
-      <c r="B83" s="8">
+      <c r="A83" s="6">
+        <v>0</v>
+      </c>
+      <c r="B83" s="6">
         <v>82</v>
       </c>
-      <c r="C83" s="8">
-        <v>0</v>
-      </c>
-      <c r="D83" s="8">
+      <c r="C83" s="6">
+        <v>0</v>
+      </c>
+      <c r="D83" s="6">
         <v>2.3514477972788494E-2</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="8">
-        <v>0</v>
-      </c>
-      <c r="B84" s="8">
+      <c r="A84" s="6">
+        <v>0</v>
+      </c>
+      <c r="B84" s="6">
         <v>83</v>
       </c>
-      <c r="C84" s="8">
-        <v>0</v>
-      </c>
-      <c r="D84" s="8">
+      <c r="C84" s="6">
+        <v>0</v>
+      </c>
+      <c r="D84" s="6">
         <v>2.3680965314814229E-2</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="8">
-        <v>0</v>
-      </c>
-      <c r="B85" s="8">
+      <c r="A85" s="6">
+        <v>0</v>
+      </c>
+      <c r="B85" s="6">
         <v>84</v>
       </c>
-      <c r="C85" s="8">
-        <v>0</v>
-      </c>
-      <c r="D85" s="8">
+      <c r="C85" s="6">
+        <v>0</v>
+      </c>
+      <c r="D85" s="6">
         <v>2.3843598096600749E-2</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="8">
-        <v>0</v>
-      </c>
-      <c r="B86" s="8">
+      <c r="A86" s="6">
+        <v>0</v>
+      </c>
+      <c r="B86" s="6">
         <v>85</v>
       </c>
-      <c r="C86" s="8">
-        <v>0</v>
-      </c>
-      <c r="D86" s="8">
+      <c r="C86" s="6">
+        <v>0</v>
+      </c>
+      <c r="D86" s="6">
         <v>2.4002503657397423E-2</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="8">
-        <v>0</v>
-      </c>
-      <c r="B87" s="8">
+      <c r="A87" s="6">
+        <v>0</v>
+      </c>
+      <c r="B87" s="6">
         <v>86</v>
       </c>
-      <c r="C87" s="8">
-        <v>0</v>
-      </c>
-      <c r="D87" s="8">
+      <c r="C87" s="6">
+        <v>0</v>
+      </c>
+      <c r="D87" s="6">
         <v>2.4157804185853005E-2</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="8">
-        <v>0</v>
-      </c>
-      <c r="B88" s="8">
+      <c r="A88" s="6">
+        <v>0</v>
+      </c>
+      <c r="B88" s="6">
         <v>87</v>
       </c>
-      <c r="C88" s="8">
-        <v>0</v>
-      </c>
-      <c r="D88" s="8">
+      <c r="C88" s="6">
+        <v>0</v>
+      </c>
+      <c r="D88" s="6">
         <v>2.4309616945233259E-2</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="8">
-        <v>0</v>
-      </c>
-      <c r="B89" s="8">
+      <c r="A89" s="6">
+        <v>0</v>
+      </c>
+      <c r="B89" s="6">
         <v>88</v>
       </c>
-      <c r="C89" s="8">
-        <v>0</v>
-      </c>
-      <c r="D89" s="8">
+      <c r="C89" s="6">
+        <v>0</v>
+      </c>
+      <c r="D89" s="6">
         <v>2.4458054489842951E-2</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="8">
-        <v>0</v>
-      </c>
-      <c r="B90" s="8">
+      <c r="A90" s="6">
+        <v>0</v>
+      </c>
+      <c r="B90" s="6">
         <v>89</v>
       </c>
-      <c r="C90" s="8">
-        <v>0</v>
-      </c>
-      <c r="D90" s="8">
+      <c r="C90" s="6">
+        <v>0</v>
+      </c>
+      <c r="D90" s="6">
         <v>2.4603224872740137E-2</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="8">
-        <v>0</v>
-      </c>
-      <c r="B91" s="8">
+      <c r="A91" s="6">
+        <v>0</v>
+      </c>
+      <c r="B91" s="6">
         <v>90</v>
       </c>
-      <c r="C91" s="8">
-        <v>0</v>
-      </c>
-      <c r="D91" s="8">
+      <c r="C91" s="6">
+        <v>0</v>
+      </c>
+      <c r="D91" s="6">
         <v>2.4745231844867099E-2</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="8">
-        <v>0</v>
-      </c>
-      <c r="B92" s="8">
+      <c r="A92" s="6">
+        <v>0</v>
+      </c>
+      <c r="B92" s="6">
         <v>91</v>
       </c>
-      <c r="C92" s="8">
-        <v>0</v>
-      </c>
-      <c r="D92" s="8">
+      <c r="C92" s="6">
+        <v>0</v>
+      </c>
+      <c r="D92" s="6">
         <v>2.4884175045773116E-2</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="8">
-        <v>0</v>
-      </c>
-      <c r="B93" s="8">
+      <c r="A93" s="6">
+        <v>0</v>
+      </c>
+      <c r="B93" s="6">
         <v>92</v>
       </c>
-      <c r="C93" s="8">
-        <v>0</v>
-      </c>
-      <c r="D93" s="8">
+      <c r="C93" s="6">
+        <v>0</v>
+      </c>
+      <c r="D93" s="6">
         <v>2.5020150186124246E-2</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="8">
-        <v>0</v>
-      </c>
-      <c r="B94" s="8">
+      <c r="A94" s="6">
+        <v>0</v>
+      </c>
+      <c r="B94" s="6">
         <v>93</v>
       </c>
-      <c r="C94" s="8">
-        <v>0</v>
-      </c>
-      <c r="D94" s="8">
+      <c r="C94" s="6">
+        <v>0</v>
+      </c>
+      <c r="D94" s="6">
         <v>2.5153249222228835E-2</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="8">
-        <v>0</v>
-      </c>
-      <c r="B95" s="8">
+      <c r="A95" s="6">
+        <v>0</v>
+      </c>
+      <c r="B95" s="6">
         <v>94</v>
       </c>
-      <c r="C95" s="8">
-        <v>0</v>
-      </c>
-      <c r="D95" s="8">
+      <c r="C95" s="6">
+        <v>0</v>
+      </c>
+      <c r="D95" s="6">
         <v>2.5283560522819881E-2</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="8">
-        <v>0</v>
-      </c>
-      <c r="B96" s="8">
+      <c r="A96" s="6">
+        <v>0</v>
+      </c>
+      <c r="B96" s="6">
         <v>95</v>
       </c>
-      <c r="C96" s="8">
-        <v>0</v>
-      </c>
-      <c r="D96" s="8">
+      <c r="C96" s="6">
+        <v>0</v>
+      </c>
+      <c r="D96" s="6">
         <v>2.5411169028346281E-2</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="8">
-        <v>0</v>
-      </c>
-      <c r="B97" s="8">
+      <c r="A97" s="6">
+        <v>0</v>
+      </c>
+      <c r="B97" s="6">
         <v>96</v>
       </c>
-      <c r="C97" s="8">
-        <v>0</v>
-      </c>
-      <c r="D97" s="8">
+      <c r="C97" s="6">
+        <v>0</v>
+      </c>
+      <c r="D97" s="6">
         <v>2.5536156403038746E-2</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="8">
-        <v>0</v>
-      </c>
-      <c r="B98" s="8">
+      <c r="A98" s="6">
+        <v>0</v>
+      </c>
+      <c r="B98" s="6">
         <v>97</v>
       </c>
-      <c r="C98" s="8">
-        <v>0</v>
-      </c>
-      <c r="D98" s="8">
+      <c r="C98" s="6">
+        <v>0</v>
+      </c>
+      <c r="D98" s="6">
         <v>2.5658601180016616E-2</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="8">
-        <v>0</v>
-      </c>
-      <c r="B99" s="8">
+      <c r="A99" s="6">
+        <v>0</v>
+      </c>
+      <c r="B99" s="6">
         <v>98</v>
       </c>
-      <c r="C99" s="8">
-        <v>0</v>
-      </c>
-      <c r="D99" s="8">
+      <c r="C99" s="6">
+        <v>0</v>
+      </c>
+      <c r="D99" s="6">
         <v>2.5778578899704474E-2</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="8">
-        <v>0</v>
-      </c>
-      <c r="B100" s="8">
+      <c r="A100" s="6">
+        <v>0</v>
+      </c>
+      <c r="B100" s="6">
         <v>99</v>
       </c>
-      <c r="C100" s="8">
-        <v>0</v>
-      </c>
-      <c r="D100" s="8">
+      <c r="C100" s="6">
+        <v>0</v>
+      </c>
+      <c r="D100" s="6">
         <v>2.5896162241828113E-2</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="8">
-        <v>0</v>
-      </c>
-      <c r="B101" s="8">
+      <c r="A101" s="6">
+        <v>0</v>
+      </c>
+      <c r="B101" s="6">
         <v>100</v>
       </c>
-      <c r="C101" s="8">
-        <v>0</v>
-      </c>
-      <c r="D101" s="8">
+      <c r="C101" s="6">
+        <v>0</v>
+      </c>
+      <c r="D101" s="6">
         <v>2.6011421151256098E-2</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="8">
-        <v>0</v>
-      </c>
-      <c r="B102" s="8">
+      <c r="A102" s="6">
+        <v>0</v>
+      </c>
+      <c r="B102" s="6">
         <v>101</v>
       </c>
-      <c r="C102" s="8">
-        <v>0</v>
-      </c>
-      <c r="D102" s="8">
+      <c r="C102" s="6">
+        <v>0</v>
+      </c>
+      <c r="D102" s="6">
         <v>2.6124422957949811E-2</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="8">
-        <v>0</v>
-      </c>
-      <c r="B103" s="8">
+      <c r="A103" s="6">
+        <v>0</v>
+      </c>
+      <c r="B103" s="6">
         <v>102</v>
       </c>
-      <c r="C103" s="8">
-        <v>0</v>
-      </c>
-      <c r="D103" s="8">
+      <c r="C103" s="6">
+        <v>0</v>
+      </c>
+      <c r="D103" s="6">
         <v>2.6235232491277127E-2</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="8">
-        <v>0</v>
-      </c>
-      <c r="B104" s="8">
+      <c r="A104" s="6">
+        <v>0</v>
+      </c>
+      <c r="B104" s="6">
         <v>103</v>
       </c>
-      <c r="C104" s="8">
-        <v>0</v>
-      </c>
-      <c r="D104" s="8">
+      <c r="C104" s="6">
+        <v>0</v>
+      </c>
+      <c r="D104" s="6">
         <v>2.6343912188943941E-2</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="8">
-        <v>0</v>
-      </c>
-      <c r="B105" s="8">
+      <c r="A105" s="6">
+        <v>0</v>
+      </c>
+      <c r="B105" s="6">
         <v>104</v>
       </c>
-      <c r="C105" s="8">
-        <v>0</v>
-      </c>
-      <c r="D105" s="8">
+      <c r="C105" s="6">
+        <v>0</v>
+      </c>
+      <c r="D105" s="6">
         <v>2.64505222007827E-2</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="8">
-        <v>0</v>
-      </c>
-      <c r="B106" s="8">
+      <c r="A106" s="6">
+        <v>0</v>
+      </c>
+      <c r="B106" s="6">
         <v>105</v>
       </c>
-      <c r="C106" s="8">
-        <v>0</v>
-      </c>
-      <c r="D106" s="8">
+      <c r="C106" s="6">
+        <v>0</v>
+      </c>
+      <c r="D106" s="6">
         <v>2.6555120487640194E-2</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="8">
-        <v>0</v>
-      </c>
-      <c r="B107" s="8">
+      <c r="A107" s="6">
+        <v>0</v>
+      </c>
+      <c r="B107" s="6">
         <v>106</v>
       </c>
-      <c r="C107" s="8">
-        <v>0</v>
-      </c>
-      <c r="D107" s="8">
+      <c r="C107" s="6">
+        <v>0</v>
+      </c>
+      <c r="D107" s="6">
         <v>2.665776291558819E-2</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="8">
-        <v>0</v>
-      </c>
-      <c r="B108" s="8">
+      <c r="A108" s="6">
+        <v>0</v>
+      </c>
+      <c r="B108" s="6">
         <v>107</v>
       </c>
-      <c r="C108" s="8">
-        <v>0</v>
-      </c>
-      <c r="D108" s="8">
+      <c r="C108" s="6">
+        <v>0</v>
+      </c>
+      <c r="D108" s="6">
         <v>2.6758503345678752E-2</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="8">
-        <v>0</v>
-      </c>
-      <c r="B109" s="8">
+      <c r="A109" s="6">
+        <v>0</v>
+      </c>
+      <c r="B109" s="6">
         <v>108</v>
       </c>
-      <c r="C109" s="8">
-        <v>0</v>
-      </c>
-      <c r="D109" s="8">
+      <c r="C109" s="6">
+        <v>0</v>
+      </c>
+      <c r="D109" s="6">
         <v>2.6857393719457612E-2</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="8">
-        <v>0</v>
-      </c>
-      <c r="B110" s="8">
+      <c r="A110" s="6">
+        <v>0</v>
+      </c>
+      <c r="B110" s="6">
         <v>109</v>
       </c>
-      <c r="C110" s="8">
-        <v>0</v>
-      </c>
-      <c r="D110" s="8">
+      <c r="C110" s="6">
+        <v>0</v>
+      </c>
+      <c r="D110" s="6">
         <v>2.6954484140437218E-2</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="8">
-        <v>0</v>
-      </c>
-      <c r="B111" s="8">
+      <c r="A111" s="6">
+        <v>0</v>
+      </c>
+      <c r="B111" s="6">
         <v>110</v>
       </c>
-      <c r="C111" s="8">
-        <v>0</v>
-      </c>
-      <c r="D111" s="8">
+      <c r="C111" s="6">
+        <v>0</v>
+      </c>
+      <c r="D111" s="6">
         <v>2.7049822951725311E-2</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="8">
-        <v>0</v>
-      </c>
-      <c r="B112" s="8">
+      <c r="A112" s="6">
+        <v>0</v>
+      </c>
+      <c r="B112" s="6">
         <v>111</v>
       </c>
-      <c r="C112" s="8">
-        <v>0</v>
-      </c>
-      <c r="D112" s="8">
+      <c r="C112" s="6">
+        <v>0</v>
+      </c>
+      <c r="D112" s="6">
         <v>2.7143456809996191E-2</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="8">
-        <v>0</v>
-      </c>
-      <c r="B113" s="8">
+      <c r="A113" s="6">
+        <v>0</v>
+      </c>
+      <c r="B113" s="6">
         <v>112</v>
       </c>
-      <c r="C113" s="8">
-        <v>0</v>
-      </c>
-      <c r="D113" s="8">
+      <c r="C113" s="6">
+        <v>0</v>
+      </c>
+      <c r="D113" s="6">
         <v>2.7235430755983003E-2</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="8">
-        <v>0</v>
-      </c>
-      <c r="B114" s="8">
+      <c r="A114" s="6">
+        <v>0</v>
+      </c>
+      <c r="B114" s="6">
         <v>113</v>
       </c>
-      <c r="C114" s="8">
-        <v>0</v>
-      </c>
-      <c r="D114" s="8">
+      <c r="C114" s="6">
+        <v>0</v>
+      </c>
+      <c r="D114" s="6">
         <v>2.7325788281662433E-2</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="8">
-        <v>0</v>
-      </c>
-      <c r="B115" s="8">
+      <c r="A115" s="6">
+        <v>0</v>
+      </c>
+      <c r="B115" s="6">
         <v>114</v>
       </c>
-      <c r="C115" s="8">
-        <v>0</v>
-      </c>
-      <c r="D115" s="8">
+      <c r="C115" s="6">
+        <v>0</v>
+      </c>
+      <c r="D115" s="6">
         <v>2.7414571394293707E-2</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="8">
-        <v>0</v>
-      </c>
-      <c r="B116" s="8">
+      <c r="A116" s="6">
+        <v>0</v>
+      </c>
+      <c r="B116" s="6">
         <v>115</v>
       </c>
-      <c r="C116" s="8">
-        <v>0</v>
-      </c>
-      <c r="D116" s="8">
+      <c r="C116" s="6">
+        <v>0</v>
+      </c>
+      <c r="D116" s="6">
         <v>2.7501820677467759E-2</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="8">
-        <v>0</v>
-      </c>
-      <c r="B117" s="8">
+      <c r="A117" s="6">
+        <v>0</v>
+      </c>
+      <c r="B117" s="6">
         <v>116</v>
       </c>
-      <c r="C117" s="8">
-        <v>0</v>
-      </c>
-      <c r="D117" s="8">
+      <c r="C117" s="6">
+        <v>0</v>
+      </c>
+      <c r="D117" s="6">
         <v>2.7587575349314886E-2</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="8">
-        <v>0</v>
-      </c>
-      <c r="B118" s="8">
+      <c r="A118" s="6">
+        <v>0</v>
+      </c>
+      <c r="B118" s="6">
         <v>117</v>
       </c>
-      <c r="C118" s="8">
-        <v>0</v>
-      </c>
-      <c r="D118" s="8">
+      <c r="C118" s="6">
+        <v>0</v>
+      </c>
+      <c r="D118" s="6">
         <v>2.7671873318010798E-2</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="8">
-        <v>0</v>
-      </c>
-      <c r="B119" s="8">
+      <c r="A119" s="6">
+        <v>0</v>
+      </c>
+      <c r="B119" s="6">
         <v>118</v>
       </c>
-      <c r="C119" s="8">
-        <v>0</v>
-      </c>
-      <c r="D119" s="8">
+      <c r="C119" s="6">
+        <v>0</v>
+      </c>
+      <c r="D119" s="6">
         <v>2.7754751234716935E-2</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="8">
-        <v>0</v>
-      </c>
-      <c r="B120" s="8">
+      <c r="A120" s="6">
+        <v>0</v>
+      </c>
+      <c r="B120" s="6">
         <v>119</v>
       </c>
-      <c r="C120" s="8">
-        <v>0</v>
-      </c>
-      <c r="D120" s="8">
+      <c r="C120" s="6">
+        <v>0</v>
+      </c>
+      <c r="D120" s="6">
         <v>2.7836244544079847E-2</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="8">
-        <v>0</v>
-      </c>
-      <c r="B121" s="8">
+      <c r="A121" s="6">
+        <v>0</v>
+      </c>
+      <c r="B121" s="6">
         <v>120</v>
       </c>
-      <c r="C121" s="8">
-        <v>0</v>
-      </c>
-      <c r="D121" s="8">
+      <c r="C121" s="6">
+        <v>0</v>
+      </c>
+      <c r="D121" s="6">
         <v>2.7916387532413101E-2</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="8">
-        <v>0</v>
-      </c>
-      <c r="B122" s="8">
+      <c r="A122" s="6">
+        <v>0</v>
+      </c>
+      <c r="B122" s="6">
         <v>121</v>
       </c>
-      <c r="C122" s="8">
-        <v>0</v>
-      </c>
-      <c r="D122" s="8">
+      <c r="C122" s="6">
+        <v>0</v>
+      </c>
+      <c r="D122" s="6">
         <v>2.7995213373676275E-2</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="8">
-        <v>0</v>
-      </c>
-      <c r="B123" s="8">
+      <c r="A123" s="6">
+        <v>0</v>
+      </c>
+      <c r="B123" s="6">
         <v>122</v>
       </c>
-      <c r="C123" s="8">
-        <v>0</v>
-      </c>
-      <c r="D123" s="8">
+      <c r="C123" s="6">
+        <v>0</v>
+      </c>
+      <c r="D123" s="6">
         <v>2.8072754173359415E-2</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="8">
-        <v>0</v>
-      </c>
-      <c r="B124" s="8">
+      <c r="A124" s="6">
+        <v>0</v>
+      </c>
+      <c r="B124" s="6">
         <v>123</v>
       </c>
-      <c r="C124" s="8">
-        <v>0</v>
-      </c>
-      <c r="D124" s="8">
+      <c r="C124" s="6">
+        <v>0</v>
+      </c>
+      <c r="D124" s="6">
         <v>2.8149041010377518E-2</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="8">
-        <v>0</v>
-      </c>
-      <c r="B125" s="8">
+      <c r="A125" s="6">
+        <v>0</v>
+      </c>
+      <c r="B125" s="6">
         <v>124</v>
       </c>
-      <c r="C125" s="8">
-        <v>0</v>
-      </c>
-      <c r="D125" s="8">
+      <c r="C125" s="6">
+        <v>0</v>
+      </c>
+      <c r="D125" s="6">
         <v>2.8224103977074533E-2</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="8">
-        <v>0</v>
-      </c>
-      <c r="B126" s="8">
+      <c r="A126" s="6">
+        <v>0</v>
+      </c>
+      <c r="B126" s="6">
         <v>125</v>
       </c>
-      <c r="C126" s="8">
-        <v>0</v>
-      </c>
-      <c r="D126" s="8">
+      <c r="C126" s="6">
+        <v>0</v>
+      </c>
+      <c r="D126" s="6">
         <v>2.8297972217427692E-2</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="8">
-        <v>0</v>
-      </c>
-      <c r="B127" s="8">
+      <c r="A127" s="6">
+        <v>0</v>
+      </c>
+      <c r="B127" s="6">
         <v>126</v>
       </c>
-      <c r="C127" s="8">
-        <v>0</v>
-      </c>
-      <c r="D127" s="8">
+      <c r="C127" s="6">
+        <v>0</v>
+      </c>
+      <c r="D127" s="6">
         <v>2.8370673963544757E-2</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="8">
-        <v>0</v>
-      </c>
-      <c r="B128" s="8">
+      <c r="A128" s="6">
+        <v>0</v>
+      </c>
+      <c r="B128" s="6">
         <v>127</v>
       </c>
-      <c r="C128" s="8">
-        <v>0</v>
-      </c>
-      <c r="D128" s="8">
+      <c r="C128" s="6">
+        <v>0</v>
+      </c>
+      <c r="D128" s="6">
         <v>2.8442236570533463E-2</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="8">
-        <v>0</v>
-      </c>
-      <c r="B129" s="8">
+      <c r="A129" s="6">
+        <v>0</v>
+      </c>
+      <c r="B129" s="6">
         <v>128</v>
       </c>
-      <c r="C129" s="8">
-        <v>0</v>
-      </c>
-      <c r="D129" s="8">
+      <c r="C129" s="6">
+        <v>0</v>
+      </c>
+      <c r="D129" s="6">
         <v>2.8512686549828858E-2</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="8">
-        <v>0</v>
-      </c>
-      <c r="B130" s="8">
+      <c r="A130" s="6">
+        <v>0</v>
+      </c>
+      <c r="B130" s="6">
         <v>129</v>
       </c>
-      <c r="C130" s="8">
-        <v>0</v>
-      </c>
-      <c r="D130" s="8">
+      <c r="C130" s="6">
+        <v>0</v>
+      </c>
+      <c r="D130" s="6">
         <v>2.8582049601048487E-2</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="8">
-        <v>0</v>
-      </c>
-      <c r="B131" s="8">
+      <c r="A131" s="6">
+        <v>0</v>
+      </c>
+      <c r="B131" s="6">
         <v>130</v>
       </c>
-      <c r="C131" s="8">
-        <v>0</v>
-      </c>
-      <c r="D131" s="8">
+      <c r="C131" s="6">
+        <v>0</v>
+      </c>
+      <c r="D131" s="6">
         <v>2.8650350642451139E-2</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="8">
-        <v>0</v>
-      </c>
-      <c r="B132" s="8">
+      <c r="A132" s="6">
+        <v>0</v>
+      </c>
+      <c r="B132" s="6">
         <v>131</v>
       </c>
-      <c r="C132" s="8">
-        <v>0</v>
-      </c>
-      <c r="D132" s="8">
+      <c r="C132" s="6">
+        <v>0</v>
+      </c>
+      <c r="D132" s="6">
         <v>2.871761384006688E-2</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="8">
-        <v>0</v>
-      </c>
-      <c r="B133" s="8">
+      <c r="A133" s="6">
+        <v>0</v>
+      </c>
+      <c r="B133" s="6">
         <v>132</v>
       </c>
-      <c r="C133" s="8">
-        <v>0</v>
-      </c>
-      <c r="D133" s="8">
+      <c r="C133" s="6">
+        <v>0</v>
+      </c>
+      <c r="D133" s="6">
         <v>2.8783862635559432E-2</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="8">
-        <v>0</v>
-      </c>
-      <c r="B134" s="8">
+      <c r="A134" s="6">
+        <v>0</v>
+      </c>
+      <c r="B134" s="6">
         <v>133</v>
       </c>
-      <c r="C134" s="8">
-        <v>0</v>
-      </c>
-      <c r="D134" s="8">
+      <c r="C134" s="6">
+        <v>0</v>
+      </c>
+      <c r="D134" s="6">
         <v>2.8849119772888399E-2</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="8">
-        <v>0</v>
-      </c>
-      <c r="B135" s="8">
+      <c r="A135" s="6">
+        <v>0</v>
+      </c>
+      <c r="B135" s="6">
         <v>134</v>
       </c>
-      <c r="C135" s="8">
-        <v>0</v>
-      </c>
-      <c r="D135" s="8">
+      <c r="C135" s="6">
+        <v>0</v>
+      </c>
+      <c r="D135" s="6">
         <v>2.8913407323822193E-2</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="8">
-        <v>0</v>
-      </c>
-      <c r="B136" s="8">
+      <c r="A136" s="6">
+        <v>0</v>
+      </c>
+      <c r="B136" s="6">
         <v>135</v>
       </c>
-      <c r="C136" s="8">
-        <v>0</v>
-      </c>
-      <c r="D136" s="8">
+      <c r="C136" s="6">
+        <v>0</v>
+      </c>
+      <c r="D136" s="6">
         <v>2.8976746712363832E-2</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="8">
-        <v>0</v>
-      </c>
-      <c r="B137" s="8">
+      <c r="A137" s="6">
+        <v>0</v>
+      </c>
+      <c r="B137" s="6">
         <v>136</v>
       </c>
-      <c r="C137" s="8">
-        <v>0</v>
-      </c>
-      <c r="D137" s="8">
+      <c r="C137" s="6">
+        <v>0</v>
+      </c>
+      <c r="D137" s="6">
         <v>2.9039158738135784E-2</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="8">
-        <v>0</v>
-      </c>
-      <c r="B138" s="8">
+      <c r="A138" s="6">
+        <v>0</v>
+      </c>
+      <c r="B138" s="6">
         <v>137</v>
       </c>
-      <c r="C138" s="8">
-        <v>0</v>
-      </c>
-      <c r="D138" s="8">
+      <c r="C138" s="6">
+        <v>0</v>
+      </c>
+      <c r="D138" s="6">
         <v>2.9100663598777388E-2</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="8">
-        <v>0</v>
-      </c>
-      <c r="B139" s="8">
+      <c r="A139" s="6">
+        <v>0</v>
+      </c>
+      <c r="B139" s="6">
         <v>138</v>
       </c>
-      <c r="C139" s="8">
-        <v>0</v>
-      </c>
-      <c r="D139" s="8">
+      <c r="C139" s="6">
+        <v>0</v>
+      </c>
+      <c r="D139" s="6">
         <v>2.9161280911400578E-2</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="8">
-        <v>0</v>
-      </c>
-      <c r="B140" s="8">
+      <c r="A140" s="6">
+        <v>0</v>
+      </c>
+      <c r="B140" s="6">
         <v>139</v>
       </c>
-      <c r="C140" s="8">
-        <v>0</v>
-      </c>
-      <c r="D140" s="8">
+      <c r="C140" s="6">
+        <v>0</v>
+      </c>
+      <c r="D140" s="6">
         <v>2.9221029733147441E-2</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="8">
-        <v>0</v>
-      </c>
-      <c r="B141" s="8">
+      <c r="A141" s="6">
+        <v>0</v>
+      </c>
+      <c r="B141" s="6">
         <v>140</v>
       </c>
-      <c r="C141" s="8">
-        <v>0</v>
-      </c>
-      <c r="D141" s="8">
+      <c r="C141" s="6">
+        <v>0</v>
+      </c>
+      <c r="D141" s="6">
         <v>2.927992858089401E-2</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="8">
-        <v>0</v>
-      </c>
-      <c r="B142" s="8">
+      <c r="A142" s="6">
+        <v>0</v>
+      </c>
+      <c r="B142" s="6">
         <v>141</v>
       </c>
-      <c r="C142" s="8">
-        <v>0</v>
-      </c>
-      <c r="D142" s="8">
+      <c r="C142" s="6">
+        <v>0</v>
+      </c>
+      <c r="D142" s="6">
         <v>2.9337995450139154E-2</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="8">
-        <v>0</v>
-      </c>
-      <c r="B143" s="8">
+      <c r="A143" s="6">
+        <v>0</v>
+      </c>
+      <c r="B143" s="6">
         <v>142</v>
       </c>
-      <c r="C143" s="8">
-        <v>0</v>
-      </c>
-      <c r="D143" s="8">
+      <c r="C143" s="6">
+        <v>0</v>
+      </c>
+      <c r="D143" s="6">
         <v>2.9395247833115423E-2</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="8">
-        <v>0</v>
-      </c>
-      <c r="B144" s="8">
+      <c r="A144" s="6">
+        <v>0</v>
+      </c>
+      <c r="B144" s="6">
         <v>143</v>
       </c>
-      <c r="C144" s="8">
-        <v>0</v>
-      </c>
-      <c r="D144" s="8">
+      <c r="C144" s="6">
+        <v>0</v>
+      </c>
+      <c r="D144" s="6">
         <v>2.9451702736162044E-2</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="8">
-        <v>0</v>
-      </c>
-      <c r="B145" s="8">
+      <c r="A145" s="6">
+        <v>0</v>
+      </c>
+      <c r="B145" s="6">
         <v>144</v>
       </c>
-      <c r="C145" s="8">
-        <v>0</v>
-      </c>
-      <c r="D145" s="8">
+      <c r="C145" s="6">
+        <v>0</v>
+      </c>
+      <c r="D145" s="6">
         <v>2.9507376696388254E-2</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="8">
-        <v>0</v>
-      </c>
-      <c r="B146" s="8">
+      <c r="A146" s="6">
+        <v>0</v>
+      </c>
+      <c r="B146" s="6">
         <v>145</v>
       </c>
-      <c r="C146" s="8">
-        <v>0</v>
-      </c>
-      <c r="D146" s="8">
+      <c r="C146" s="6">
+        <v>0</v>
+      </c>
+      <c r="D146" s="6">
         <v>2.9562285797666732E-2</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="8">
-        <v>0</v>
-      </c>
-      <c r="B147" s="8">
+      <c r="A147" s="6">
+        <v>0</v>
+      </c>
+      <c r="B147" s="6">
         <v>146</v>
       </c>
-      <c r="C147" s="8">
-        <v>0</v>
-      </c>
-      <c r="D147" s="8">
+      <c r="C147" s="6">
+        <v>0</v>
+      </c>
+      <c r="D147" s="6">
         <v>2.9616445685981319E-2</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="8">
-        <v>0</v>
-      </c>
-      <c r="B148" s="8">
+      <c r="A148" s="6">
+        <v>0</v>
+      </c>
+      <c r="B148" s="6">
         <v>147</v>
       </c>
-      <c r="C148" s="8">
-        <v>0</v>
-      </c>
-      <c r="D148" s="8">
+      <c r="C148" s="6">
+        <v>0</v>
+      </c>
+      <c r="D148" s="6">
         <v>2.9669871584162344E-2</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="8">
-        <v>0</v>
-      </c>
-      <c r="B149" s="8">
+      <c r="A149" s="6">
+        <v>0</v>
+      </c>
+      <c r="B149" s="6">
         <v>148</v>
       </c>
-      <c r="C149" s="8">
-        <v>0</v>
-      </c>
-      <c r="D149" s="8">
+      <c r="C149" s="6">
+        <v>0</v>
+      </c>
+      <c r="D149" s="6">
         <v>2.9722578306037306E-2</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="8">
-        <v>0</v>
-      </c>
-      <c r="B150" s="8">
+      <c r="A150" s="6">
+        <v>0</v>
+      </c>
+      <c r="B150" s="6">
         <v>149</v>
       </c>
-      <c r="C150" s="8">
-        <v>0</v>
-      </c>
-      <c r="D150" s="8">
+      <c r="C150" s="6">
+        <v>0</v>
+      </c>
+      <c r="D150" s="6">
         <v>2.9774580270021778E-2</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="8">
-        <v>0</v>
-      </c>
-      <c r="B151" s="8">
+      <c r="A151" s="6">
+        <v>0</v>
+      </c>
+      <c r="B151" s="6">
         <v>150</v>
       </c>
-      <c r="C151" s="8">
-        <v>0</v>
-      </c>
-      <c r="D151" s="8">
+      <c r="C151" s="6">
+        <v>0</v>
+      </c>
+      <c r="D151" s="6">
         <v>2.9825891512175629E-2</v>
       </c>
     </row>
@@ -10231,573 +10269,574 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE47FA15-E43F-4DFC-8DA2-6C359667E5B8}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="12" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="1" width="6.33203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>9.2496718772093669E-3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>1.0589694258098003E-2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>1.1032270549913577E-2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>1.1044292518813812E-2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <v>1</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>1.3788334788232146E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <v>1</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>6</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>1.6944242364738148E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>1</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>7</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>1.8429378313447282E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>1</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>8</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>1.8642466810056619E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>9</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>2.0102347240970622E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>10</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <v>2.1872288777203999E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>0</v>
-      </c>
-      <c r="B12" s="8">
+      <c r="A12" s="6">
+        <v>0</v>
+      </c>
+      <c r="B12" s="6">
         <v>11</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <v>2.2981233811356312E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>1</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>12</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="6">
         <v>2.4615215165166154E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>0</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="A14" s="6">
+        <v>0</v>
+      </c>
+      <c r="B14" s="6">
         <v>13</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>2.5867811793301054E-2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>0</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="6">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6">
         <v>14</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <v>2.6940024191389973E-2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>1</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>15</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>2.7786457864007751E-2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>0</v>
-      </c>
-      <c r="B17" s="8">
+      <c r="A17" s="6">
+        <v>0</v>
+      </c>
+      <c r="B17" s="6">
         <v>16</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>2.7961998837721332E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>0</v>
-      </c>
-      <c r="B18" s="8">
+      <c r="A18" s="6">
+        <v>0</v>
+      </c>
+      <c r="B18" s="6">
         <v>17</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
         <v>2.8432307445889947E-2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>0</v>
-      </c>
-      <c r="B19" s="8">
+      <c r="A19" s="6">
+        <v>0</v>
+      </c>
+      <c r="B19" s="6">
         <v>18</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="6">
         <v>2.8665104618739178E-2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>0</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="A20" s="6">
+        <v>0</v>
+      </c>
+      <c r="B20" s="6">
         <v>19</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="6">
         <v>2.8956926872526014E-2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <v>1</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="6">
         <v>20</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="6">
         <v>2.9492299797021254E-2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>0</v>
-      </c>
-      <c r="B22" s="8">
+      <c r="A22" s="6">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6">
         <v>21</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>3.0425194965994863E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>0</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="6">
+        <v>0</v>
+      </c>
+      <c r="B23" s="6">
         <v>22</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="6">
         <v>3.0899262864683863E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
-        <v>0</v>
-      </c>
-      <c r="B24" s="8">
+      <c r="A24" s="6">
+        <v>0</v>
+      </c>
+      <c r="B24" s="6">
         <v>23</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="6">
         <v>3.1509179791222114E-2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
-        <v>0</v>
-      </c>
-      <c r="B25" s="8">
+      <c r="A25" s="6">
+        <v>0</v>
+      </c>
+      <c r="B25" s="6">
         <v>24</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>3.2274458320078969E-2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>0</v>
-      </c>
-      <c r="B26" s="8">
+      <c r="A26" s="6">
+        <v>0</v>
+      </c>
+      <c r="B26" s="6">
         <v>25</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <v>3.3004411020988313E-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
-        <v>0</v>
-      </c>
-      <c r="B27" s="8">
+      <c r="A27" s="6">
+        <v>0</v>
+      </c>
+      <c r="B27" s="6">
         <v>26</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="6">
         <v>3.349589889482734E-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
-        <v>0</v>
-      </c>
-      <c r="B28" s="8">
+      <c r="A28" s="6">
+        <v>0</v>
+      </c>
+      <c r="B28" s="6">
         <v>27</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="6">
         <v>3.3780265686537352E-2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>0</v>
-      </c>
-      <c r="B29" s="8">
+      <c r="A29" s="6">
+        <v>0</v>
+      </c>
+      <c r="B29" s="6">
         <v>28</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="6">
         <v>3.4466641415851526E-2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>0</v>
-      </c>
-      <c r="B30" s="8">
+      <c r="A30" s="6">
+        <v>0</v>
+      </c>
+      <c r="B30" s="6">
         <v>29</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="6">
         <v>3.4588648213692223E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
-        <v>0</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="6">
+        <v>0</v>
+      </c>
+      <c r="B31" s="6">
         <v>30</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="6">
         <v>3.4633928585448177E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
-        <v>0</v>
-      </c>
-      <c r="B32" s="8">
+      <c r="A32" s="6">
+        <v>0</v>
+      </c>
+      <c r="B32" s="6">
         <v>31</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="6">
         <v>3.4923272597156385E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
-        <v>0</v>
-      </c>
-      <c r="B33" s="8">
+      <c r="A33" s="6">
+        <v>0</v>
+      </c>
+      <c r="B33" s="6">
         <v>32</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="6">
         <v>3.541116892193058E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
-        <v>0</v>
-      </c>
-      <c r="B34" s="8">
+      <c r="A34" s="6">
+        <v>0</v>
+      </c>
+      <c r="B34" s="6">
         <v>33</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="6">
         <v>3.5713706153336522E-2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
-        <v>0</v>
-      </c>
-      <c r="B35" s="8">
+      <c r="A35" s="6">
+        <v>0</v>
+      </c>
+      <c r="B35" s="6">
         <v>34</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="6">
         <v>3.6297765136776385E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
-        <v>0</v>
-      </c>
-      <c r="B36" s="8">
+      <c r="A36" s="6">
+        <v>0</v>
+      </c>
+      <c r="B36" s="6">
         <v>35</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="6">
         <v>3.6464062868989157E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
-        <v>0</v>
-      </c>
-      <c r="B37" s="8">
+      <c r="A37" s="6">
+        <v>0</v>
+      </c>
+      <c r="B37" s="6">
         <v>36</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="6">
         <v>3.6835715037200692E-2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
-        <v>0</v>
-      </c>
-      <c r="B38" s="8">
+      <c r="A38" s="6">
+        <v>0</v>
+      </c>
+      <c r="B38" s="6">
         <v>37</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="6">
         <v>3.7061412798874274E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
-        <v>0</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="6">
+        <v>0</v>
+      </c>
+      <c r="B39" s="6">
         <v>38</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="6">
         <v>3.7461684848288324E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="8">
-        <v>0</v>
-      </c>
-      <c r="B40" s="8">
+      <c r="A40" s="6">
+        <v>0</v>
+      </c>
+      <c r="B40" s="6">
         <v>39</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="6">
         <v>3.7774971723381533E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="8">
-        <v>0</v>
-      </c>
-      <c r="B41" s="8">
+      <c r="A41" s="6">
+        <v>0</v>
+      </c>
+      <c r="B41" s="6">
         <v>40</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="6">
         <v>3.8056420537358172E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="8">
-        <v>0</v>
-      </c>
-      <c r="B42" s="8">
+      <c r="A42" s="6">
+        <v>0</v>
+      </c>
+      <c r="B42" s="6">
         <v>41</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="6">
         <v>3.8489913626744553E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
-        <v>0</v>
-      </c>
-      <c r="B43" s="8">
+      <c r="A43" s="6">
+        <v>0</v>
+      </c>
+      <c r="B43" s="6">
         <v>42</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="6">
         <v>3.8828913271326211E-2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
-        <v>0</v>
-      </c>
-      <c r="B44" s="8">
+      <c r="A44" s="6">
+        <v>0</v>
+      </c>
+      <c r="B44" s="6">
         <v>43</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="6">
         <v>3.8915424852211743E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
-        <v>0</v>
-      </c>
-      <c r="B45" s="8">
+      <c r="A45" s="6">
+        <v>0</v>
+      </c>
+      <c r="B45" s="6">
         <v>44</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="6">
         <v>3.9224144229902523E-2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="8">
-        <v>0</v>
-      </c>
-      <c r="B46" s="8">
+      <c r="A46" s="6">
+        <v>0</v>
+      </c>
+      <c r="B46" s="6">
         <v>45</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="6">
         <v>3.9421649415220895E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="8">
-        <v>0</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="6">
+        <v>0</v>
+      </c>
+      <c r="B47" s="6">
         <v>46</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="6">
         <v>3.9495100727106977E-2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="8">
-        <v>0</v>
-      </c>
-      <c r="B48" s="8">
+      <c r="A48" s="6">
+        <v>0</v>
+      </c>
+      <c r="B48" s="6">
         <v>47</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="6">
         <v>3.9679731487326481E-2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
-        <v>0</v>
-      </c>
-      <c r="B49" s="8">
+      <c r="A49" s="6">
+        <v>0</v>
+      </c>
+      <c r="B49" s="6">
         <v>48</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="6">
         <v>3.980159479077483E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="8">
-        <v>0</v>
-      </c>
-      <c r="B50" s="8">
+      <c r="A50" s="6">
+        <v>0</v>
+      </c>
+      <c r="B50" s="6">
         <v>49</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="6">
         <v>4.0207915648931766E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
-        <v>0</v>
-      </c>
-      <c r="B51" s="8">
+      <c r="A51" s="6">
+        <v>0</v>
+      </c>
+      <c r="B51" s="6">
         <v>50</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="6">
         <v>4.0221039434912016E-2</v>
       </c>
     </row>

--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8E182A-8F93-4563-A0BE-F5AE984E7498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5965FBC8-9A67-4CA9-B322-8C695AD36BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="zero_rates_alt" sheetId="1" r:id="rId1"/>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20">
         <v>19</v>

--- a/inputs.xlsx
+++ b/inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d-fine\Projects\SII Review Tool\SII Review Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5965FBC8-9A67-4CA9-B322-8C695AD36BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB54F301-C41E-4029-8936-BA98FE0D7196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43200" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="zero_rates_alt" sheetId="1" r:id="rId1"/>
@@ -6004,7 +6004,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B23">
@@ -6134,7 +6134,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="6">
@@ -6199,7 +6199,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B26">
@@ -6329,7 +6329,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="6">
@@ -6394,7 +6394,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="6">
@@ -6459,7 +6459,7 @@
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B30">
@@ -6654,7 +6654,7 @@
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B33">
@@ -6719,7 +6719,7 @@
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B34">
@@ -6784,7 +6784,7 @@
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B35" s="6">
@@ -6849,7 +6849,7 @@
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="6">
@@ -6979,7 +6979,7 @@
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B38">
@@ -7044,7 +7044,7 @@
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B39">
@@ -7109,7 +7109,7 @@
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B40">
@@ -7174,7 +7174,7 @@
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B41">
@@ -7245,7 +7245,7 @@
       <c r="AB41" s="5"/>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B42">
@@ -7316,7 +7316,7 @@
       <c r="AB42" s="5"/>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B43">
@@ -7387,7 +7387,7 @@
       <c r="AB43" s="5"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B44">
@@ -7600,7 +7600,7 @@
       <c r="AB46" s="5"/>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B47">
@@ -7666,7 +7666,7 @@
       <c r="W47" s="5"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B48">
@@ -7737,7 +7737,7 @@
       <c r="AB48" s="5"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B49">
@@ -7808,7 +7808,7 @@
       <c r="AB49" s="5"/>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B50">
@@ -7879,7 +7879,7 @@
       <c r="AB50" s="5"/>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B51">
